--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -932,10 +932,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>412530</v>
+        <v>411690</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -948,14 +948,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>NOVA ESPERANCA</t>
         </is>
       </c>
       <c r="G5">
-        <v>5170</v>
+        <v>27142</v>
       </c>
       <c r="H5">
-        <v>38.7</v>
+        <v>44.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>411690</v>
+        <v>412530</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -982,14 +982,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NOVA ESPERANCA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G6">
-        <v>27142</v>
+        <v>5170</v>
       </c>
       <c r="H6">
-        <v>36.8</v>
+        <v>38.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1000,75 +1000,75 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>411740</v>
+        <v>411520</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G7">
-        <v>3193</v>
+        <v>429660</v>
       </c>
       <c r="H7">
-        <v>31.3</v>
+        <v>34.2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>411520</v>
+        <v>411110</v>
       </c>
       <c r="B8">
-        <v>122</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G8">
-        <v>429660</v>
+        <v>6228</v>
       </c>
       <c r="H8">
-        <v>28.4</v>
+        <v>32.1</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>410220</v>
+        <v>411740</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G9">
-        <v>4046</v>
+        <v>3193</v>
       </c>
       <c r="H9">
-        <v>24.7</v>
+        <v>31.3</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1102,36 +1102,36 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>411630</v>
+        <v>412625</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G10">
-        <v>4057</v>
+        <v>128106</v>
       </c>
       <c r="H10">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1139,7 +1139,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>21.4</v>
+        <v>25.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>411810</v>
+        <v>410220</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G12">
-        <v>9549</v>
+        <v>4046</v>
       </c>
       <c r="H12">
-        <v>20.9</v>
+        <v>24.7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>410780</v>
+        <v>411630</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1216,18 +1216,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G13">
-        <v>4805</v>
+        <v>4057</v>
       </c>
       <c r="H13">
-        <v>20.8</v>
+        <v>24.6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1238,30 +1238,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>411410</v>
+        <v>411480</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G14">
-        <v>34521</v>
+        <v>44749</v>
       </c>
       <c r="H14">
-        <v>20.3</v>
+        <v>22.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1272,64 +1272,64 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>412625</v>
+        <v>411810</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G15">
-        <v>128106</v>
+        <v>9549</v>
       </c>
       <c r="H15">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="I15">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G16">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H16">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1340,41 +1340,41 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>411750</v>
+        <v>411410</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G17">
-        <v>48695</v>
+        <v>34521</v>
       </c>
       <c r="H17">
-        <v>16.4</v>
+        <v>20.3</v>
       </c>
       <c r="I17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>411110</v>
+        <v>411000</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1386,18 +1386,18 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>IGUARACU</t>
         </is>
       </c>
       <c r="G18">
-        <v>6228</v>
+        <v>5693</v>
       </c>
       <c r="H18">
-        <v>16.1</v>
+        <v>17.6</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1408,64 +1408,64 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>410730</v>
+        <v>411750</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DOUTOR CAMARGO</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G19">
-        <v>6517</v>
+        <v>48695</v>
       </c>
       <c r="H19">
-        <v>15.3</v>
+        <v>16.4</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>411420</v>
+        <v>410730</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>DOUTOR CAMARGO</t>
         </is>
       </c>
       <c r="G20">
-        <v>38313</v>
+        <v>6517</v>
       </c>
       <c r="H20">
-        <v>7.8</v>
+        <v>15.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,35 +1476,69 @@
     </row>
     <row r="21">
       <c r="A21">
+        <v>411420</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MANDAGUARI</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>38313</v>
+      </c>
+      <c r="H21">
+        <v>7.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
         <v>410210</v>
       </c>
-      <c r="B21">
-        <v>2</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>ASTORGA</t>
         </is>
       </c>
-      <c r="G21">
+      <c r="G22">
         <v>26203</v>
       </c>
-      <c r="H21">
+      <c r="H22">
         <v>7.6</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
         <v>0</v>
       </c>
     </row>
@@ -1515,7 +1549,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1552,13 +1586,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1567,49 +1601,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>VILA MORANGUEIRA</t>
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VILA MORANGUEIRA</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1624,7 +1658,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL REQUIAO</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B6">
@@ -1634,7 +1668,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1643,26 +1677,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>CONJUNTO HABITACIONAL REQUIAO</t>
         </is>
       </c>
       <c r="B8">
@@ -1672,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1681,7 +1715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B9">
@@ -1700,26 +1734,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B11">
@@ -1729,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1738,11 +1772,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1757,11 +1791,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1770,23 +1804,23 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1795,7 +1829,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B15">
@@ -1805,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1814,7 +1848,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B16">
@@ -1824,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1833,7 +1867,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B17">
@@ -1852,7 +1886,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B18">
@@ -1871,7 +1905,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B19">
@@ -1890,7 +1924,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B20">
@@ -1900,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1909,7 +1943,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B21">
@@ -1928,7 +1962,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B22">
@@ -1938,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1947,7 +1981,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B23">
@@ -1957,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1966,112 +2000,112 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2080,17 +2114,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2099,45 +2133,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B33">
@@ -2147,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2156,7 +2190,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B34">
@@ -2175,7 +2209,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B35">
@@ -2194,7 +2228,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B36">
@@ -2213,7 +2247,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B37">
@@ -2232,7 +2266,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B38">
@@ -2242,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -2251,7 +2285,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B39">
@@ -2261,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2270,7 +2304,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B40">
@@ -2280,7 +2314,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2289,7 +2323,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B41">
@@ -2308,7 +2342,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B42">
@@ -2327,7 +2361,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B43">
@@ -2346,26 +2380,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B45">
@@ -2384,7 +2418,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B46">
@@ -2403,26 +2437,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B48">
@@ -2441,7 +2475,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B49">
@@ -2451,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2460,7 +2494,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B50">
@@ -2470,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2479,7 +2513,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B51">
@@ -2498,7 +2532,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B52">
@@ -2508,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2517,26 +2551,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B54">
@@ -2555,7 +2589,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B55">
@@ -2574,7 +2608,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B56">
@@ -2584,7 +2618,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2593,7 +2627,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B57">
@@ -2612,7 +2646,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B58">
@@ -2631,7 +2665,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B59">
@@ -2650,7 +2684,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B60">
@@ -2660,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2669,7 +2703,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B61">
@@ -2688,7 +2722,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B62">
@@ -2707,7 +2741,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B63">
@@ -2717,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2726,26 +2760,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B65">
@@ -2764,7 +2798,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B66">
@@ -2774,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2783,7 +2817,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B67">
@@ -2802,7 +2836,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B68">
@@ -2812,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2821,7 +2855,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B69">
@@ -2840,7 +2874,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B70">
@@ -2859,7 +2893,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B71">
@@ -2878,7 +2912,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B72">
@@ -2897,7 +2931,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B73">
@@ -2916,7 +2950,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B74">
@@ -2926,7 +2960,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2935,7 +2969,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B75">
@@ -2954,7 +2988,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B76">
@@ -2973,7 +3007,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B77">
@@ -2983,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2992,7 +3026,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B78">
@@ -3011,7 +3045,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B79">
@@ -3030,7 +3064,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B80">
@@ -3040,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3049,7 +3083,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B81">
@@ -3068,7 +3102,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>SANTA TEREZINHA</t>
         </is>
       </c>
       <c r="B82">
@@ -3078,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3087,19 +3121,209 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SUMARE</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VILA ESPERANCA</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VILA NOVA</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VILA SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ZONA 05</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ZONA 06</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ZONA 08</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>ZONA 7</t>
         </is>
       </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83">
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+      <c r="E93">
         <v>0</v>
       </c>
     </row>
@@ -3110,7 +3334,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3143,7 +3367,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>ALVAMAR</t>
         </is>
       </c>
       <c r="B2">
@@ -3153,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3162,17 +3386,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALVAMAR</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3181,7 +3405,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>COMETA</t>
         </is>
       </c>
       <c r="B4">
@@ -3191,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3200,7 +3424,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B5">
@@ -3219,36 +3443,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3257,26 +3481,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMETA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B9">
@@ -3295,7 +3519,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B10">
@@ -3305,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3314,7 +3538,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B11">
@@ -3333,7 +3557,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B12">
@@ -3343,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3352,7 +3576,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B13">
@@ -3371,7 +3595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B14">
@@ -3381,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3390,7 +3614,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B15">
@@ -3409,7 +3633,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B16">
@@ -3419,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3428,7 +3652,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B17">
@@ -3447,7 +3671,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B18">
@@ -3466,7 +3690,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B19">
@@ -3485,7 +3709,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B20">
@@ -3504,19 +3728,95 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>NOVA PAULISTA</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NOVO PANORAMA</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PANORAMA</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR II</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
         <v>0</v>
       </c>
     </row>
@@ -3527,7 +3827,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3639,7 +3939,17 @@
         </is>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3649,7 +3959,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4134,7 +4444,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -4147,7 +4457,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -4160,7 +4470,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -4173,7 +4483,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -4182,11 +4492,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -4195,11 +4505,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C42">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -4208,11 +4518,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44">
@@ -4221,11 +4531,63 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>10</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C44">
-        <v>6</v>
+      <c r="C45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -13,6 +13,7 @@
     <sheet name="casos_bairro_sarandi" sheetId="4" r:id="rId4"/>
     <sheet name="serie_temporal" sheetId="5" r:id="rId5"/>
     <sheet name="serie_por_classificacao" sheetId="6" r:id="rId6"/>
+    <sheet name="variacao_semanal" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -773,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -932,10 +933,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>411690</v>
+        <v>412530</v>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -948,14 +949,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NOVA ESPERANCA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G5">
-        <v>27142</v>
+        <v>5170</v>
       </c>
       <c r="H5">
-        <v>44.2</v>
+        <v>38.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -966,10 +967,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>412530</v>
+        <v>411690</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -982,14 +983,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>NOVA ESPERANCA</t>
         </is>
       </c>
       <c r="G6">
-        <v>5170</v>
+        <v>27142</v>
       </c>
       <c r="H6">
-        <v>38.7</v>
+        <v>36.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1000,75 +1001,75 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>411520</v>
+        <v>411740</v>
       </c>
       <c r="B7">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G7">
-        <v>429660</v>
+        <v>3193</v>
       </c>
       <c r="H7">
-        <v>34.2</v>
+        <v>31.3</v>
       </c>
       <c r="I7">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>411110</v>
+        <v>411520</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G8">
-        <v>6228</v>
+        <v>429660</v>
       </c>
       <c r="H8">
-        <v>32.1</v>
+        <v>28.4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>411740</v>
+        <v>410220</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1084,14 +1085,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G9">
-        <v>3193</v>
+        <v>4046</v>
       </c>
       <c r="H9">
-        <v>31.3</v>
+        <v>24.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1102,36 +1103,36 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>412625</v>
+        <v>411630</v>
       </c>
       <c r="B10">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G10">
-        <v>128106</v>
+        <v>4057</v>
       </c>
       <c r="H10">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="I10">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1139,7 +1140,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1160,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>25.7</v>
+        <v>21.4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,10 +1171,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>410220</v>
+        <v>411810</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1186,14 +1187,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G12">
-        <v>4046</v>
+        <v>9549</v>
       </c>
       <c r="H12">
-        <v>24.7</v>
+        <v>20.9</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1204,7 +1205,7 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>411630</v>
+        <v>410780</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1216,18 +1217,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G13">
-        <v>4057</v>
+        <v>4805</v>
       </c>
       <c r="H13">
-        <v>24.6</v>
+        <v>20.8</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1238,30 +1239,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>411480</v>
+        <v>411410</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G14">
-        <v>44749</v>
+        <v>34521</v>
       </c>
       <c r="H14">
-        <v>22.3</v>
+        <v>20.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1272,64 +1273,64 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>411810</v>
+        <v>412625</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G15">
-        <v>9549</v>
+        <v>128106</v>
       </c>
       <c r="H15">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>410780</v>
+        <v>411480</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G16">
-        <v>4805</v>
+        <v>44749</v>
       </c>
       <c r="H16">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1340,41 +1341,41 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>411410</v>
+        <v>411750</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G17">
-        <v>34521</v>
+        <v>48695</v>
       </c>
       <c r="H17">
-        <v>20.3</v>
+        <v>16.4</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>411000</v>
+        <v>411110</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1386,18 +1387,18 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IGUARACU</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G18">
-        <v>5693</v>
+        <v>6228</v>
       </c>
       <c r="H18">
-        <v>17.6</v>
+        <v>16.1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1408,64 +1409,64 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>411750</v>
+        <v>410730</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>DOUTOR CAMARGO</t>
         </is>
       </c>
       <c r="G19">
-        <v>48695</v>
+        <v>6517</v>
       </c>
       <c r="H19">
-        <v>16.4</v>
+        <v>15.3</v>
       </c>
       <c r="I19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>410730</v>
+        <v>411420</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DOUTOR CAMARGO</t>
+          <t>MANDAGUARI</t>
         </is>
       </c>
       <c r="G20">
-        <v>6517</v>
+        <v>38313</v>
       </c>
       <c r="H20">
-        <v>15.3</v>
+        <v>7.8</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,69 +1477,35 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411420</v>
+        <v>410210</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G21">
-        <v>38313</v>
+        <v>26203</v>
       </c>
       <c r="H21">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>410210</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ASTORGA</t>
-        </is>
-      </c>
-      <c r="G22">
-        <v>26203</v>
-      </c>
-      <c r="H22">
-        <v>7.6</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
         <v>0</v>
       </c>
     </row>
@@ -1549,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1586,13 +1553,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1601,49 +1568,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VILA MORANGUEIRA</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>VILA MORANGUEIRA</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1658,7 +1625,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>CONJUNTO HABITACIONAL REQUIAO</t>
         </is>
       </c>
       <c r="B6">
@@ -1668,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1677,26 +1644,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL REQUIAO</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B8">
@@ -1706,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1715,7 +1682,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B9">
@@ -1734,26 +1701,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B11">
@@ -1763,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1772,11 +1739,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1791,11 +1758,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1804,23 +1771,23 @@
         <v>2</v>
       </c>
       <c r="E13">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1829,7 +1796,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B15">
@@ -1839,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1848,7 +1815,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B16">
@@ -1858,7 +1825,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1867,7 +1834,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B17">
@@ -1886,7 +1853,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B18">
@@ -1905,7 +1872,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B19">
@@ -1924,7 +1891,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B20">
@@ -1934,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1943,7 +1910,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B21">
@@ -1962,7 +1929,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B22">
@@ -1972,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1981,7 +1948,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B23">
@@ -1991,7 +1958,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2000,112 +1967,112 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2114,17 +2081,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2133,45 +2100,45 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B32">
         <v>1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B33">
@@ -2181,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2190,7 +2157,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B34">
@@ -2209,7 +2176,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B35">
@@ -2228,7 +2195,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B36">
@@ -2247,7 +2214,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B37">
@@ -2266,7 +2233,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B38">
@@ -2276,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -2285,7 +2252,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B39">
@@ -2295,7 +2262,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2304,7 +2271,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B40">
@@ -2314,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2323,7 +2290,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B41">
@@ -2342,7 +2309,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B42">
@@ -2361,7 +2328,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B43">
@@ -2380,26 +2347,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B45">
@@ -2418,7 +2385,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B46">
@@ -2437,26 +2404,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B48">
@@ -2475,7 +2442,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B49">
@@ -2485,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2494,7 +2461,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B50">
@@ -2504,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2513,7 +2480,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B51">
@@ -2532,7 +2499,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B52">
@@ -2542,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2551,26 +2518,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B54">
@@ -2589,7 +2556,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B55">
@@ -2608,7 +2575,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B56">
@@ -2618,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2627,7 +2594,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B57">
@@ -2646,7 +2613,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B58">
@@ -2665,7 +2632,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B59">
@@ -2684,7 +2651,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B60">
@@ -2694,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2703,7 +2670,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B61">
@@ -2722,7 +2689,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B62">
@@ -2741,7 +2708,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B63">
@@ -2751,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2760,26 +2727,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B65">
@@ -2798,7 +2765,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B66">
@@ -2808,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2817,7 +2784,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B67">
@@ -2836,7 +2803,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B68">
@@ -2846,7 +2813,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2855,7 +2822,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B69">
@@ -2874,7 +2841,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B70">
@@ -2893,7 +2860,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B71">
@@ -2912,7 +2879,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B72">
@@ -2931,7 +2898,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>TUIUTI</t>
         </is>
       </c>
       <c r="B73">
@@ -2950,7 +2917,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B74">
@@ -2960,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2969,7 +2936,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B75">
@@ -2988,7 +2955,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B76">
@@ -3007,7 +2974,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B77">
@@ -3017,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3026,7 +2993,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B78">
@@ -3045,7 +3012,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B79">
@@ -3064,7 +3031,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B80">
@@ -3074,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3083,7 +3050,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B81">
@@ -3102,7 +3069,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>ZONA 3</t>
         </is>
       </c>
       <c r="B82">
@@ -3112,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3121,7 +3088,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B83">
@@ -3131,199 +3098,9 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SUMARE</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
-      </c>
-      <c r="D84">
-        <v>0</v>
-      </c>
-      <c r="E84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TUIUTI</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85">
-        <v>0</v>
-      </c>
-      <c r="D85">
-        <v>0</v>
-      </c>
-      <c r="E85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>VILA ESPERANCA</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
-      <c r="D86">
-        <v>0</v>
-      </c>
-      <c r="E86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>VILA NOVA</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-      <c r="E87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>VILA SANTA IZABEL</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>1</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
-      </c>
-      <c r="D88">
-        <v>0</v>
-      </c>
-      <c r="E88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>ZONA 05</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>1</v>
-      </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>ZONA 06</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>1</v>
-      </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>ZONA 08</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>1</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
-      </c>
-      <c r="D91">
-        <v>0</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>ZONA 3</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>1</v>
-      </c>
-      <c r="C92">
-        <v>1</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-      <c r="E92">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>ZONA 7</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93">
-        <v>0</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-      <c r="E93">
         <v>0</v>
       </c>
     </row>
@@ -3334,7 +3111,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3367,7 +3144,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALVAMAR</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B2">
@@ -3377,7 +3154,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3386,17 +3163,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>ALVAMAR</t>
         </is>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3405,7 +3182,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COMETA</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B4">
@@ -3415,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -3424,7 +3201,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B5">
@@ -3443,36 +3220,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3481,26 +3258,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>COMETA</t>
         </is>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B9">
@@ -3519,7 +3296,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B10">
@@ -3529,7 +3306,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3538,7 +3315,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B11">
@@ -3557,7 +3334,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B12">
@@ -3567,7 +3344,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -3576,7 +3353,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B13">
@@ -3595,7 +3372,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B14">
@@ -3605,7 +3382,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3614,7 +3391,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B15">
@@ -3633,7 +3410,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B16">
@@ -3643,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -3652,7 +3429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B17">
@@ -3671,7 +3448,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B18">
@@ -3690,7 +3467,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>NOVO PANORAMA</t>
         </is>
       </c>
       <c r="B19">
@@ -3709,7 +3486,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>PARQUE ALVAMAR II</t>
         </is>
       </c>
       <c r="B20">
@@ -3728,7 +3505,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>SAO PAULO</t>
         </is>
       </c>
       <c r="B21">
@@ -3738,85 +3515,9 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NOVO PANORAMA</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>PANORAMA</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PARQUE ALVAMAR II</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SAO PAULO</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25">
-        <v>0</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25">
         <v>0</v>
       </c>
     </row>
@@ -3827,7 +3528,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3939,17 +3640,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3959,7 +3650,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4444,7 +4135,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -4457,7 +4148,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -4470,7 +4161,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -4483,7 +4174,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -4492,11 +4183,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -4505,11 +4196,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
@@ -4518,11 +4209,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C43">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4531,63 +4222,177 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SEM_NOT</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>variacao</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>var_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>-6</v>
+      </c>
+      <c r="D5">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>26</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>23.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>21</v>
+      </c>
+      <c r="C10">
+        <v>-11</v>
+      </c>
+      <c r="D10">
+        <v>-34.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>11</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Influenza</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47">
-        <v>11</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Não classificado</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>11</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C48">
-        <v>5</v>
+      <c r="B11">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>28.6</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -774,7 +774,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>411640</v>
+        <v>411690</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -911,18 +911,18 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>NOVA ESPERANCA</t>
         </is>
       </c>
       <c r="G4">
-        <v>3669</v>
+        <v>27142</v>
       </c>
       <c r="H4">
-        <v>54.5</v>
+        <v>55.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>412530</v>
+        <v>411640</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -945,18 +945,18 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G5">
-        <v>5170</v>
+        <v>3669</v>
       </c>
       <c r="H5">
-        <v>38.7</v>
+        <v>54.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>411690</v>
+        <v>411090</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -983,14 +983,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NOVA ESPERANCA</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G6">
-        <v>27142</v>
+        <v>4530</v>
       </c>
       <c r="H6">
-        <v>36.8</v>
+        <v>44.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>411740</v>
+        <v>412530</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1017,14 +1017,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G7">
-        <v>3193</v>
+        <v>5170</v>
       </c>
       <c r="H7">
-        <v>31.3</v>
+        <v>38.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1038,16 +1038,16 @@
         <v>411520</v>
       </c>
       <c r="B8">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1058,21 +1058,21 @@
         <v>429660</v>
       </c>
       <c r="H8">
-        <v>28.4</v>
+        <v>36.1</v>
       </c>
       <c r="I8">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>410220</v>
+        <v>411110</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1085,14 +1085,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G9">
-        <v>4046</v>
+        <v>6228</v>
       </c>
       <c r="H9">
-        <v>24.7</v>
+        <v>32.1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>411630</v>
+        <v>411740</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1115,18 +1115,18 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G10">
-        <v>4057</v>
+        <v>3193</v>
       </c>
       <c r="H10">
-        <v>24.6</v>
+        <v>31.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1137,78 +1137,78 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>410590</v>
+        <v>412625</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COLORADO</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G11">
-        <v>23313</v>
+        <v>128106</v>
       </c>
       <c r="H11">
-        <v>21.4</v>
+        <v>28.9</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>411810</v>
+        <v>411480</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G12">
-        <v>9549</v>
+        <v>44749</v>
       </c>
       <c r="H12">
-        <v>20.9</v>
+        <v>26.8</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>410780</v>
+        <v>410590</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1217,18 +1217,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>COLORADO</t>
         </is>
       </c>
       <c r="G13">
-        <v>4805</v>
+        <v>23313</v>
       </c>
       <c r="H13">
-        <v>20.8</v>
+        <v>25.7</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>411410</v>
+        <v>410220</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1251,18 +1251,18 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G14">
-        <v>34521</v>
+        <v>4046</v>
       </c>
       <c r="H14">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1273,64 +1273,64 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>412625</v>
+        <v>411630</v>
       </c>
       <c r="B15">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G15">
-        <v>128106</v>
+        <v>4057</v>
       </c>
       <c r="H15">
-        <v>20.3</v>
+        <v>24.6</v>
       </c>
       <c r="I15">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>411480</v>
+        <v>411410</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G16">
-        <v>44749</v>
+        <v>34521</v>
       </c>
       <c r="H16">
-        <v>20.1</v>
+        <v>23.2</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1341,64 +1341,64 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>411750</v>
+        <v>411360</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G17">
-        <v>48695</v>
+        <v>4707</v>
       </c>
       <c r="H17">
-        <v>16.4</v>
+        <v>21.2</v>
       </c>
       <c r="I17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>411110</v>
+        <v>411810</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G18">
-        <v>6228</v>
+        <v>9549</v>
       </c>
       <c r="H18">
-        <v>16.1</v>
+        <v>20.9</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>410730</v>
+        <v>410780</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1425,14 +1425,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DOUTOR CAMARGO</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G19">
-        <v>6517</v>
+        <v>4805</v>
       </c>
       <c r="H19">
-        <v>15.3</v>
+        <v>20.8</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1443,30 +1443,30 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>411420</v>
+        <v>411000</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>IGUARACU</t>
         </is>
       </c>
       <c r="G20">
-        <v>38313</v>
+        <v>5693</v>
       </c>
       <c r="H20">
-        <v>7.8</v>
+        <v>17.6</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1477,35 +1477,137 @@
     </row>
     <row r="21">
       <c r="A21">
+        <v>411750</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PAICANDU</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>48695</v>
+      </c>
+      <c r="H21">
+        <v>16.4</v>
+      </c>
+      <c r="I21">
+        <v>2.1</v>
+      </c>
+      <c r="J21">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>410730</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DOUTOR CAMARGO</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>6517</v>
+      </c>
+      <c r="H22">
+        <v>15.3</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>411420</v>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MANDAGUARI</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>38313</v>
+      </c>
+      <c r="H23">
+        <v>10.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
         <v>410210</v>
       </c>
-      <c r="B21">
+      <c r="B24">
         <v>2</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>ASTORGA</t>
         </is>
       </c>
-      <c r="G21">
+      <c r="G24">
         <v>26203</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>7.6</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
         <v>0</v>
       </c>
     </row>
@@ -1516,7 +1618,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1553,13 +1655,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1568,55 +1670,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>VILA MORANGUEIRA</t>
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VILA MORANGUEIRA</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
       <c r="E4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1625,17 +1727,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL REQUIAO</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1644,17 +1746,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>3</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1663,7 +1765,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B8">
@@ -1682,45 +1784,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>CONJUNTO HABITACIONAL REQUIAO</t>
         </is>
       </c>
       <c r="B10">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B11">
@@ -1730,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1739,17 +1841,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1758,30 +1860,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1796,17 +1898,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1815,26 +1917,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <v>2</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
       <c r="E16">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B17">
@@ -1844,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1853,7 +1955,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B18">
@@ -1863,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1872,7 +1974,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B19">
@@ -1891,7 +1993,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B20">
@@ -1901,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1910,7 +2012,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B21">
@@ -1920,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1929,7 +2031,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B22">
@@ -1939,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1948,7 +2050,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B23">
@@ -1958,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1967,112 +2069,112 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B24">
         <v>2</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B25">
         <v>2</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2081,17 +2183,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2100,11 +2202,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2119,11 +2221,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -2132,13 +2234,13 @@
         <v>1</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B33">
@@ -2148,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2157,7 +2259,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B34">
@@ -2176,7 +2278,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B35">
@@ -2195,7 +2297,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B36">
@@ -2205,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2214,7 +2316,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B37">
@@ -2224,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2233,45 +2335,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B38">
         <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B39">
         <v>1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B40">
@@ -2281,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2290,7 +2392,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B41">
@@ -2309,7 +2411,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B42">
@@ -2328,7 +2430,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B43">
@@ -2347,26 +2449,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B45">
@@ -2385,7 +2487,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B46">
@@ -2404,26 +2506,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B48">
@@ -2442,7 +2544,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B49">
@@ -2452,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2461,7 +2563,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B50">
@@ -2471,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2480,7 +2582,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B51">
@@ -2499,7 +2601,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B52">
@@ -2509,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2518,26 +2620,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B54">
@@ -2556,7 +2658,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B55">
@@ -2575,7 +2677,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B56">
@@ -2585,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2594,7 +2696,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B57">
@@ -2613,7 +2715,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B58">
@@ -2632,7 +2734,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B59">
@@ -2651,7 +2753,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B60">
@@ -2670,7 +2772,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B61">
@@ -2680,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2689,7 +2791,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B62">
@@ -2708,7 +2810,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B63">
@@ -2718,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2727,7 +2829,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B64">
@@ -2746,7 +2848,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B65">
@@ -2765,26 +2867,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B67">
@@ -2803,7 +2905,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B68">
@@ -2822,7 +2924,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B69">
@@ -2841,7 +2943,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B70">
@@ -2860,7 +2962,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B71">
@@ -2879,7 +2981,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B72">
@@ -2898,7 +3000,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B73">
@@ -2917,7 +3019,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B74">
@@ -2936,7 +3038,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B75">
@@ -2955,7 +3057,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B76">
@@ -2974,7 +3076,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B77">
@@ -2984,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2993,7 +3095,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B78">
@@ -3012,7 +3114,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B79">
@@ -3031,7 +3133,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B80">
@@ -3050,7 +3152,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B81">
@@ -3069,7 +3171,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B82">
@@ -3079,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3088,19 +3190,247 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>PINHEIROS</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QUEBEC</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SUMARE</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VILA NOVA</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VILA SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ZONA 05</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ZONA 06</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ZONA 08</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>ZONA 7</t>
         </is>
       </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
-        <v>0</v>
-      </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83">
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
         <v>0</v>
       </c>
     </row>
@@ -3111,7 +3441,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3144,7 +3474,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>ALVAMAR</t>
         </is>
       </c>
       <c r="B2">
@@ -3154,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -3163,17 +3493,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALVAMAR</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>2</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -3182,11 +3512,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -3201,7 +3531,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>COMETA</t>
         </is>
       </c>
       <c r="B5">
@@ -3211,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -3220,36 +3550,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3258,17 +3588,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMETA</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3277,26 +3607,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B10">
@@ -3306,7 +3636,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3315,7 +3645,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B11">
@@ -3334,7 +3664,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B12">
@@ -3353,7 +3683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B13">
@@ -3372,7 +3702,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B14">
@@ -3391,7 +3721,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B15">
@@ -3410,7 +3740,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B16">
@@ -3429,7 +3759,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B17">
@@ -3448,7 +3778,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B18">
@@ -3458,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3467,7 +3797,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B19">
@@ -3486,7 +3816,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B20">
@@ -3505,19 +3835,133 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>JARDIM UNIVERSAL</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MONTEREY</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NOVA PAULISTA</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NOVO PANORAMA</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR II</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
         <v>0</v>
       </c>
     </row>
@@ -3528,7 +3972,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3620,7 +4064,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -3640,7 +4084,27 @@
         </is>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3650,7 +4114,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3901,7 +4365,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -3923,24 +4387,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -3949,11 +4413,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3962,11 +4426,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -3975,11 +4439,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3988,24 +4452,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -4014,11 +4478,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -4027,11 +4491,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4040,11 +4504,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -4053,24 +4517,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -4079,7 +4543,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C33">
@@ -4092,11 +4556,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -4105,11 +4569,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -4118,24 +4582,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C36">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -4144,11 +4608,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C38">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -4157,11 +4621,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -4170,7 +4634,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C40">
@@ -4179,15 +4643,15 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
@@ -4196,11 +4660,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C42">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -4209,11 +4673,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -4222,11 +4686,128 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>10</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>10</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C44">
-        <v>6</v>
+      <c r="C46">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>11</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>12</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>12</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>12</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4236,7 +4817,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4358,13 +4939,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>23.1</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="10">
@@ -4375,10 +4956,10 @@
         <v>21</v>
       </c>
       <c r="C10">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="D10">
-        <v>-34.4</v>
+        <v>-32.3</v>
       </c>
     </row>
     <row r="11">
@@ -4386,13 +4967,41 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>28.6</v>
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>37</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>14</v>
+      </c>
+      <c r="C13">
+        <v>-23</v>
+      </c>
+      <c r="D13">
+        <v>-62.2</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -13,7 +13,6 @@
     <sheet name="casos_bairro_sarandi" sheetId="4" r:id="rId4"/>
     <sheet name="serie_temporal" sheetId="5" r:id="rId5"/>
     <sheet name="serie_por_classificacao" sheetId="6" r:id="rId6"/>
-    <sheet name="variacao_semanal" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -774,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -831,10 +830,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>412450</v>
+        <v>412830</v>
       </c>
       <c r="B2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -843,18 +842,18 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>UNIFLOR</t>
         </is>
       </c>
       <c r="G2">
-        <v>6463</v>
+        <v>2106</v>
       </c>
       <c r="H2">
-        <v>139.3</v>
+        <v>142.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -865,10 +864,10 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>412830</v>
+        <v>412450</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -877,18 +876,18 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>UNIFLOR</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G3">
-        <v>2106</v>
+        <v>6463</v>
       </c>
       <c r="H3">
-        <v>95</v>
+        <v>139.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -902,7 +901,7 @@
         <v>411690</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -911,7 +910,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -922,7 +921,7 @@
         <v>27142</v>
       </c>
       <c r="H4">
-        <v>55.3</v>
+        <v>95.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -936,7 +935,7 @@
         <v>411640</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -956,7 +955,7 @@
         <v>3669</v>
       </c>
       <c r="H5">
-        <v>54.5</v>
+        <v>81.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -967,10 +966,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>411090</v>
+        <v>411110</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -979,18 +978,18 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G6">
-        <v>4530</v>
+        <v>6228</v>
       </c>
       <c r="H6">
-        <v>44.2</v>
+        <v>64.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1001,7 +1000,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>412530</v>
+        <v>411740</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1017,14 +1016,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G7">
-        <v>5170</v>
+        <v>3193</v>
       </c>
       <c r="H7">
-        <v>38.7</v>
+        <v>62.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1035,44 +1034,44 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>411520</v>
+        <v>410780</v>
       </c>
       <c r="B8">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G8">
-        <v>429660</v>
+        <v>4805</v>
       </c>
       <c r="H8">
-        <v>36.1</v>
+        <v>62.4</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>7.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>411110</v>
+        <v>412530</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1081,18 +1080,18 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G9">
-        <v>6228</v>
+        <v>5170</v>
       </c>
       <c r="H9">
-        <v>32.1</v>
+        <v>58</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1103,70 +1102,70 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>411740</v>
+        <v>411520</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>235</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G10">
-        <v>3193</v>
+        <v>429660</v>
       </c>
       <c r="H10">
-        <v>31.3</v>
+        <v>54.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>412625</v>
+        <v>410590</v>
       </c>
       <c r="B11">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>COLORADO</t>
         </is>
       </c>
       <c r="G11">
-        <v>128106</v>
+        <v>23313</v>
       </c>
       <c r="H11">
-        <v>28.9</v>
+        <v>51.5</v>
       </c>
       <c r="I11">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>2.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1174,7 +1173,7 @@
         <v>411480</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1183,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,21 +1193,21 @@
         <v>44749</v>
       </c>
       <c r="H12">
-        <v>26.8</v>
+        <v>49.2</v>
       </c>
       <c r="I12">
         <v>2.2</v>
       </c>
       <c r="J12">
-        <v>8.300000000000001</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>410590</v>
+        <v>411090</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1217,18 +1216,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COLORADO</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G13">
-        <v>23313</v>
+        <v>4530</v>
       </c>
       <c r="H13">
-        <v>25.7</v>
+        <v>44.2</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1239,30 +1238,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>410220</v>
+        <v>411810</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G14">
-        <v>4046</v>
+        <v>9549</v>
       </c>
       <c r="H14">
-        <v>24.7</v>
+        <v>41.9</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1273,36 +1272,36 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>411630</v>
+        <v>412625</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G15">
-        <v>4057</v>
+        <v>128106</v>
       </c>
       <c r="H15">
-        <v>24.6</v>
+        <v>35.1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="16">
@@ -1310,7 +1309,7 @@
         <v>411410</v>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1319,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1330,7 +1329,7 @@
         <v>34521</v>
       </c>
       <c r="H16">
-        <v>23.2</v>
+        <v>29</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1341,7 +1340,7 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>411360</v>
+        <v>410220</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1357,14 +1356,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G17">
-        <v>4707</v>
+        <v>4046</v>
       </c>
       <c r="H17">
-        <v>21.2</v>
+        <v>24.7</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1375,30 +1374,30 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>411810</v>
+        <v>411630</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G18">
-        <v>9549</v>
+        <v>4057</v>
       </c>
       <c r="H18">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1409,41 +1408,41 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>410780</v>
+        <v>411750</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G19">
-        <v>4805</v>
+        <v>48695</v>
       </c>
       <c r="H19">
-        <v>20.8</v>
+        <v>24.6</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>411000</v>
+        <v>411360</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1455,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IGUARACU</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G20">
-        <v>5693</v>
+        <v>4707</v>
       </c>
       <c r="H20">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1477,44 +1476,44 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411750</v>
+        <v>411000</v>
       </c>
       <c r="B21">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>IGUARACU</t>
         </is>
       </c>
       <c r="G21">
-        <v>48695</v>
+        <v>5693</v>
       </c>
       <c r="H21">
-        <v>16.4</v>
+        <v>17.6</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>410730</v>
+        <v>412340</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1523,18 +1522,18 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DOUTOR CAMARGO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G22">
-        <v>6517</v>
+        <v>11730</v>
       </c>
       <c r="H22">
-        <v>15.3</v>
+        <v>17.1</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1548,16 +1547,16 @@
         <v>411420</v>
       </c>
       <c r="B23">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
         <v>4</v>
-      </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1568,7 +1567,7 @@
         <v>38313</v>
       </c>
       <c r="H23">
-        <v>10.4</v>
+        <v>15.7</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1579,35 +1578,69 @@
     </row>
     <row r="24">
       <c r="A24">
+        <v>410730</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>DOUTOR CAMARGO</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>6517</v>
+      </c>
+      <c r="H24">
+        <v>15.3</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
         <v>410210</v>
       </c>
-      <c r="B24">
-        <v>2</v>
-      </c>
-      <c r="C24">
-        <v>0</v>
-      </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>ASTORGA</t>
         </is>
       </c>
-      <c r="G24">
+      <c r="G25">
         <v>26203</v>
       </c>
-      <c r="H24">
-        <v>7.6</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
+      <c r="H25">
+        <v>11.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
         <v>0</v>
       </c>
     </row>
@@ -1618,7 +1651,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1655,13 +1688,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1670,74 +1703,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VILA MORANGUEIRA</t>
+          <t>CONJUNTO HABITACIONAL REQUIAO</t>
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>VILA MORANGUEIRA</t>
         </is>
       </c>
       <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>4</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1746,17 +1779,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1765,17 +1798,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1784,36 +1817,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL REQUIAO</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1822,17 +1855,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1841,36 +1874,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>3</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1879,7 +1912,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B14">
@@ -1889,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1898,55 +1931,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B15">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B16">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1955,11 +1988,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1974,11 +2007,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1993,30 +2026,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -2031,11 +2064,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2050,11 +2083,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -2069,11 +2102,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -2088,7 +2121,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B25">
@@ -2098,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2107,64 +2140,64 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B26">
         <v>2</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B29">
@@ -2174,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2183,7 +2216,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B30">
@@ -2193,7 +2226,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2202,68 +2235,68 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2278,11 +2311,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2297,11 +2330,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2316,11 +2349,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2335,17 +2368,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2354,36 +2387,36 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2392,17 +2425,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2411,30 +2444,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2449,17 +2482,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44">
         <v>100</v>
@@ -2468,17 +2501,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2487,17 +2520,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2506,30 +2539,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2544,26 +2577,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B50">
@@ -2582,7 +2615,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B51">
@@ -2601,7 +2634,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B52">
@@ -2620,7 +2653,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B53">
@@ -2639,7 +2672,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B54">
@@ -2658,7 +2691,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B55">
@@ -2668,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2677,7 +2710,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B56">
@@ -2687,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2696,7 +2729,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B57">
@@ -2706,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2715,7 +2748,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B58">
@@ -2734,7 +2767,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B59">
@@ -2753,7 +2786,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B60">
@@ -2763,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2772,7 +2805,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B61">
@@ -2782,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2791,26 +2824,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B63">
@@ -2820,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2829,7 +2862,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B64">
@@ -2839,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2848,7 +2881,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B65">
@@ -2867,26 +2900,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B67">
@@ -2896,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2905,7 +2938,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B68">
@@ -2915,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2924,7 +2957,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B69">
@@ -2934,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2943,7 +2976,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B70">
@@ -2962,7 +2995,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B71">
@@ -2981,7 +3014,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B72">
@@ -3000,7 +3033,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B73">
@@ -3010,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3019,26 +3052,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B75">
@@ -3048,7 +3081,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3057,7 +3090,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B76">
@@ -3067,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3076,7 +3109,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B77">
@@ -3095,7 +3128,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B78">
@@ -3114,7 +3147,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B79">
@@ -3124,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3133,7 +3166,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B80">
@@ -3152,7 +3185,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B81">
@@ -3171,7 +3204,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B82">
@@ -3190,7 +3223,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B83">
@@ -3200,7 +3233,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3209,7 +3242,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B84">
@@ -3228,7 +3261,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B85">
@@ -3247,7 +3280,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B86">
@@ -3266,7 +3299,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B87">
@@ -3276,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3285,7 +3318,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B88">
@@ -3295,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3304,7 +3337,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B89">
@@ -3323,7 +3356,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B90">
@@ -3342,7 +3375,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B91">
@@ -3361,7 +3394,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B92">
@@ -3371,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3380,7 +3413,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B93">
@@ -3399,26 +3432,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B95">
@@ -3431,6 +3464,557 @@
         <v>1</v>
       </c>
       <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>JARDIM SOCIAL</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>JARDIM TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>KARINA</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>LEA LEAL</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>LOT SUMARE</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO BELA VISTA</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO MADRID</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>MONTE REI</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>MORANGUEIRA</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NEY BRAGA</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>NOVO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PARQUE DAS BANDEIRAS</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PARQUE INDUSTRIAL 200</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PINHEIROS</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>QUEBEC</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SUMARE</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VILA EMILIA</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>1</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VILA SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ZONA 05</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>ZONA 06</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>1</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ZONA 08</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>1</v>
+      </c>
+      <c r="E123">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
         <v>0</v>
       </c>
     </row>
@@ -3441,7 +4025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3569,7 +4153,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B7">
@@ -3579,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -3588,7 +4172,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B8">
@@ -3598,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -3607,7 +4191,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B9">
@@ -3626,17 +4210,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -3645,45 +4229,45 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B13">
@@ -3702,7 +4286,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B14">
@@ -3712,7 +4296,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -3721,7 +4305,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="B15">
@@ -3731,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -3740,7 +4324,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B16">
@@ -3759,7 +4343,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>ECOVALLEY</t>
         </is>
       </c>
       <c r="B17">
@@ -3778,7 +4362,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>ECOVALLEY ECOLOGIC CITY</t>
         </is>
       </c>
       <c r="B18">
@@ -3797,7 +4381,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B19">
@@ -3816,7 +4400,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B20">
@@ -3826,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3835,7 +4419,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B21">
@@ -3854,7 +4438,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM COMETA</t>
         </is>
       </c>
       <c r="B22">
@@ -3873,7 +4457,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>JARDIM DOM BOSCO</t>
         </is>
       </c>
       <c r="B23">
@@ -3892,7 +4476,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B24">
@@ -3911,7 +4495,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B25">
@@ -3930,7 +4514,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B26">
@@ -3949,19 +4533,114 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>JARDIM TRIANGULO</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MONTEREY</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NOVO PANORAMA</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR II</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>SAO PAULO</t>
         </is>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27">
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
         <v>0</v>
       </c>
     </row>
@@ -3972,7 +4651,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4104,7 +4783,47 @@
         </is>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4114,7 +4833,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4352,7 +5071,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -4361,7 +5080,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro agente etiológico</t>
         </is>
       </c>
       <c r="C19">
@@ -4374,7 +5093,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Outro agente etiológico</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C20">
@@ -4387,24 +5106,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -4413,11 +5132,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -4426,11 +5145,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -4439,11 +5158,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -4452,24 +5171,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -4478,11 +5197,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4491,11 +5210,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -4504,11 +5223,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -4517,24 +5236,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -4543,11 +5262,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -4556,11 +5275,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -4569,11 +5288,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C35">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -4582,24 +5301,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -4608,11 +5327,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -4621,11 +5340,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -4634,24 +5353,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -4660,11 +5379,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -4673,11 +5392,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -4686,37 +5405,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C46">
         <v>10</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -4725,11 +5444,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4738,11 +5457,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C48">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -4751,24 +5470,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -4777,11 +5496,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -4790,11 +5509,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -4803,205 +5522,219 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>12</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C53">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SEM_NOT</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>variacao</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>var_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
+      <c r="C54">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>13</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>13</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>13</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>13</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
         <v>14</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>14</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C60">
         <v>15</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>14</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>14</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>15</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>15</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>15</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>15</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>15</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C67">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>20</v>
-      </c>
-      <c r="C4">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>33.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>14</v>
-      </c>
-      <c r="C5">
-        <v>-6</v>
-      </c>
-      <c r="D5">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>26</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>31</v>
-      </c>
-      <c r="C9">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>21</v>
-      </c>
-      <c r="C10">
-        <v>-10</v>
-      </c>
-      <c r="D10">
-        <v>-32.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>37</v>
-      </c>
-      <c r="C11">
+    </row>
+    <row r="68">
+      <c r="A68">
         <v>16</v>
       </c>
-      <c r="D11">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>16</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C69">
         <v>11</v>
-      </c>
-      <c r="B12">
-        <v>37</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>14</v>
-      </c>
-      <c r="C13">
-        <v>-23</v>
-      </c>
-      <c r="D13">
-        <v>-62.2</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -826,6 +826,856 @@
         <is>
           <t>letalidade_pct</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>412830</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UNIFLOR</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>2106</v>
+      </c>
+      <c r="H2">
+        <v>189.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>412450</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SANTO INACIO</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>6463</v>
+      </c>
+      <c r="H3">
+        <v>139.3</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>411690</v>
+      </c>
+      <c r="B4">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NOVA ESPERANCA</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>27142</v>
+      </c>
+      <c r="H4">
+        <v>132.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>411090</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ITAGUAJE</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>4530</v>
+      </c>
+      <c r="H5">
+        <v>110.4</v>
+      </c>
+      <c r="I5">
+        <v>22.1</v>
+      </c>
+      <c r="J5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>411640</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>NOSSA SENHORA DAS GRACAS</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>3669</v>
+      </c>
+      <c r="H6">
+        <v>109</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>412530</v>
+      </c>
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SAO JORGE DO IVAI</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>5170</v>
+      </c>
+      <c r="H7">
+        <v>96.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>411520</v>
+      </c>
+      <c r="B8">
+        <v>346</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>98</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>MARINGA</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>429660</v>
+      </c>
+      <c r="H8">
+        <v>80.5</v>
+      </c>
+      <c r="I8">
+        <v>5.8</v>
+      </c>
+      <c r="J8">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>410590</v>
+      </c>
+      <c r="B9">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COLORADO</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>23313</v>
+      </c>
+      <c r="H9">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>411110</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ITAMBE</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>6228</v>
+      </c>
+      <c r="H10">
+        <v>64.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>411740</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OURIZONA</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>3193</v>
+      </c>
+      <c r="H11">
+        <v>62.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>410780</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>FLORAI</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>4805</v>
+      </c>
+      <c r="H12">
+        <v>62.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>412360</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SANTA INES</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>1745</v>
+      </c>
+      <c r="H13">
+        <v>57.3</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>411480</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>MARIALVA</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>44749</v>
+      </c>
+      <c r="H14">
+        <v>55.9</v>
+      </c>
+      <c r="I14">
+        <v>4.5</v>
+      </c>
+      <c r="J14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>411810</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PARANACITY</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>9549</v>
+      </c>
+      <c r="H15">
+        <v>52.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>412625</v>
+      </c>
+      <c r="B16">
+        <v>58</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+      <c r="E16">
+        <v>25</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SARANDI</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>128106</v>
+      </c>
+      <c r="H16">
+        <v>45.3</v>
+      </c>
+      <c r="I16">
+        <v>3.1</v>
+      </c>
+      <c r="J16">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>411410</v>
+      </c>
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>MANDAGUACU</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>34521</v>
+      </c>
+      <c r="H17">
+        <v>40.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>412340</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SANTA FE</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>11730</v>
+      </c>
+      <c r="H18">
+        <v>34.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>411750</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>7</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PAICANDU</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>48695</v>
+      </c>
+      <c r="H19">
+        <v>30.8</v>
+      </c>
+      <c r="I19">
+        <v>2.1</v>
+      </c>
+      <c r="J19">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>410220</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ATALAIA</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>4046</v>
+      </c>
+      <c r="H20">
+        <v>24.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>411630</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MUNHOZ DE MELO</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>4057</v>
+      </c>
+      <c r="H21">
+        <v>24.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>411360</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>LOBATO</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>4707</v>
+      </c>
+      <c r="H22">
+        <v>21.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>411000</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>IGUARACU</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>5693</v>
+      </c>
+      <c r="H23">
+        <v>17.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>411420</v>
+      </c>
+      <c r="B24">
+        <v>6</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MANDAGUARI</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>38313</v>
+      </c>
+      <c r="H24">
+        <v>15.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>410210</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ASTORGA</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>26203</v>
+      </c>
+      <c r="H25">
+        <v>15.3</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>410730</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DOUTOR CAMARGO</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>6517</v>
+      </c>
+      <c r="H26">
+        <v>15.3</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -863,6 +1713,2989 @@
         <is>
           <t>letalidade</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JARDIM ALVORADA</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL REQUIAO</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VILA MORANGUEIRA</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>JARDIM SAO SILVESTRE</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PARQUE HORTENCIA</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ZONA 01</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ZONA 04</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ZONA 07</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALVORADA</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JARDIM DIAMANTE</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PARQUE DAS LARANJEIRAS</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JARDIM AMERICA</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JARDIM OLIMPICO</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JARDIM TROPICAL</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO MADRID</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO SUMARE</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PARQUE TARUMA</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VILA MARUMBY</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VILA VARDELINA</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AEROPORTO</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JARDIM ITALIA</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>3</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JARDIM NOVO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JARDIM NOVO OASIS</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JARDIM REAL</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>JARDIM UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PARQUE DAS BANDEIRAS</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>3</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VILA ESPERANCA</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VILA NOVA</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ZONA 7</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>3</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CHACARA PAULISTA</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>2</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>2</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>2</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EBENEZER</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>2</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EVEREST</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>GREVILEAS</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>JARDIM ALVORADA III</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>JARDIM ANDRADE</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JARDIM ARAUCARIA</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>0</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>JARDIM COLINA VERDE</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>JARDIM IPANEMA</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>JARDIM ITAIPU</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>2</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JARDIM MONTE CARLO</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>2</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>JARDIM MONTE REI</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>2</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>JARDIM OASIS</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JARDIM PARAISO</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>2</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>JARDIM SAN REMO</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>2</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>JARDIM SANTA ROSA</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="E61">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>JOAO DE BARROS</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+      <c r="E62">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>2</v>
+      </c>
+      <c r="E63">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PARQUE INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PARQUE PALMEIRAS</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VILA EMILIA</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VILA SANTO ANTONIO</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ZONA 03</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ZONA 06</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ZONA 08</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ALTO DAS GREVILEAS</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ARMAZEM</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>0</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ATLANTA</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AURORA</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AVENIDA</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BELA VISTA</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BOM JARDIM</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BRASIL</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CAMPOS ELISIOS</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CIDADE UNIVERSITARIA</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CONJUNTO JOAO DE BARRO I</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>COPACABANA</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DIAMANTE</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FORTALEZA</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>GALEAO</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>GLEBA PATRIMONIO MARINGA</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>HORTENSIA</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IBIRAPUERA</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IGUATEMI</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>1</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ITAIPU</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>JARDIM BELA VISTA</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>JARDIM BERTIOGA</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>1</v>
+      </c>
+      <c r="E98">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>JARDIM BRASIL</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>1</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>JARDIM BRASILIA</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>JARDIM CANADA</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>1</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>JARDIM COPACABANA</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>JARDIM DAS FLORES</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>JARDIM DIAS I</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>JARDIM DO CARMO</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>JARDIM IMPERIAL II</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>JARDIM INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>JARDIM INTERNORTE</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>JARDIM LIBERDADE</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>1</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>JARDIM MARAVILHA</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>JARDIM NOVO PAULISTA</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>JARDIM OURO COLA</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>1</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>JARDIM PARIS</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>JARDIM PAULISTA</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>JARDIM PINHEIROS III</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>JARDIM REBOUCAS</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>JARDIM SANTA HELENA</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>JARDIM SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>JARDIM SAO JORGE</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>JARDIM SOCIAL</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>JARDIM TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>KARINA</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>LEA LEAL</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>LOT SUMARE</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO BATEL</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO BELA VISTA</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>1</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>LOTEAMENTO GRAJAU</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>MADRID</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>1</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>MARUMBY</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>1</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MONTE REI</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>MORANGUEIRA</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NEY BRAGA</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NOVO HORIZONTE</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>PARAISO</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PARQUE INDUSTRIAL 200</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>PIATA</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>PINHEIROS</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>PORTO SEGURO</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>QUEBEC</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>REQUIAO</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL IBIRAPUERA</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SUMARE</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TARUMA</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>1</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>1</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VILA SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>ZONA 05</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>1</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+      <c r="E156">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ZONA 8</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>1</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -872,7 +4705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -900,6 +4733,690 @@
         <is>
           <t>letalidade</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JARDIM INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ALVAMAR</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>JARDIM UNIVERSAL</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>PANORAMA</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COMETA</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>JARDIM PANORAMA</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>JARDIM VERAO</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MAUA</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NOVA PAULISTA</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NOVO PANORAMA</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VERAO</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALPHAVILLE</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BELA VISTA</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CENTRO</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CEREJEIRA</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ECOVALLEY</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ECOVALLEY ECOLOGIC CITY</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ESPLANADA</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FLORESTA</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>GRALHA AZUL</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JARDIM COMETA</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JARDIM DOM BOSCO</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JARDIM MONTEREY</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JARDIM NOVA PAULISTA</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>JARDIM PERIMETRAL</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>JARDIM TRIANGULO</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MONTEREY</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NOVA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>OURO VERDE</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR II</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VERA CRUZ</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -909,7 +5426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -922,6 +5439,196 @@
         <is>
           <t>total</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -931,7 +5638,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -951,6 +5658,1072 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Outro agente etiológico</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>4</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>4</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Outro agente etiológico</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>6</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>6</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>6</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>6</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>7</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>7</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>7</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>7</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>8</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>8</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>8</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>9</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>9</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>10</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>10</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>10</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>10</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>11</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>11</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>12</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>12</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>12</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>12</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>12</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>13</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>13</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>13</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>14</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>14</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>14</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>14</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>15</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>15</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>15</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>15</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>15</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>16</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>16</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>16</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>16</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>16</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>17</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>17</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>17</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>17</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>18</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>18</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>18</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>18</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>19</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>19</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>19</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>19</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -833,7 +833,7 @@
         <v>412830</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -853,7 +853,7 @@
         <v>2106</v>
       </c>
       <c r="H2">
-        <v>189.9</v>
+        <v>237.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -864,10 +864,10 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>412450</v>
+        <v>411690</v>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -876,18 +876,18 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>NOVA ESPERANCA</t>
         </is>
       </c>
       <c r="G3">
-        <v>6463</v>
+        <v>27142</v>
       </c>
       <c r="H3">
-        <v>139.3</v>
+        <v>180.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>411690</v>
+        <v>412450</v>
       </c>
       <c r="B4">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -914,14 +914,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NOVA ESPERANCA</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G4">
-        <v>27142</v>
+        <v>6463</v>
       </c>
       <c r="H4">
-        <v>132.6</v>
+        <v>154.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,98 +932,98 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>411090</v>
+        <v>411640</v>
       </c>
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G5">
-        <v>4530</v>
+        <v>3669</v>
       </c>
       <c r="H5">
-        <v>110.4</v>
+        <v>136.3</v>
       </c>
       <c r="I5">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>411640</v>
+        <v>411090</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G6">
-        <v>3669</v>
+        <v>4530</v>
       </c>
       <c r="H6">
-        <v>109</v>
+        <v>132.5</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>412530</v>
+        <v>411740</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G7">
-        <v>5170</v>
+        <v>3193</v>
       </c>
       <c r="H7">
-        <v>96.7</v>
+        <v>125.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1037,16 +1037,16 @@
         <v>411520</v>
       </c>
       <c r="B8">
-        <v>346</v>
+        <v>458</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>12</v>
       </c>
       <c r="E8">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1057,41 +1057,41 @@
         <v>429660</v>
       </c>
       <c r="H8">
-        <v>80.5</v>
+        <v>106.6</v>
       </c>
       <c r="I8">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>410590</v>
+        <v>412530</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COLORADO</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G9">
-        <v>23313</v>
+        <v>5170</v>
       </c>
       <c r="H9">
-        <v>72.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>411110</v>
+        <v>410590</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1114,18 +1114,18 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>COLORADO</t>
         </is>
       </c>
       <c r="G10">
-        <v>6228</v>
+        <v>23313</v>
       </c>
       <c r="H10">
-        <v>64.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1136,44 +1136,44 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>411740</v>
+        <v>411480</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G11">
-        <v>3193</v>
+        <v>44749</v>
       </c>
       <c r="H11">
-        <v>62.6</v>
+        <v>67</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1186,14 +1186,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G12">
-        <v>4805</v>
+        <v>6228</v>
       </c>
       <c r="H12">
-        <v>62.4</v>
+        <v>64.2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1204,30 +1204,30 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>412360</v>
+        <v>411810</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G13">
-        <v>1745</v>
+        <v>9549</v>
       </c>
       <c r="H13">
-        <v>57.3</v>
+        <v>62.8</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1238,64 +1238,64 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G14">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H14">
-        <v>55.9</v>
+        <v>62.4</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>411810</v>
+        <v>412360</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G15">
-        <v>9549</v>
+        <v>1745</v>
       </c>
       <c r="H15">
-        <v>52.4</v>
+        <v>57.3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1309,16 +1309,16 @@
         <v>412625</v>
       </c>
       <c r="B16">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C16">
         <v>4</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1329,21 +1329,21 @@
         <v>128106</v>
       </c>
       <c r="H16">
-        <v>45.3</v>
+        <v>53.1</v>
       </c>
       <c r="I16">
         <v>3.1</v>
       </c>
       <c r="J16">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>411410</v>
+        <v>411360</v>
       </c>
       <c r="B17">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1352,18 +1352,18 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G17">
-        <v>34521</v>
+        <v>4707</v>
       </c>
       <c r="H17">
-        <v>40.6</v>
+        <v>42.5</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>412340</v>
+        <v>411410</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1386,18 +1386,18 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G18">
-        <v>11730</v>
+        <v>34521</v>
       </c>
       <c r="H18">
-        <v>34.1</v>
+        <v>40.6</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1411,7 +1411,7 @@
         <v>411750</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         <v>48695</v>
       </c>
       <c r="H19">
-        <v>30.8</v>
+        <v>37</v>
       </c>
       <c r="I19">
         <v>2.1</v>
       </c>
       <c r="J19">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>410220</v>
+        <v>412340</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1454,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G20">
-        <v>4046</v>
+        <v>11730</v>
       </c>
       <c r="H20">
-        <v>24.7</v>
+        <v>34.1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411630</v>
+        <v>410210</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1492,14 +1492,14 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G21">
-        <v>4057</v>
+        <v>26203</v>
       </c>
       <c r="H21">
-        <v>24.6</v>
+        <v>26.7</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>411360</v>
+        <v>410220</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1526,14 +1526,14 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G22">
-        <v>4707</v>
+        <v>4046</v>
       </c>
       <c r="H22">
-        <v>21.2</v>
+        <v>24.7</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>411000</v>
+        <v>411630</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1560,14 +1560,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IGUARACU</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G23">
-        <v>5693</v>
+        <v>4057</v>
       </c>
       <c r="H23">
-        <v>17.6</v>
+        <v>24.6</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>411420</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>38313</v>
       </c>
       <c r="H24">
-        <v>15.7</v>
+        <v>18.3</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>410210</v>
+        <v>411000</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1624,18 +1624,18 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>IGUARACU</t>
         </is>
       </c>
       <c r="G25">
-        <v>26203</v>
+        <v>5693</v>
       </c>
       <c r="H25">
-        <v>15.3</v>
+        <v>17.6</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1646,35 +1646,69 @@
     </row>
     <row r="26">
       <c r="A26">
+        <v>410790</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>FLORESTA</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>11522</v>
+      </c>
+      <c r="H26">
+        <v>17.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
         <v>410730</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>DOUTOR CAMARGO</t>
         </is>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>6517</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>15.3</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
         <v>0</v>
       </c>
     </row>
@@ -1685,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1722,16 +1756,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3">
@@ -1741,7 +1775,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1760,7 +1794,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1769,74 +1803,74 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1851,68 +1885,68 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1927,17 +1961,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1946,17 +1980,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1965,17 +1999,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1984,36 +2018,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2022,30 +2056,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2060,55 +2094,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2117,55 +2151,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23">
         <v>4</v>
       </c>
-      <c r="C23">
-        <v>0</v>
-      </c>
-      <c r="D23">
-        <v>0</v>
-      </c>
       <c r="E23">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2174,17 +2208,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B26">
+        <v>5</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
         <v>3</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2193,11 +2227,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -2206,23 +2240,23 @@
         <v>1</v>
       </c>
       <c r="E27">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2231,11 +2265,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2254,7 +2288,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -2269,74 +2303,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B31">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
         <v>3</v>
       </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
       <c r="E31">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2349,13 +2383,13 @@
         </is>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2364,17 +2398,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2383,17 +2417,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2402,36 +2436,36 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>ZONA 03</t>
         </is>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2440,36 +2474,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>1</v>
       </c>
       <c r="E40">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
         </is>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2478,30 +2512,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2516,11 +2550,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2535,11 +2569,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -2554,17 +2588,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2573,30 +2607,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -2611,11 +2645,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2630,30 +2664,30 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2668,11 +2702,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2687,17 +2721,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM COLINA VERDE</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2706,7 +2740,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B54">
@@ -2725,7 +2759,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B55">
@@ -2744,7 +2778,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B56">
@@ -2754,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2763,7 +2797,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B57">
@@ -2773,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2782,7 +2816,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B58">
@@ -2792,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2801,7 +2835,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B59">
@@ -2811,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2820,26 +2854,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B61">
@@ -2849,7 +2883,7 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>50</v>
@@ -2858,45 +2892,45 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B64">
@@ -2915,7 +2949,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B65">
@@ -2934,7 +2968,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B66">
@@ -2944,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2953,7 +2987,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B67">
@@ -2972,7 +3006,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B68">
@@ -2982,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2991,7 +3025,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ZONA 03</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B69">
@@ -3001,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3010,7 +3044,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B70">
@@ -3020,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3029,7 +3063,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B71">
@@ -3039,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3048,17 +3082,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3067,36 +3101,36 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3105,36 +3139,36 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3143,11 +3177,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>RESIDENCIAL IBIRAPUERA</t>
         </is>
       </c>
       <c r="B77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3162,11 +3196,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3181,11 +3215,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3200,30 +3234,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3238,7 +3272,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B82">
@@ -3257,7 +3291,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B83">
@@ -3267,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3276,7 +3310,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B84">
@@ -3295,7 +3329,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B85">
@@ -3305,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3314,26 +3348,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B87">
@@ -3343,7 +3377,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3352,7 +3386,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B88">
@@ -3362,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3371,7 +3405,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B89">
@@ -3390,7 +3424,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B90">
@@ -3409,7 +3443,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B91">
@@ -3428,7 +3462,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B92">
@@ -3438,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3447,7 +3481,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B93">
@@ -3466,7 +3500,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B94">
@@ -3485,7 +3519,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
         </is>
       </c>
       <c r="B95">
@@ -3495,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3504,7 +3538,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B96">
@@ -3523,45 +3557,45 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B99">
@@ -3571,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3580,7 +3614,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B100">
@@ -3599,7 +3633,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B101">
@@ -3609,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3618,7 +3652,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B102">
@@ -3628,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3637,7 +3671,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B103">
@@ -3647,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3656,7 +3690,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B104">
@@ -3666,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3675,7 +3709,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B105">
@@ -3685,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3694,7 +3728,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B106">
@@ -3713,7 +3747,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B107">
@@ -3732,7 +3766,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B108">
@@ -3751,7 +3785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B109">
@@ -3761,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3770,7 +3804,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B110">
@@ -3780,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3789,7 +3823,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B111">
@@ -3808,26 +3842,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B113">
@@ -3846,7 +3880,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B114">
@@ -3865,7 +3899,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B115">
@@ -3875,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3884,7 +3918,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B116">
@@ -3903,7 +3937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B117">
@@ -3913,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3922,7 +3956,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B118">
@@ -3941,7 +3975,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B119">
@@ -3960,7 +3994,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B120">
@@ -3979,7 +4013,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B121">
@@ -3998,7 +4032,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B122">
@@ -4017,7 +4051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B123">
@@ -4027,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4036,7 +4070,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B124">
@@ -4046,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4055,7 +4089,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B125">
@@ -4074,7 +4108,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B126">
@@ -4093,7 +4127,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B127">
@@ -4103,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4112,26 +4146,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B129">
@@ -4150,7 +4184,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B130">
@@ -4160,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4169,7 +4203,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B131">
@@ -4179,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4188,7 +4222,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B132">
@@ -4207,7 +4241,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B133">
@@ -4217,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4226,7 +4260,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B134">
@@ -4245,7 +4279,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B135">
@@ -4264,7 +4298,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B136">
@@ -4283,45 +4317,45 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B139">
@@ -4340,7 +4374,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B140">
@@ -4359,7 +4393,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B141">
@@ -4378,7 +4412,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B142">
@@ -4397,7 +4431,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B143">
@@ -4416,7 +4450,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B144">
@@ -4426,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4435,7 +4469,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B145">
@@ -4454,7 +4488,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B146">
@@ -4473,7 +4507,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B147">
@@ -4492,7 +4526,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B148">
@@ -4502,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -4511,7 +4545,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B149">
@@ -4530,7 +4564,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B150">
@@ -4549,7 +4583,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B151">
@@ -4559,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -4568,7 +4602,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B152">
@@ -4587,7 +4621,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B153">
@@ -4606,7 +4640,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B154">
@@ -4625,7 +4659,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B155">
@@ -4644,7 +4678,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B156">
@@ -4654,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156">
         <v>100</v>
@@ -4663,38 +4697,475 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>1</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PIATA</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PINHEIROS</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>1</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PORTO SEGURO</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>QUEBEC</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>1</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RECANTO DOS MAGNATAS</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>REQUIAO</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SANENGE</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SUMARE</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TARUMA</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>1</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>VILA BOSQUE</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>1</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>VILA IPIRANGA</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>VILA SANTA IZABEL</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>1</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>1</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>1</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>1</v>
+      </c>
+      <c r="E179">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>ZONA 8</t>
         </is>
       </c>
-      <c r="B158">
-        <v>1</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>1</v>
-      </c>
-      <c r="E158">
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>1</v>
+      </c>
+      <c r="E181">
         <v>0</v>
       </c>
     </row>
@@ -4705,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -4738,7 +5209,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>ALVAMAR</t>
         </is>
       </c>
       <c r="B2">
@@ -4748,7 +5219,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4757,17 +5228,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALVAMAR</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>3</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -4776,26 +5247,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B5">
@@ -4814,55 +5285,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>COMETA</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4871,45 +5342,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>COMETA</t>
         </is>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MAUA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B11">
@@ -4919,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4928,7 +5399,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B12">
@@ -4947,7 +5418,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B13">
@@ -4957,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4966,7 +5437,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR</t>
+          <t>MAUA</t>
         </is>
       </c>
       <c r="B14">
@@ -4976,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4985,30 +5456,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>NOVO PANORAMA</t>
         </is>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5023,17 +5494,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>PARQUE ALVAMAR</t>
         </is>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5042,7 +5513,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B18">
@@ -5052,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5061,7 +5532,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>ALVAMAR II</t>
         </is>
       </c>
       <c r="B19">
@@ -5080,26 +5551,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ECOVALLEY</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ECOVALLEY ECOLOGIC CITY</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="B21">
@@ -5118,7 +5589,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B22">
@@ -5137,26 +5608,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>ECOVALLEY</t>
         </is>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>ECOVALLEY ECOLOGIC CITY</t>
         </is>
       </c>
       <c r="B24">
@@ -5166,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5175,7 +5646,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JARDIM COMETA</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B25">
@@ -5194,7 +5665,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JARDIM DOM BOSCO</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B26">
@@ -5204,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5213,7 +5684,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>JARDIM COMETA</t>
         </is>
       </c>
       <c r="B27">
@@ -5232,7 +5703,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>JARDIM DOM BOSCO</t>
         </is>
       </c>
       <c r="B28">
@@ -5242,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5251,7 +5722,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM NOVA PAULISTA</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B29">
@@ -5261,7 +5732,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5270,7 +5741,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>JARDIM NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B30">
@@ -5280,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5289,7 +5760,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>JARDIM OURO VERDE III</t>
         </is>
       </c>
       <c r="B31">
@@ -5299,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5308,7 +5779,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B32">
@@ -5327,7 +5798,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B33">
@@ -5346,7 +5817,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OURO VERDE</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B34">
@@ -5365,7 +5836,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>NACOES</t>
         </is>
       </c>
       <c r="B35">
@@ -5375,7 +5846,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5384,7 +5855,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>NOVA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B36">
@@ -5394,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5403,19 +5874,95 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>NOVA INDEPENDENCIA I</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OURO VERDE</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PARQUE ALVAMAR II</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>VERA CRUZ</t>
         </is>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37">
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
         <v>0</v>
       </c>
     </row>
@@ -5426,7 +5973,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5518,7 +6065,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -5628,7 +6175,37 @@
         </is>
       </c>
       <c r="B20">
-        <v>45</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -5638,7 +6215,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6032,7 +6609,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -6045,7 +6622,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -6084,7 +6661,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -6097,7 +6674,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -6110,7 +6687,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -6136,7 +6713,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -6145,11 +6722,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -6158,24 +6735,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -6184,11 +6761,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -6197,11 +6774,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
@@ -6210,24 +6787,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C44">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C45">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -6236,11 +6813,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -6249,11 +6826,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -6262,24 +6839,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C48">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C49">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -6288,11 +6865,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -6301,11 +6878,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -6314,37 +6891,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C52">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C53">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -6353,37 +6930,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C57">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -6392,11 +6969,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -6405,37 +6982,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C61">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
@@ -6444,11 +7021,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -6457,11 +7034,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C63">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -6470,37 +7047,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C66">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -6509,11 +7086,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -6522,11 +7099,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -6535,7 +7112,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C69">
@@ -6544,28 +7121,28 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C71">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -6574,11 +7151,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C72">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73">
@@ -6587,37 +7164,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C73">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C74">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C75">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -6626,11 +7203,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
@@ -6639,37 +7216,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C77">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C78">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C79">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
@@ -6678,11 +7255,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="81">
@@ -6691,37 +7268,167 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C81">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C82">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>20</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>20</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>20</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C83">
+      <c r="C86">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>21</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>21</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>21</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>21</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>22</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>22</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C92">
         <v>11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>22</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -867,7 +867,7 @@
         <v>411690</v>
       </c>
       <c r="B3">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>27142</v>
       </c>
       <c r="H3">
-        <v>180.5</v>
+        <v>206.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>412450</v>
+        <v>411640</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -910,18 +910,18 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G4">
-        <v>6463</v>
+        <v>3669</v>
       </c>
       <c r="H4">
-        <v>154.7</v>
+        <v>163.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,10 +932,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>411640</v>
+        <v>412450</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -944,18 +944,18 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G5">
-        <v>3669</v>
+        <v>6463</v>
       </c>
       <c r="H5">
-        <v>136.3</v>
+        <v>154.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -969,7 +969,7 @@
         <v>411090</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -989,13 +989,13 @@
         <v>4530</v>
       </c>
       <c r="H6">
-        <v>132.5</v>
+        <v>154.5</v>
       </c>
       <c r="I6">
         <v>22.1</v>
       </c>
       <c r="J6">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="7">
@@ -1034,98 +1034,98 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>411520</v>
+        <v>410220</v>
       </c>
       <c r="B8">
-        <v>458</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G8">
-        <v>429660</v>
+        <v>4046</v>
       </c>
       <c r="H8">
-        <v>106.6</v>
+        <v>123.6</v>
       </c>
       <c r="I8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>6.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>412530</v>
+        <v>411520</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>506</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>142</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G9">
-        <v>5170</v>
+        <v>429660</v>
       </c>
       <c r="H9">
-        <v>96.7</v>
+        <v>117.8</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>410590</v>
+        <v>412530</v>
       </c>
       <c r="B10">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COLORADO</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G10">
-        <v>23313</v>
+        <v>5170</v>
       </c>
       <c r="H10">
-        <v>94.40000000000001</v>
+        <v>116.1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1136,98 +1136,98 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>411480</v>
+        <v>410590</v>
       </c>
       <c r="B11">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
         <v>2</v>
       </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>16</v>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>COLORADO</t>
         </is>
       </c>
       <c r="G11">
-        <v>44749</v>
+        <v>23313</v>
       </c>
       <c r="H11">
-        <v>67</v>
+        <v>102.9</v>
       </c>
       <c r="I11">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>6.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>411110</v>
+        <v>411480</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G12">
-        <v>6228</v>
+        <v>44749</v>
       </c>
       <c r="H12">
-        <v>64.2</v>
+        <v>69.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>411810</v>
+        <v>411110</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G13">
-        <v>9549</v>
+        <v>6228</v>
       </c>
       <c r="H13">
-        <v>62.8</v>
+        <v>64.2</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1238,30 +1238,30 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>410780</v>
+        <v>411810</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G14">
-        <v>4805</v>
+        <v>9549</v>
       </c>
       <c r="H14">
-        <v>62.4</v>
+        <v>62.8</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>412360</v>
+        <v>410780</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1284,18 +1284,18 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G15">
-        <v>1745</v>
+        <v>4805</v>
       </c>
       <c r="H15">
-        <v>57.3</v>
+        <v>62.4</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1306,78 +1306,78 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>412625</v>
+        <v>412360</v>
       </c>
       <c r="B16">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G16">
-        <v>128106</v>
+        <v>1745</v>
       </c>
       <c r="H16">
-        <v>53.1</v>
+        <v>57.3</v>
       </c>
       <c r="I16">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>411360</v>
+        <v>412625</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G17">
-        <v>4707</v>
+        <v>128106</v>
       </c>
       <c r="H17">
-        <v>42.5</v>
+        <v>57</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>411410</v>
+        <v>411360</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1386,18 +1386,18 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G18">
-        <v>34521</v>
+        <v>4707</v>
       </c>
       <c r="H18">
-        <v>40.6</v>
+        <v>42.5</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1408,78 +1408,78 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>411750</v>
+        <v>411410</v>
       </c>
       <c r="B19">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G19">
-        <v>48695</v>
+        <v>34521</v>
       </c>
       <c r="H19">
-        <v>37</v>
+        <v>40.6</v>
       </c>
       <c r="I19">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>412340</v>
+        <v>411750</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G20">
-        <v>11730</v>
+        <v>48695</v>
       </c>
       <c r="H20">
-        <v>34.1</v>
+        <v>37</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>410210</v>
+        <v>410790</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1488,18 +1488,18 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="G21">
-        <v>26203</v>
+        <v>11522</v>
       </c>
       <c r="H21">
-        <v>26.7</v>
+        <v>34.7</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>410220</v>
+        <v>410210</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1522,18 +1522,18 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G22">
-        <v>4046</v>
+        <v>26203</v>
       </c>
       <c r="H22">
-        <v>24.7</v>
+        <v>34.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>411630</v>
+        <v>412340</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1556,18 +1556,18 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G23">
-        <v>4057</v>
+        <v>11730</v>
       </c>
       <c r="H23">
-        <v>24.6</v>
+        <v>34.1</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1578,30 +1578,30 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>411420</v>
+        <v>411630</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G24">
-        <v>38313</v>
+        <v>4057</v>
       </c>
       <c r="H24">
-        <v>18.3</v>
+        <v>24.6</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1612,30 +1612,30 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>411000</v>
+        <v>411420</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IGUARACU</t>
+          <t>MANDAGUARI</t>
         </is>
       </c>
       <c r="G25">
-        <v>5693</v>
+        <v>38313</v>
       </c>
       <c r="H25">
-        <v>17.6</v>
+        <v>18.3</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1646,10 +1646,10 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>410790</v>
+        <v>411000</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1658,18 +1658,18 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>IGUARACU</t>
         </is>
       </c>
       <c r="G26">
-        <v>11522</v>
+        <v>5693</v>
       </c>
       <c r="H26">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1719,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>7.7</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="3">
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1866,26 +1866,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B8">
         <v>8</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B9">
@@ -1904,55 +1904,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11">
-        <v>42.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1961,7 +1961,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B13">
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1980,7 +1980,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B14">
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1999,17 +1999,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2018,30 +2018,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B16">
         <v>6</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2056,17 +2056,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2075,64 +2075,64 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM COLINA VERDE</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B22">
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2151,26 +2151,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B23">
         <v>5</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B24">
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2189,7 +2189,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B25">
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2208,55 +2208,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2265,17 +2265,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2284,26 +2284,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM NOVO OASIS</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B30">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B31">
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2322,45 +2322,45 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B33">
         <v>4</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>1</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B34">
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2379,39 +2379,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2531,7 +2531,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B43">
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2550,7 +2550,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B44">
@@ -2569,26 +2569,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B46">
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2607,7 +2607,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B47">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2626,7 +2626,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B48">
@@ -2645,7 +2645,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B49">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2664,26 +2664,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B50">
         <v>3</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B51">
@@ -2702,26 +2702,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B53">
@@ -2740,17 +2740,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2759,17 +2759,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2778,17 +2778,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>VILA IPIRANGA</t>
         </is>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2797,11 +2797,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2816,26 +2816,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>BRANCA VIEIRA</t>
         </is>
       </c>
       <c r="B59">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2854,7 +2854,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B60">
@@ -2873,26 +2873,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B62">
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B63">
@@ -2930,7 +2930,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B64">
@@ -2949,7 +2949,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
         </is>
       </c>
       <c r="B65">
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B66">
@@ -2987,7 +2987,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>COPACABANA RESIDENCIAL</t>
         </is>
       </c>
       <c r="B67">
@@ -3006,7 +3006,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B68">
@@ -3025,7 +3025,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B69">
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B70">
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B71">
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B72">
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3101,26 +3101,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B74">
@@ -3130,7 +3130,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3139,26 +3139,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B76">
@@ -3177,7 +3177,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B77">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B78">
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3215,7 +3215,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B79">
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3234,7 +3234,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B80">
@@ -3244,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80">
         <v>50</v>
@@ -3253,7 +3253,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B81">
@@ -3272,17 +3272,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3291,55 +3291,55 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3348,11 +3348,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>RESIDENCIAL IBIRAPUERA</t>
         </is>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3367,11 +3367,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3386,11 +3386,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3405,11 +3405,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3424,11 +3424,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3443,7 +3443,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CIDADE JARDIM</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B91">
@@ -3462,7 +3462,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B92">
@@ -3481,7 +3481,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B93">
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3500,7 +3500,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B94">
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3519,7 +3519,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B95">
@@ -3529,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3538,7 +3538,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B96">
@@ -3557,26 +3557,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B98">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3595,7 +3595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DONA ANGELINA</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B99">
@@ -3614,7 +3614,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>CHACARAS AEROPORTO</t>
         </is>
       </c>
       <c r="B100">
@@ -3633,7 +3633,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B101">
@@ -3652,7 +3652,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B102">
@@ -3671,7 +3671,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GUAIRACA</t>
+          <t>CJ RES PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B103">
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3690,7 +3690,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
         </is>
       </c>
       <c r="B104">
@@ -3709,7 +3709,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B105">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B106">
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3747,26 +3747,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B108">
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3785,7 +3785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JARDIM ATLANTA</t>
+          <t>DISTRITO IGUATEMI</t>
         </is>
       </c>
       <c r="B109">
@@ -3804,7 +3804,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B110">
@@ -3814,7 +3814,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3823,7 +3823,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>JARDIM BELO HORIZONTE IGUATEM</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B111">
@@ -3842,26 +3842,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B113">
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3880,7 +3880,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B114">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>HABITACIONAL SOL NASCENTE</t>
         </is>
       </c>
       <c r="B115">
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -3918,7 +3918,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JARDIM CERRO AZUL</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B116">
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B117">
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>JARDIM DAS ESTACOES</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B118">
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3975,7 +3975,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B119">
@@ -3994,7 +3994,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B120">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JARDIM DOS PASSAROS</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B121">
@@ -4032,7 +4032,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JARDIM EVEREST</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B122">
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4051,7 +4051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JARDIM GUAIRACA</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B123">
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4070,26 +4070,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124">
         <v>1</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B125">
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4108,7 +4108,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B126">
@@ -4127,7 +4127,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA II</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B127">
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4146,26 +4146,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM CIDADE MONCOES</t>
         </is>
       </c>
       <c r="B129">
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4184,7 +4184,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B130">
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B131">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4222,7 +4222,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JARDIM PARIS III</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B132">
@@ -4241,7 +4241,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B133">
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4260,7 +4260,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B134">
@@ -4279,7 +4279,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B135">
@@ -4298,7 +4298,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B136">
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B137">
@@ -4336,7 +4336,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B138">
@@ -4355,7 +4355,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JARDIM TABAETE</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B139">
@@ -4374,7 +4374,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B140">
@@ -4393,26 +4393,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B142">
@@ -4431,7 +4431,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM NOROESTE</t>
         </is>
       </c>
       <c r="B143">
@@ -4450,7 +4450,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B144">
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4469,7 +4469,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B145">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4488,7 +4488,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LUCIANOPOLIS</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B146">
@@ -4507,7 +4507,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B147">
@@ -4526,7 +4526,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B148">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -4545,7 +4545,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B149">
@@ -4564,7 +4564,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B150">
@@ -4583,7 +4583,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B151">
@@ -4602,7 +4602,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B152">
@@ -4621,7 +4621,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B153">
@@ -4640,7 +4640,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PARQUE DA GAVEA</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B154">
@@ -4659,7 +4659,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B155">
@@ -4678,45 +4678,45 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B158">
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL QUEBEC</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B159">
@@ -4754,7 +4754,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B160">
@@ -4773,7 +4773,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B161">
@@ -4792,7 +4792,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B162">
@@ -4802,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -4811,7 +4811,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B163">
@@ -4830,7 +4830,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RECANTO DOS MAGNATAS</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B164">
@@ -4849,7 +4849,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B165">
@@ -4868,7 +4868,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SANENGE</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="B166">
@@ -4887,7 +4887,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B167">
@@ -4906,7 +4906,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B168">
@@ -4916,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -4925,7 +4925,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B169">
@@ -4944,26 +4944,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
         <v>0</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
         </is>
       </c>
       <c r="B171">
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4982,7 +4982,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TROPICAL</t>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
         </is>
       </c>
       <c r="B172">
@@ -5001,7 +5001,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>PIATA</t>
         </is>
       </c>
       <c r="B173">
@@ -5020,7 +5020,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B174">
@@ -5039,7 +5039,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>VILA BOSQUE</t>
+          <t>PORTAL DAS TORRES</t>
         </is>
       </c>
       <c r="B175">
@@ -5058,7 +5058,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>VILA IPIRANGA</t>
+          <t>PORTO SEGURO</t>
         </is>
       </c>
       <c r="B176">
@@ -5077,7 +5077,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B177">
@@ -5096,7 +5096,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>RECANTO DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B178">
@@ -5115,26 +5115,26 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>REQUIAO</t>
         </is>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>SANENGE</t>
         </is>
       </c>
       <c r="B180">
@@ -5153,19 +5153,266 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>1</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>TARUMA</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>1</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>1</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>1</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VILA BOSQUE</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>1</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>VILA SANTO AMARAL</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>1</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>1</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+      <c r="D192">
+        <v>1</v>
+      </c>
+      <c r="E192">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>1</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>ZONA 8</t>
         </is>
       </c>
-      <c r="B181">
-        <v>1</v>
-      </c>
-      <c r="C181">
-        <v>0</v>
-      </c>
-      <c r="D181">
-        <v>1</v>
-      </c>
-      <c r="E181">
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>1</v>
+      </c>
+      <c r="E194">
         <v>0</v>
       </c>
     </row>
@@ -5213,7 +5460,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -5228,102 +5475,102 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B8">
@@ -5342,20 +5589,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B9">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5501,13 +5748,13 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -5973,7 +6220,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6195,7 +6442,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -6205,7 +6452,17 @@
         </is>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -6215,7 +6472,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6596,7 +6853,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -6609,7 +6866,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -6661,7 +6918,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -6687,7 +6944,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
@@ -6765,7 +7022,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -6778,7 +7035,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -6817,7 +7074,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -6830,7 +7087,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -6869,7 +7126,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -6882,7 +7139,7 @@
         </is>
       </c>
       <c r="C51">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -6908,7 +7165,7 @@
         </is>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -6921,7 +7178,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -6947,7 +7204,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
@@ -6973,7 +7230,7 @@
         </is>
       </c>
       <c r="C58">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -7012,7 +7269,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -7038,7 +7295,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
@@ -7077,7 +7334,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -7103,7 +7360,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69">
@@ -7129,7 +7386,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
@@ -7155,7 +7412,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -7233,7 +7490,7 @@
         </is>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -7246,7 +7503,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>28</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
@@ -7259,7 +7516,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
@@ -7272,7 +7529,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
@@ -7298,7 +7555,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
@@ -7311,7 +7568,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85">
@@ -7324,7 +7581,7 @@
         </is>
       </c>
       <c r="C85">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
@@ -7337,7 +7594,7 @@
         </is>
       </c>
       <c r="C86">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -7350,7 +7607,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88">
@@ -7363,7 +7620,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
@@ -7376,7 +7633,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90">
@@ -7389,7 +7646,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91">
@@ -7402,7 +7659,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
@@ -7415,7 +7672,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93">
@@ -7424,11 +7681,63 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>22</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C93">
-        <v>1</v>
+      <c r="C94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>23</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>23</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>23</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -867,7 +867,7 @@
         <v>411690</v>
       </c>
       <c r="B3">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>27142</v>
       </c>
       <c r="H3">
-        <v>206.3</v>
+        <v>232.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>411640</v>
+        <v>410220</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -910,18 +910,18 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G4">
-        <v>3669</v>
+        <v>4046</v>
       </c>
       <c r="H4">
-        <v>163.5</v>
+        <v>173</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,10 +932,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>412450</v>
+        <v>411640</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -944,18 +944,18 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G5">
-        <v>6463</v>
+        <v>3669</v>
       </c>
       <c r="H5">
-        <v>154.7</v>
+        <v>163.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -966,47 +966,47 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>411090</v>
+        <v>412450</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G6">
-        <v>4530</v>
+        <v>6463</v>
       </c>
       <c r="H6">
-        <v>154.5</v>
+        <v>154.7</v>
       </c>
       <c r="I6">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>411740</v>
+        <v>411090</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1016,48 +1016,48 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G7">
-        <v>3193</v>
+        <v>4530</v>
       </c>
       <c r="H7">
-        <v>125.3</v>
+        <v>154.5</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>410220</v>
+        <v>412530</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G8">
-        <v>4046</v>
+        <v>5170</v>
       </c>
       <c r="H8">
-        <v>123.6</v>
+        <v>135.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1071,16 +1071,16 @@
         <v>411520</v>
       </c>
       <c r="B9">
-        <v>506</v>
+        <v>556</v>
       </c>
       <c r="C9">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1091,41 +1091,41 @@
         <v>429660</v>
       </c>
       <c r="H9">
-        <v>117.8</v>
+        <v>129.4</v>
       </c>
       <c r="I9">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>412530</v>
+        <v>411740</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G10">
-        <v>5170</v>
+        <v>3193</v>
       </c>
       <c r="H10">
-        <v>116.1</v>
+        <v>125.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>102.9</v>
+        <v>111.5</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,70 +1170,70 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B12">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G12">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H12">
-        <v>69.3</v>
+        <v>83.2</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>411110</v>
+        <v>411480</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G13">
-        <v>6228</v>
+        <v>44749</v>
       </c>
       <c r="H13">
-        <v>64.2</v>
+        <v>76</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="14">
@@ -1241,7 +1241,7 @@
         <v>411810</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1261,7 +1261,7 @@
         <v>9549</v>
       </c>
       <c r="H14">
-        <v>62.8</v>
+        <v>73.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1288,14 +1288,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G15">
-        <v>4805</v>
+        <v>6228</v>
       </c>
       <c r="H15">
-        <v>62.4</v>
+        <v>64.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1306,70 +1306,70 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>412360</v>
+        <v>412625</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G16">
-        <v>1745</v>
+        <v>128106</v>
       </c>
       <c r="H16">
-        <v>57.3</v>
+        <v>61.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>412625</v>
+        <v>412360</v>
       </c>
       <c r="B17">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G17">
-        <v>128106</v>
+        <v>1745</v>
       </c>
       <c r="H17">
-        <v>57</v>
+        <v>57.3</v>
       </c>
       <c r="I17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1442,78 +1442,78 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>411750</v>
+        <v>410210</v>
       </c>
       <c r="B20">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G20">
-        <v>48695</v>
+        <v>26203</v>
       </c>
       <c r="H20">
-        <v>37</v>
+        <v>38.2</v>
       </c>
       <c r="I20">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>410790</v>
+        <v>411750</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G21">
-        <v>11522</v>
+        <v>48695</v>
       </c>
       <c r="H21">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>410210</v>
+        <v>410790</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1522,18 +1522,18 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="G22">
-        <v>26203</v>
+        <v>11522</v>
       </c>
       <c r="H22">
-        <v>34.3</v>
+        <v>34.7</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>411420</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>2</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>38313</v>
       </c>
       <c r="H25">
-        <v>18.3</v>
+        <v>20.9</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1719,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>11.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="3">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1803,7 +1803,7 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="5">
@@ -1828,7 +1828,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B6">
@@ -1838,7 +1838,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1847,20 +1847,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1879,51 +1879,51 @@
         <v>2</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
       <c r="E9">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B11">
@@ -1942,45 +1942,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B12">
         <v>8</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B14">
@@ -1999,7 +1999,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B15">
@@ -2018,17 +2018,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2037,11 +2037,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JARDIM COLINA VERDE</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -2056,7 +2056,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B18">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2075,26 +2075,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B19">
         <v>6</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B20">
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B21">
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>16.7</v>
@@ -2132,17 +2132,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2151,26 +2151,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B24">
@@ -2180,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2189,45 +2189,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B25">
         <v>5</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B26">
         <v>5</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B27">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2246,7 +2246,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B28">
@@ -2265,55 +2265,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B29">
         <v>5</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2322,26 +2322,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B32">
         <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JARDIM NOVO OASIS</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B33">
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2360,7 +2360,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
         </is>
       </c>
       <c r="B34">
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2379,45 +2379,45 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B36">
         <v>4</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B37">
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2436,26 +2436,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B38">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZONA 03</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B39">
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2474,17 +2474,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
         <v>3</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2493,68 +2493,68 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>ZONA 03</t>
         </is>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2569,26 +2569,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B45">
         <v>3</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="E45">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B46">
@@ -2607,7 +2607,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
         </is>
       </c>
       <c r="B47">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2626,26 +2626,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B49">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2664,7 +2664,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B50">
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2683,7 +2683,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B51">
@@ -2702,26 +2702,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
       <c r="E52">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B53">
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2740,7 +2740,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B54">
@@ -2759,45 +2759,45 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VILA IPIRANGA</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>1</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B57">
@@ -2816,36 +2816,36 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BRANCA VIEIRA</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2854,11 +2854,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>VILA IPIRANGA</t>
         </is>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2873,17 +2873,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2892,11 +2892,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2911,30 +2911,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2949,7 +2949,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+          <t>BRANCA VIEIRA</t>
         </is>
       </c>
       <c r="B65">
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2968,7 +2968,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B66">
@@ -2987,7 +2987,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>COPACABANA RESIDENCIAL</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B67">
@@ -3006,7 +3006,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B68">
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3025,7 +3025,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B69">
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3044,7 +3044,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
         </is>
       </c>
       <c r="B70">
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3063,7 +3063,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B71">
@@ -3073,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3082,7 +3082,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>COPACABANA RESIDENCIAL</t>
         </is>
       </c>
       <c r="B72">
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3101,7 +3101,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B73">
@@ -3120,7 +3120,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B74">
@@ -3139,7 +3139,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B75">
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3158,7 +3158,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B76">
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3177,7 +3177,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B77">
@@ -3187,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B78">
@@ -3215,7 +3215,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B79">
@@ -3234,26 +3234,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B81">
@@ -3263,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3272,7 +3272,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B82">
@@ -3291,26 +3291,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B84">
@@ -3329,7 +3329,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B85">
@@ -3339,7 +3339,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3348,7 +3348,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B86">
@@ -3358,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3367,45 +3367,45 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B89">
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3424,7 +3424,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>RECANTO DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B90">
@@ -3443,11 +3443,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>REQUIAO</t>
         </is>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3462,11 +3462,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>RESIDENCIAL IBIRAPUERA</t>
         </is>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3481,17 +3481,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3500,11 +3500,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>VILA BOSQUE</t>
         </is>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3519,11 +3519,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3538,7 +3538,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B96">
@@ -3557,7 +3557,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B97">
@@ -3576,7 +3576,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B98">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3595,7 +3595,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B99">
@@ -3614,7 +3614,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CHACARAS AEROPORTO</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B100">
@@ -3633,7 +3633,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CIDADE JARDIM</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B101">
@@ -3652,7 +3652,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B102">
@@ -3671,7 +3671,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CJ RES PARIGOT DE SOUZA</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B103">
@@ -3690,7 +3690,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B104">
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3709,7 +3709,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>CHACARAS AEROPORTO</t>
         </is>
       </c>
       <c r="B105">
@@ -3719,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B106">
@@ -3747,26 +3747,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>CJ RES PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B108">
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3785,7 +3785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>DISTRITO IGUATEMI</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B109">
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3804,7 +3804,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>DONA ANGELINA</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B110">
@@ -3823,26 +3823,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B112">
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3861,7 +3861,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>DISTRITO IGUATEMI</t>
         </is>
       </c>
       <c r="B113">
@@ -3880,7 +3880,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GUAIRACA</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B114">
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -3899,7 +3899,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>HABITACIONAL SOL NASCENTE</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B115">
@@ -3918,7 +3918,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B116">
@@ -3928,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B117">
@@ -3956,7 +3956,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B118">
@@ -3975,7 +3975,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>HABITACIONAL SOL NASCENTE</t>
         </is>
       </c>
       <c r="B119">
@@ -3994,7 +3994,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B120">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4013,7 +4013,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>JARDIM ATLANTA</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B121">
@@ -4032,7 +4032,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B122">
@@ -4051,7 +4051,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>JARDIM BELO HORIZONTE IGUATEM</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B123">
@@ -4070,26 +4070,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B125">
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4108,7 +4108,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B126">
@@ -4118,7 +4118,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4127,7 +4127,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B127">
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4146,26 +4146,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JARDIM CERRO AZUL</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JARDIM CIDADE MONCOES</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B129">
@@ -4184,7 +4184,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B130">
@@ -4194,7 +4194,7 @@
         <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4203,7 +4203,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JARDIM DAS ESTACOES</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B131">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4222,7 +4222,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B132">
@@ -4241,7 +4241,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>JARDIM CIDADE MONCOES</t>
         </is>
       </c>
       <c r="B133">
@@ -4260,7 +4260,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JARDIM DOS PASSAROS</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B134">
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4279,7 +4279,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JARDIM EVEREST</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B135">
@@ -4298,7 +4298,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JARDIM GUAIRACA</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B136">
@@ -4308,7 +4308,7 @@
         <v>0</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4317,7 +4317,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B137">
@@ -4336,7 +4336,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B138">
@@ -4355,7 +4355,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B139">
@@ -4374,7 +4374,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA II</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B140">
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4393,26 +4393,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM IGUACU</t>
         </is>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B142">
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4431,7 +4431,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JARDIM NOROESTE</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B143">
@@ -4450,7 +4450,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B144">
@@ -4469,7 +4469,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B145">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -4488,7 +4488,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>JARDIM PARIS III</t>
+          <t>JARDIM MANDACARU</t>
         </is>
       </c>
       <c r="B146">
@@ -4498,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4507,26 +4507,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B148">
@@ -4545,7 +4545,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM NOROESTE</t>
         </is>
       </c>
       <c r="B149">
@@ -4564,7 +4564,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B150">
@@ -4583,7 +4583,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM ORIENTAL</t>
         </is>
       </c>
       <c r="B151">
@@ -4593,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B152">
@@ -4612,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -4621,7 +4621,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JARDIM TABAETE</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B153">
@@ -4640,7 +4640,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM PINHEIROS II</t>
         </is>
       </c>
       <c r="B154">
@@ -4659,7 +4659,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B155">
@@ -4678,7 +4678,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B156">
@@ -4697,7 +4697,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM SANTA ALICE</t>
         </is>
       </c>
       <c r="B157">
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -4716,7 +4716,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B158">
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -4735,7 +4735,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B159">
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -4754,7 +4754,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LUCIANOPOLIS</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B160">
@@ -4773,7 +4773,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B161">
@@ -4792,7 +4792,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM TOQUIO</t>
         </is>
       </c>
       <c r="B162">
@@ -4811,7 +4811,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B163">
@@ -4830,7 +4830,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JOAO DE BARRO</t>
         </is>
       </c>
       <c r="B164">
@@ -4840,7 +4840,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -4849,7 +4849,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B165">
@@ -4868,7 +4868,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OASIS</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B166">
@@ -4887,7 +4887,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B167">
@@ -4906,7 +4906,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PARQUE DA GAVEA</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B168">
@@ -4925,7 +4925,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B169">
@@ -4944,26 +4944,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170">
         <v>0</v>
       </c>
       <c r="E170">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B171">
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4982,7 +4982,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL QUEBEC</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B172">
@@ -4992,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5001,7 +5001,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B173">
@@ -5020,7 +5020,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B174">
@@ -5039,7 +5039,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PORTAL DAS TORRES</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B175">
@@ -5058,7 +5058,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="B176">
@@ -5077,7 +5077,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B177">
@@ -5096,7 +5096,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RECANTO DOS MAGNATAS</t>
+          <t>PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B178">
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -5115,7 +5115,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B179">
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SANENGE</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B180">
@@ -5153,26 +5153,26 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
         </is>
       </c>
       <c r="B182">
@@ -5182,7 +5182,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -5191,7 +5191,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
         </is>
       </c>
       <c r="B183">
@@ -5210,7 +5210,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PIATA</t>
         </is>
       </c>
       <c r="B184">
@@ -5229,7 +5229,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TRES LAGOAS</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B185">
@@ -5248,7 +5248,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TROPICAL</t>
+          <t>PORTAL DAS TORRES</t>
         </is>
       </c>
       <c r="B186">
@@ -5267,7 +5267,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>PORTO SEGURO</t>
         </is>
       </c>
       <c r="B187">
@@ -5286,7 +5286,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>PORTO SEGURO II</t>
         </is>
       </c>
       <c r="B188">
@@ -5296,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -5305,7 +5305,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>VILA BOSQUE</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B189">
@@ -5324,7 +5324,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VILA SANTO AMARAL</t>
+          <t>RESIDENCIAL DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B190">
@@ -5334,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -5343,7 +5343,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
         </is>
       </c>
       <c r="B191">
@@ -5362,26 +5362,26 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>SANENGE</t>
         </is>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>SANTA TEREZINHA</t>
         </is>
       </c>
       <c r="B193">
@@ -5400,19 +5400,266 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SAO SILVESTRE</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>1</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>TARUMA</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>1</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>1</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>UNIVERSO</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>1</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>VILA SANTO AMARAL</t>
+        </is>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>ZONA 2</t>
+        </is>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>1</v>
+      </c>
+      <c r="D205">
+        <v>1</v>
+      </c>
+      <c r="E205">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B206">
+        <v>1</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
           <t>ZONA 8</t>
         </is>
       </c>
-      <c r="B194">
-        <v>1</v>
-      </c>
-      <c r="C194">
-        <v>0</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194">
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>1</v>
+      </c>
+      <c r="E207">
         <v>0</v>
       </c>
     </row>
@@ -5423,7 +5670,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5475,7 +5722,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B3">
@@ -5485,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -5494,83 +5741,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>COMETA</t>
         </is>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B8">
@@ -5589,7 +5836,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B9">
@@ -5608,17 +5855,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COMETA</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6178,7 +6425,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PIONEIROS</t>
         </is>
       </c>
       <c r="B40">
@@ -6188,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6197,19 +6444,76 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>SAO JOSE</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VALE AZUL</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>VERA CRUZ</t>
         </is>
       </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41">
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
         <v>0</v>
       </c>
     </row>
@@ -6220,7 +6524,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6432,7 +6736,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -6442,7 +6746,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
@@ -6452,7 +6756,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24">
@@ -6462,7 +6766,17 @@
         </is>
       </c>
       <c r="B24">
-        <v>17</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -6472,7 +6786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C97"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7269,7 +7583,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
@@ -7295,7 +7609,7 @@
         </is>
       </c>
       <c r="C63">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="64">
@@ -7399,7 +7713,7 @@
         </is>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -7412,7 +7726,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="73">
@@ -7451,7 +7765,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -7464,7 +7778,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="77">
@@ -7490,7 +7804,7 @@
         </is>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -7503,7 +7817,7 @@
         </is>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80">
@@ -7516,7 +7830,7 @@
         </is>
       </c>
       <c r="C80">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81">
@@ -7529,7 +7843,7 @@
         </is>
       </c>
       <c r="C81">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82">
@@ -7555,7 +7869,7 @@
         </is>
       </c>
       <c r="C83">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -7568,7 +7882,7 @@
         </is>
       </c>
       <c r="C84">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85">
@@ -7581,7 +7895,7 @@
         </is>
       </c>
       <c r="C85">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -7607,7 +7921,7 @@
         </is>
       </c>
       <c r="C87">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88">
@@ -7620,7 +7934,7 @@
         </is>
       </c>
       <c r="C88">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
@@ -7633,7 +7947,7 @@
         </is>
       </c>
       <c r="C89">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -7646,7 +7960,7 @@
         </is>
       </c>
       <c r="C90">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91">
@@ -7659,7 +7973,7 @@
         </is>
       </c>
       <c r="C91">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -7672,7 +7986,7 @@
         </is>
       </c>
       <c r="C92">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93">
@@ -7685,7 +7999,7 @@
         </is>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
@@ -7698,7 +8012,7 @@
         </is>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
@@ -7711,7 +8025,7 @@
         </is>
       </c>
       <c r="C95">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96">
@@ -7724,7 +8038,7 @@
         </is>
       </c>
       <c r="C96">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="97">
@@ -7733,11 +8047,63 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>23</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C97">
+      <c r="C98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>24</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C99">
         <v>3</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>24</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>24</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -830,44 +830,44 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>412830</v>
+        <v>411690</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>UNIFLOR</t>
+          <t>NOVA ESPERANCA</t>
         </is>
       </c>
       <c r="G2">
-        <v>2106</v>
+        <v>27142</v>
       </c>
       <c r="H2">
-        <v>237.4</v>
+        <v>261.6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>411690</v>
+        <v>412830</v>
       </c>
       <c r="B3">
-        <v>63</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -876,18 +876,18 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NOVA ESPERANCA</t>
+          <t>UNIFLOR</t>
         </is>
       </c>
       <c r="G3">
-        <v>27142</v>
+        <v>2106</v>
       </c>
       <c r="H3">
-        <v>232.1</v>
+        <v>237.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>410220</v>
+        <v>411640</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -910,18 +910,18 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G4">
-        <v>4046</v>
+        <v>3669</v>
       </c>
       <c r="H4">
-        <v>173</v>
+        <v>190.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,10 +932,10 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>411640</v>
+        <v>410220</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -944,18 +944,18 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G5">
-        <v>3669</v>
+        <v>4046</v>
       </c>
       <c r="H5">
-        <v>163.5</v>
+        <v>173</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>412450</v>
+        <v>411740</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -978,18 +978,18 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G6">
-        <v>6463</v>
+        <v>3193</v>
       </c>
       <c r="H6">
-        <v>154.7</v>
+        <v>156.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1000,36 +1000,36 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>411090</v>
+        <v>412450</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G7">
-        <v>4530</v>
+        <v>6463</v>
       </c>
       <c r="H7">
-        <v>154.5</v>
+        <v>154.7</v>
       </c>
       <c r="I7">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1037,10 +1037,10 @@
         <v>412530</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1057,81 +1057,81 @@
         <v>5170</v>
       </c>
       <c r="H8">
-        <v>135.4</v>
+        <v>154.7</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>411520</v>
+        <v>411090</v>
       </c>
       <c r="B9">
-        <v>556</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G9">
-        <v>429660</v>
+        <v>4530</v>
       </c>
       <c r="H9">
-        <v>129.4</v>
+        <v>154.5</v>
       </c>
       <c r="I9">
-        <v>9.1</v>
+        <v>22.1</v>
       </c>
       <c r="J9">
-        <v>7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>411740</v>
+        <v>411520</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>624</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G10">
-        <v>3193</v>
+        <v>429660</v>
       </c>
       <c r="H10">
-        <v>125.3</v>
+        <v>145.2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="11">
@@ -1139,7 +1139,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>111.5</v>
+        <v>124.4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,70 +1170,70 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>410780</v>
+        <v>411480</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G12">
-        <v>4805</v>
+        <v>44749</v>
       </c>
       <c r="H12">
-        <v>83.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B13">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G13">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H13">
-        <v>76</v>
+        <v>83.2</v>
       </c>
       <c r="I13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>5.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1272,70 +1272,70 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>411110</v>
+        <v>412625</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G15">
-        <v>6228</v>
+        <v>128106</v>
       </c>
       <c r="H15">
-        <v>64.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>412625</v>
+        <v>411110</v>
       </c>
       <c r="B16">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G16">
-        <v>128106</v>
+        <v>6228</v>
       </c>
       <c r="H16">
-        <v>61.7</v>
+        <v>64.2</v>
       </c>
       <c r="I16">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>6.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>411360</v>
+        <v>410790</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1386,18 +1386,18 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="G18">
-        <v>4707</v>
+        <v>11522</v>
       </c>
       <c r="H18">
-        <v>42.5</v>
+        <v>52.1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>411410</v>
+        <v>412340</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1420,18 +1420,18 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G19">
-        <v>34521</v>
+        <v>11730</v>
       </c>
       <c r="H19">
-        <v>40.6</v>
+        <v>42.6</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>410210</v>
+        <v>411360</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1454,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G20">
-        <v>26203</v>
+        <v>4707</v>
       </c>
       <c r="H20">
-        <v>38.2</v>
+        <v>42.5</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,78 +1476,78 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411750</v>
+        <v>411410</v>
       </c>
       <c r="B21">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G21">
-        <v>48695</v>
+        <v>34521</v>
       </c>
       <c r="H21">
-        <v>37</v>
+        <v>40.6</v>
       </c>
       <c r="I21">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>5.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>410790</v>
+        <v>411750</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G22">
-        <v>11522</v>
+        <v>48695</v>
       </c>
       <c r="H22">
-        <v>34.7</v>
+        <v>37</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>412340</v>
+        <v>410210</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1560,14 +1560,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G23">
-        <v>11730</v>
+        <v>26203</v>
       </c>
       <c r="H23">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1612,30 +1612,30 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>411420</v>
+        <v>412040</v>
       </c>
       <c r="B25">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>PRESIDENTE CASTELO BRANCO</t>
         </is>
       </c>
       <c r="G25">
-        <v>38313</v>
+        <v>4304</v>
       </c>
       <c r="H25">
-        <v>20.9</v>
+        <v>23.2</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1646,30 +1646,30 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>411000</v>
+        <v>411420</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IGUARACU</t>
+          <t>MANDAGUARI</t>
         </is>
       </c>
       <c r="G26">
-        <v>5693</v>
+        <v>38313</v>
       </c>
       <c r="H26">
-        <v>17.6</v>
+        <v>20.9</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1680,35 +1680,69 @@
     </row>
     <row r="27">
       <c r="A27">
+        <v>411000</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>IGUARACU</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>5693</v>
+      </c>
+      <c r="H27">
+        <v>17.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
         <v>410730</v>
       </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>DOUTOR CAMARGO</t>
         </is>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>6517</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>15.3</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
         <v>0</v>
       </c>
     </row>
@@ -1719,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1756,7 +1790,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -1765,7 +1799,7 @@
         <v>13</v>
       </c>
       <c r="E2">
-        <v>10.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1775,16 +1809,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -1794,7 +1828,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1803,45 +1837,45 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7">
@@ -1866,55 +1900,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>4</v>
       </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
       <c r="E8">
-        <v>44.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E9">
-        <v>11.1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1923,20 +1957,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1946,70 +1980,70 @@
         </is>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2018,17 +2052,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>ZONA 03</t>
         </is>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2037,7 +2071,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B17">
@@ -2047,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2056,17 +2090,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM COLINA VERDE</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2075,112 +2109,112 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <v>2</v>
       </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
       <c r="E19">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B20">
         <v>6</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B21">
         <v>6</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E21">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B22">
         <v>6</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2189,26 +2223,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B25">
         <v>5</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B26">
@@ -2218,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>20</v>
@@ -2227,7 +2261,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B27">
@@ -2246,7 +2280,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B28">
@@ -2265,26 +2299,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B29">
         <v>5</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B30">
@@ -2303,7 +2337,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B31">
@@ -2313,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2322,20 +2356,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2379,26 +2413,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B36">
@@ -2408,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2417,7 +2451,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B37">
@@ -2436,7 +2470,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B38">
@@ -2446,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2455,7 +2489,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JARDIM NOVO OASIS</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B39">
@@ -2465,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2474,7 +2508,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B40">
@@ -2484,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2493,26 +2527,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B42">
@@ -2522,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2531,7 +2565,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B43">
@@ -2550,7 +2584,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ZONA 03</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B44">
@@ -2560,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2569,36 +2603,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2607,17 +2641,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2626,64 +2660,64 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B51">
@@ -2693,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2702,7 +2736,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B52">
@@ -2712,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2721,7 +2755,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
         </is>
       </c>
       <c r="B53">
@@ -2731,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2740,7 +2774,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B54">
@@ -2759,26 +2793,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
         </is>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B56">
@@ -2788,7 +2822,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>33.3</v>
@@ -2797,7 +2831,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B57">
@@ -2816,26 +2850,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B59">
@@ -2854,7 +2888,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VILA IPIRANGA</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B60">
@@ -2873,7 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B61">
@@ -2892,7 +2926,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B62">
@@ -2902,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2911,74 +2945,74 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B63">
         <v>3</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BRANCA VIEIRA</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B66">
+        <v>3</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
         <v>2</v>
-      </c>
-      <c r="C66">
-        <v>0</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2987,17 +3021,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -3006,30 +3040,30 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B68">
+        <v>3</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68">
         <v>2</v>
       </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
       <c r="E68">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -3044,17 +3078,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3063,17 +3097,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>VILA BOSQUE</t>
         </is>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3082,11 +3116,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>COPACABANA RESIDENCIAL</t>
+          <t>VILA IPIRANGA</t>
         </is>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3101,17 +3135,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3120,17 +3154,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3139,7 +3173,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B75">
@@ -3158,7 +3192,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>BRANCA VIEIRA</t>
         </is>
       </c>
       <c r="B76">
@@ -3168,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3177,7 +3211,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B77">
@@ -3196,7 +3230,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B78">
@@ -3206,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3215,7 +3249,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B79">
@@ -3225,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3234,26 +3268,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>COPACABANA RESIDENCIAL</t>
         </is>
       </c>
       <c r="B81">
@@ -3263,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3272,7 +3306,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B82">
@@ -3291,7 +3325,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B83">
@@ -3310,26 +3344,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B84">
         <v>2</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E84">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B85">
@@ -3348,7 +3382,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B86">
@@ -3358,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3367,45 +3401,45 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B89">
@@ -3415,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3424,7 +3458,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RECANTO DOS MAGNATAS</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B90">
@@ -3434,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3443,7 +3477,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B91">
@@ -3453,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3462,7 +3496,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B92">
@@ -3472,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3481,7 +3515,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B93">
@@ -3500,7 +3534,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VILA BOSQUE</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B94">
@@ -3510,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3519,7 +3553,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B95">
@@ -3538,36 +3572,36 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3576,17 +3610,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
         </is>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3595,11 +3629,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -3614,11 +3648,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>RECANTO DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -3633,30 +3667,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>REQUIAO</t>
         </is>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>RESIDENCIAL IBIRAPUERA</t>
         </is>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -3671,11 +3705,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -3690,17 +3724,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>TARUMA</t>
         </is>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3709,17 +3743,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>CHACARAS AEROPORTO</t>
+          <t>UNIVERSO</t>
         </is>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3728,7 +3762,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CIDADE JARDIM</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B106">
@@ -3747,7 +3781,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B107">
@@ -3757,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3766,7 +3800,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CJ RES PARIGOT DE SOUZA</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B108">
@@ -3785,7 +3819,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B109">
@@ -3804,7 +3838,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B110">
@@ -3823,26 +3857,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B112">
@@ -3852,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3861,7 +3895,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DISTRITO IGUATEMI</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B113">
@@ -3880,7 +3914,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>DONA ANGELINA</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B114">
@@ -3899,7 +3933,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>CHACARAS AEROPORTO</t>
         </is>
       </c>
       <c r="B115">
@@ -3918,7 +3952,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B116">
@@ -3937,7 +3971,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B117">
@@ -3956,7 +3990,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GUAIRACA</t>
+          <t>CJ RES PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B118">
@@ -3966,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -3975,7 +4009,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>HABITACIONAL SOL NASCENTE</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B119">
@@ -3985,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -3994,7 +4028,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B120">
@@ -4004,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4013,7 +4047,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B121">
@@ -4023,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4032,7 +4066,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>DISTRITO IGUATEMI</t>
         </is>
       </c>
       <c r="B122">
@@ -4042,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4051,7 +4085,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B123">
@@ -4070,7 +4104,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B124">
@@ -4089,7 +4123,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JARDIM ATLANTA</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B125">
@@ -4108,7 +4142,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B126">
@@ -4118,7 +4152,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4127,7 +4161,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JARDIM BELO HORIZONTE IGUATEM</t>
+          <t>GRAJAU</t>
         </is>
       </c>
       <c r="B127">
@@ -4146,26 +4180,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>HABITACIONAL SOL NASCENTE</t>
         </is>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B129">
@@ -4184,7 +4218,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B130">
@@ -4203,7 +4237,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B131">
@@ -4222,7 +4256,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>JARDIM CERRO AZUL</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B132">
@@ -4241,7 +4275,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JARDIM CIDADE MONCOES</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B133">
@@ -4251,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4260,26 +4294,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>JARDIM AURORA</t>
         </is>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JARDIM DAS ESTACOES</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B135">
@@ -4289,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4298,7 +4332,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B136">
@@ -4317,26 +4351,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
         <v>1</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JARDIM DOS PASSAROS</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B138">
@@ -4346,7 +4380,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4355,7 +4389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JARDIM EVEREST</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B139">
@@ -4374,7 +4408,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JARDIM GUAIRACA</t>
+          <t>JARDIM CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B140">
@@ -4384,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4393,7 +4427,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JARDIM IGUACU</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B141">
@@ -4403,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4412,7 +4446,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B142">
@@ -4422,7 +4456,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4431,7 +4465,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM CIDADE MONCOES</t>
         </is>
       </c>
       <c r="B143">
@@ -4441,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4450,7 +4484,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B144">
@@ -4460,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4469,7 +4503,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA II</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B145">
@@ -4488,7 +4522,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>JARDIM MANDACARU</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B146">
@@ -4498,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -4507,26 +4541,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B148">
@@ -4545,7 +4579,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JARDIM NOROESTE</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B149">
@@ -4564,7 +4598,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B150">
@@ -4574,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -4583,7 +4617,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JARDIM ORIENTAL</t>
+          <t>JARDIM IGUACU</t>
         </is>
       </c>
       <c r="B151">
@@ -4602,7 +4636,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B152">
@@ -4621,7 +4655,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JARDIM PARIS III</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B153">
@@ -4640,7 +4674,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS II</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B154">
@@ -4659,7 +4693,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B155">
@@ -4678,26 +4712,26 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM LIBERDADE III</t>
         </is>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ALICE</t>
+          <t>JARDIM MANDACARU</t>
         </is>
       </c>
       <c r="B157">
@@ -4716,26 +4750,26 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B159">
@@ -4745,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -4754,7 +4788,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B160">
@@ -4773,7 +4807,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JARDIM TABAETE</t>
+          <t>JARDIM NOROESTE</t>
         </is>
       </c>
       <c r="B161">
@@ -4792,7 +4826,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>JARDIM TOQUIO</t>
+          <t>JARDIM NOVO ALVORADA</t>
         </is>
       </c>
       <c r="B162">
@@ -4802,7 +4836,7 @@
         <v>0</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -4811,7 +4845,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B163">
@@ -4830,7 +4864,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JOAO DE BARRO</t>
+          <t>JARDIM ORIENTAL</t>
         </is>
       </c>
       <c r="B164">
@@ -4840,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -4849,7 +4883,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B165">
@@ -4859,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -4868,7 +4902,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM PAULISTA III</t>
         </is>
       </c>
       <c r="B166">
@@ -4887,7 +4921,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM PINHEIROS II</t>
         </is>
       </c>
       <c r="B167">
@@ -4906,7 +4940,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B168">
@@ -4916,7 +4950,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -4925,7 +4959,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B169">
@@ -4944,7 +4978,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>LUCIANOPOLIS</t>
+          <t>JARDIM SANTA ALICE</t>
         </is>
       </c>
       <c r="B170">
@@ -4954,7 +4988,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -4963,7 +4997,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B171">
@@ -4973,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -4982,7 +5016,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B172">
@@ -4992,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5001,7 +5035,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B173">
@@ -5011,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5020,7 +5054,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM SOCIAL</t>
         </is>
       </c>
       <c r="B174">
@@ -5039,7 +5073,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B175">
@@ -5058,7 +5092,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>OASIS</t>
+          <t>JARDIM TOQUIO</t>
         </is>
       </c>
       <c r="B176">
@@ -5068,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5077,7 +5111,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B177">
@@ -5096,7 +5130,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PARIGOT DE SOUZA</t>
+          <t>JARDIM VITORIA</t>
         </is>
       </c>
       <c r="B178">
@@ -5115,26 +5149,26 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PARQUE DA GAVEA</t>
+          <t>JOAO DE BARRO</t>
         </is>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D179">
         <v>1</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B180">
@@ -5153,26 +5187,26 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B182">
@@ -5182,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -5191,7 +5225,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL QUEBEC</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B183">
@@ -5210,7 +5244,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B184">
@@ -5229,7 +5263,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B185">
@@ -5248,7 +5282,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PORTAL DAS TORRES</t>
+          <t>MANDACARU</t>
         </is>
       </c>
       <c r="B186">
@@ -5267,7 +5301,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B187">
@@ -5277,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -5286,7 +5320,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PORTO SEGURO II</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B188">
@@ -5296,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -5305,7 +5339,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B189">
@@ -5324,7 +5358,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RESIDENCIAL DOS MAGNATAS</t>
+          <t>NOVA ALVORADA</t>
         </is>
       </c>
       <c r="B190">
@@ -5334,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -5343,7 +5377,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B191">
@@ -5362,7 +5396,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SANENGE</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="B192">
@@ -5381,7 +5415,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B193">
@@ -5400,7 +5434,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B194">
@@ -5410,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -5419,7 +5453,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SAO SILVESTRE</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="B195">
@@ -5438,7 +5472,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>PARQUE AVENIDA</t>
         </is>
       </c>
       <c r="B196">
@@ -5457,7 +5491,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B197">
@@ -5467,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -5476,26 +5510,26 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TRES LAGOAS</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TROPICAL</t>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
         </is>
       </c>
       <c r="B199">
@@ -5505,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -5514,7 +5548,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>PIATA</t>
         </is>
       </c>
       <c r="B200">
@@ -5533,7 +5567,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B201">
@@ -5552,7 +5586,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>VILA SANTO AMARAL</t>
+          <t>PIONEIRO ODWALDO BUENO</t>
         </is>
       </c>
       <c r="B202">
@@ -5571,7 +5605,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>PORTAL DAS TORRES</t>
         </is>
       </c>
       <c r="B203">
@@ -5590,7 +5624,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ZONA 2</t>
+          <t>PORTO SEGURO</t>
         </is>
       </c>
       <c r="B204">
@@ -5600,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -5609,26 +5643,26 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>PORTO SEGURO II</t>
         </is>
       </c>
       <c r="B205">
         <v>1</v>
       </c>
       <c r="C205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D205">
         <v>1</v>
       </c>
       <c r="E205">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>RESIDENCIAL DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B206">
@@ -5638,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -5647,19 +5681,361 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
+          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
+        </is>
+      </c>
+      <c r="B207">
+        <v>1</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SANENGE</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>1</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B210">
+        <v>1</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>SAO JORGE</t>
+        </is>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>SAO SILVESTRE</t>
+        </is>
+      </c>
+      <c r="B212">
+        <v>1</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+      <c r="D215">
+        <v>1</v>
+      </c>
+      <c r="E215">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B216">
+        <v>1</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>VILA CLEOPATRA</t>
+        </is>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>VILA SANTO AMARAL</t>
+        </is>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>ZONA 1</t>
+        </is>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>ZONA 2</t>
+        </is>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>1</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222">
+        <v>1</v>
+      </c>
+      <c r="D222">
+        <v>1</v>
+      </c>
+      <c r="E222">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
           <t>ZONA 8</t>
         </is>
       </c>
-      <c r="B207">
-        <v>1</v>
-      </c>
-      <c r="C207">
-        <v>0</v>
-      </c>
-      <c r="D207">
-        <v>1</v>
-      </c>
-      <c r="E207">
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>ZONA ARMAZEM</t>
+        </is>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
         <v>0</v>
       </c>
     </row>
@@ -5670,7 +6046,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -5726,7 +6102,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -5735,7 +6111,7 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -5767,57 +6143,57 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B8">
@@ -5827,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5836,7 +6212,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B9">
@@ -5855,7 +6231,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B10">
@@ -5874,17 +6250,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>NOVO PANORAMA</t>
         </is>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5893,11 +6269,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -5912,7 +6288,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B13">
@@ -5922,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5931,7 +6307,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MAUA</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B14">
@@ -5950,7 +6326,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>MAUA</t>
         </is>
       </c>
       <c r="B15">
@@ -5960,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5969,7 +6345,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B16">
@@ -5988,36 +6364,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR</t>
+          <t>NOVA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B17">
         <v>2</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6026,26 +6402,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALVAMAR II</t>
+          <t>PARQUE ALVAMAR</t>
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B20">
@@ -6064,7 +6440,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>ALVAMAR II</t>
         </is>
       </c>
       <c r="B21">
@@ -6074,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6083,7 +6459,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B22">
@@ -6102,26 +6478,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ECOVALLEY</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ECOVALLEY ECOLOGIC CITY</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B24">
@@ -6131,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6140,26 +6516,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>ECOVALLEY</t>
         </is>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>ECOVALLEY ECOLOGIC CITY</t>
         </is>
       </c>
       <c r="B26">
@@ -6169,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6178,7 +6554,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JARDIM COMETA</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B27">
@@ -6197,7 +6573,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM DOM BOSCO</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B28">
@@ -6207,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6216,7 +6592,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>JARDIM COMETA</t>
         </is>
       </c>
       <c r="B29">
@@ -6235,7 +6611,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM NOVA PAULISTA</t>
+          <t>JARDIM DOM BOSCO</t>
         </is>
       </c>
       <c r="B30">
@@ -6254,7 +6630,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM OURO VERDE III</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B31">
@@ -6264,7 +6640,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6273,7 +6649,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>JARDIM NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B32">
@@ -6283,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6292,7 +6668,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>JARDIM OURO VERDE III</t>
         </is>
       </c>
       <c r="B33">
@@ -6302,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6311,7 +6687,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B34">
@@ -6330,7 +6706,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NACOES</t>
+          <t>JARDIM SAO PAULO II</t>
         </is>
       </c>
       <c r="B35">
@@ -6349,7 +6725,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B36">
@@ -6368,7 +6744,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA I</t>
+          <t>NACOES</t>
         </is>
       </c>
       <c r="B37">
@@ -6378,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6387,7 +6763,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>OURO VERDE</t>
+          <t>NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B38">
@@ -6406,7 +6782,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>OURO VERDE</t>
         </is>
       </c>
       <c r="B39">
@@ -6425,7 +6801,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PIONEIROS</t>
+          <t>PARQUE ALVAMAR II</t>
         </is>
       </c>
       <c r="B40">
@@ -6444,7 +6820,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SAO JOSE</t>
+          <t>PARQUE RESIDENCIAL BELA VISTA</t>
         </is>
       </c>
       <c r="B41">
@@ -6463,7 +6839,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PIONEIROS</t>
         </is>
       </c>
       <c r="B42">
@@ -6473,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6482,7 +6858,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VALE AZUL</t>
+          <t>RESIDENCIAL GOVERNADOR JOSE RI</t>
         </is>
       </c>
       <c r="B43">
@@ -6492,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -6501,19 +6877,76 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>SAO JOSE</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VALE AZUL</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>VERA CRUZ</t>
         </is>
       </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="C44">
-        <v>0</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44">
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
         <v>0</v>
       </c>
     </row>
@@ -6524,7 +6957,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6606,7 +7039,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -6616,7 +7049,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6636,7 +7069,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -6656,7 +7089,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -6686,7 +7119,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
@@ -6696,7 +7129,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
@@ -6716,7 +7149,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20">
@@ -6736,7 +7169,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -6746,7 +7179,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -6776,7 +7209,27 @@
         </is>
       </c>
       <c r="B25">
-        <v>27</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -6786,7 +7239,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7163,11 +7616,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -7176,24 +7629,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -7202,7 +7655,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C32">
@@ -7215,11 +7668,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -7228,37 +7681,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C36">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -7267,11 +7720,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -7280,33 +7733,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C40">
@@ -7319,11 +7772,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -7332,37 +7785,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C44">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
@@ -7371,11 +7824,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -7384,37 +7837,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
@@ -7423,11 +7876,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -7436,37 +7889,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -7475,37 +7928,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C53">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -7514,11 +7967,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C56">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -7527,37 +7980,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C57">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C58">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
@@ -7566,11 +8019,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61">
@@ -7579,11 +8032,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C61">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -7592,37 +8045,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C62">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C63">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C64">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -7631,11 +8084,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
@@ -7644,11 +8097,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C66">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -7657,37 +8110,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C67">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C68">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C69">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -7696,11 +8149,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C70">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="71">
@@ -7709,37 +8162,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C72">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C73">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -7748,11 +8201,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -7761,11 +8214,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C75">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="76">
@@ -7774,24 +8227,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C76">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C77">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -7800,11 +8253,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
@@ -7813,11 +8266,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C79">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -7826,24 +8279,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C80">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C81">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -7852,11 +8305,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
@@ -7865,11 +8318,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C83">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
@@ -7878,11 +8331,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C84">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
@@ -7891,20 +8344,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C85">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C86">
@@ -7917,11 +8370,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C87">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88">
@@ -7930,11 +8383,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C88">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -7943,24 +8396,24 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90">
+        <v>22</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C90">
         <v>21</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C90">
-        <v>17</v>
       </c>
     </row>
     <row r="91">
@@ -7969,11 +8422,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C91">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
@@ -7982,11 +8435,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C92">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93">
@@ -7995,24 +8448,24 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C93">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C94">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -8021,11 +8474,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C95">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96">
@@ -8034,11 +8487,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C96">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
@@ -8047,24 +8500,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C97">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98">
       <c r="A98">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
@@ -8073,11 +8526,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100">
@@ -8086,11 +8539,11 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C100">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -8099,11 +8552,128 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>25</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>25</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>25</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>25</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>Outro vírus respiratório</t>
         </is>
       </c>
-      <c r="C101">
-        <v>1</v>
+      <c r="C105">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>25</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>26</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>26</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>26</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>26</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -833,7 +833,7 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C2">
         <v>2</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -853,13 +853,13 @@
         <v>27142</v>
       </c>
       <c r="H2">
-        <v>261.6</v>
+        <v>320.5</v>
       </c>
       <c r="I2">
         <v>7.4</v>
       </c>
       <c r="J2">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>411640</v>
+        <v>410220</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -910,18 +910,18 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>ATALAIA</t>
         </is>
       </c>
       <c r="G4">
-        <v>3669</v>
+        <v>4046</v>
       </c>
       <c r="H4">
-        <v>190.8</v>
+        <v>197.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,44 +932,44 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>410220</v>
+        <v>412530</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ATALAIA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G5">
-        <v>4046</v>
+        <v>5170</v>
       </c>
       <c r="H5">
-        <v>173</v>
+        <v>193.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>411740</v>
+        <v>411640</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -978,18 +978,18 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G6">
-        <v>3193</v>
+        <v>3669</v>
       </c>
       <c r="H6">
-        <v>156.6</v>
+        <v>190.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1000,138 +1000,138 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>412450</v>
+        <v>411520</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>708</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G7">
-        <v>6463</v>
+        <v>429660</v>
       </c>
       <c r="H7">
-        <v>154.7</v>
+        <v>164.8</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>412530</v>
+        <v>411740</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G8">
-        <v>5170</v>
+        <v>3193</v>
       </c>
       <c r="H8">
-        <v>154.7</v>
+        <v>156.6</v>
       </c>
       <c r="I8">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>411090</v>
+        <v>412450</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G9">
-        <v>4530</v>
+        <v>6463</v>
       </c>
       <c r="H9">
-        <v>154.5</v>
+        <v>154.7</v>
       </c>
       <c r="I9">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>411520</v>
+        <v>411090</v>
       </c>
       <c r="B10">
-        <v>624</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G10">
-        <v>429660</v>
+        <v>4530</v>
       </c>
       <c r="H10">
-        <v>145.2</v>
+        <v>154.5</v>
       </c>
       <c r="I10">
-        <v>11.4</v>
+        <v>22.1</v>
       </c>
       <c r="J10">
-        <v>7.9</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="11">
@@ -1139,7 +1139,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>124.4</v>
+        <v>150.1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,44 +1170,44 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B12">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MARIALVA</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G12">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H12">
-        <v>96.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>4.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1216,18 +1216,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G13">
-        <v>4805</v>
+        <v>6228</v>
       </c>
       <c r="H13">
-        <v>83.2</v>
+        <v>112.4</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1238,104 +1238,104 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>411810</v>
+        <v>411480</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>MARIALVA</t>
         </is>
       </c>
       <c r="G14">
-        <v>9549</v>
+        <v>44749</v>
       </c>
       <c r="H14">
-        <v>73.3</v>
+        <v>109.5</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>412625</v>
+        <v>411810</v>
       </c>
       <c r="B15">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G15">
-        <v>128106</v>
+        <v>9549</v>
       </c>
       <c r="H15">
-        <v>67.90000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="I15">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>6.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>411110</v>
+        <v>412625</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>95</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G16">
-        <v>6228</v>
+        <v>128106</v>
       </c>
       <c r="H16">
-        <v>64.2</v>
+        <v>74.2</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="17">
@@ -1408,10 +1408,10 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>412340</v>
+        <v>412040</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1420,18 +1420,18 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>PRESIDENTE CASTELO BRANCO</t>
         </is>
       </c>
       <c r="G19">
-        <v>11730</v>
+        <v>4304</v>
       </c>
       <c r="H19">
-        <v>42.6</v>
+        <v>46.5</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>411360</v>
+        <v>412340</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1454,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G20">
-        <v>4707</v>
+        <v>11730</v>
       </c>
       <c r="H20">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,10 +1476,10 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411410</v>
+        <v>411360</v>
       </c>
       <c r="B21">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1488,18 +1488,18 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G21">
-        <v>34521</v>
+        <v>4707</v>
       </c>
       <c r="H21">
-        <v>40.6</v>
+        <v>42.5</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>411750</v>
       </c>
       <c r="B22">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1533,41 +1533,41 @@
         <v>48695</v>
       </c>
       <c r="H22">
-        <v>37</v>
+        <v>41.1</v>
       </c>
       <c r="I22">
         <v>2.1</v>
       </c>
       <c r="J22">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>410210</v>
+        <v>411410</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G23">
-        <v>26203</v>
+        <v>34521</v>
       </c>
       <c r="H23">
-        <v>34.3</v>
+        <v>40.6</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>411630</v>
+        <v>410210</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1590,18 +1590,18 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G24">
-        <v>4057</v>
+        <v>26203</v>
       </c>
       <c r="H24">
-        <v>24.6</v>
+        <v>38.2</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1612,30 +1612,30 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>412040</v>
+        <v>411420</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PRESIDENTE CASTELO BRANCO</t>
+          <t>MANDAGUARI</t>
         </is>
       </c>
       <c r="G25">
-        <v>4304</v>
+        <v>38313</v>
       </c>
       <c r="H25">
-        <v>23.2</v>
+        <v>26.1</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1646,30 +1646,30 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>411420</v>
+        <v>411630</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G26">
-        <v>38313</v>
+        <v>4057</v>
       </c>
       <c r="H26">
-        <v>20.9</v>
+        <v>24.6</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1753,7 +1753,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="3">
@@ -1809,7 +1809,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1818,7 +1818,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -1837,45 +1837,45 @@
         <v>4</v>
       </c>
       <c r="E4">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JARDIM SAO SILVESTRE</t>
+          <t>ZONA 07</t>
         </is>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ZONA 07</t>
+          <t>JARDIM SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>7.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
@@ -1885,35 +1885,35 @@
         </is>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>6</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ALVORADA</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -1932,7 +1932,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>40</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="10">
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>ALVORADA</t>
         </is>
       </c>
       <c r="B11">
@@ -1995,55 +1995,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B13">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E13">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>ZONA 03</t>
         </is>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2052,20 +2052,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ZONA 03</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B16">
         <v>8</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="17">
@@ -2078,133 +2078,133 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B18">
         <v>7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B24">
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2223,112 +2223,112 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL HERMANN</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
         <v>5</v>
       </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
       <c r="E29">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2337,20 +2337,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31">
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -2375,17 +2375,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2394,49 +2394,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+          <t>CONJUNTO HABITACIONAL HERMANN</t>
         </is>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2451,17 +2451,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2470,74 +2470,74 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>JARDIM NOVO OASIS</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2546,30 +2546,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2578,13 +2578,13 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B44">
@@ -2594,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2603,45 +2603,45 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
         </is>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
         </is>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B47">
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2660,7 +2660,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B48">
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2679,55 +2679,55 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>1</v>
       </c>
       <c r="E50">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B51">
+        <v>4</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
         <v>3</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2736,36 +2736,36 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2774,11 +2774,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2793,11 +2793,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -2812,36 +2812,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2850,26 +2850,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>1</v>
       </c>
       <c r="E58">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B59">
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2888,7 +2888,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B60">
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2907,7 +2907,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B61">
@@ -2926,7 +2926,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
         </is>
       </c>
       <c r="B62">
@@ -2936,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2945,7 +2945,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JARDIM PARIS III</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B63">
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2964,7 +2964,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B64">
@@ -2974,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E64">
         <v>33.3</v>
@@ -2983,45 +2983,45 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B66">
         <v>3</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B67">
@@ -3040,26 +3040,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B68">
         <v>3</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B69">
@@ -3078,7 +3078,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B70">
@@ -3088,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3097,7 +3097,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>VILA BOSQUE</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B71">
@@ -3107,7 +3107,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3116,26 +3116,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>VILA IPIRANGA</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B72">
         <v>3</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B73">
@@ -3154,7 +3154,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B74">
@@ -3164,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3173,17 +3173,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3192,17 +3192,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BRANCA VIEIRA</t>
+          <t>VILA BOSQUE</t>
         </is>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3211,17 +3211,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>VILA IPIRANGA</t>
         </is>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3230,11 +3230,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3249,7 +3249,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B79">
@@ -3268,26 +3268,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>BRANCA VIEIRA</t>
         </is>
       </c>
       <c r="B80">
         <v>2</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>COPACABANA RESIDENCIAL</t>
+          <t>CHACARAS AEROPORTO</t>
         </is>
       </c>
       <c r="B81">
@@ -3297,7 +3297,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3306,7 +3306,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>CJ RES PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B82">
@@ -3316,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3325,7 +3325,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B83">
@@ -3344,7 +3344,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GUAIRACA</t>
+          <t>COPACABANA RESIDENCIAL</t>
         </is>
       </c>
       <c r="B84">
@@ -3363,7 +3363,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B85">
@@ -3373,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3382,7 +3382,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B86">
@@ -3401,7 +3401,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B87">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B88">
@@ -3430,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B89">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3458,7 +3458,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B90">
@@ -3468,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3477,7 +3477,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B91">
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B92">
@@ -3506,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3515,7 +3515,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>JARDIM CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B93">
@@ -3534,7 +3534,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM CIDADE MONCOES</t>
         </is>
       </c>
       <c r="B94">
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3553,7 +3553,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B95">
@@ -3572,45 +3572,45 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B96">
         <v>2</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
       <c r="E96">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL QUEBEC</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B98">
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3629,7 +3629,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B99">
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3648,7 +3648,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RECANTO DOS MAGNATAS</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B100">
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3667,26 +3667,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B102">
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3705,7 +3705,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>JARDIM NOVO ALVORADA</t>
         </is>
       </c>
       <c r="B103">
@@ -3724,26 +3724,26 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B104">
         <v>2</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
         <v>1</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>JARDIM PAULISTA III</t>
         </is>
       </c>
       <c r="B105">
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3762,17 +3762,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3781,11 +3781,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -3800,11 +3800,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -3819,17 +3819,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3838,17 +3838,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3857,11 +3857,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -3876,11 +3876,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -3895,11 +3895,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>PARQUE AVENIDA</t>
         </is>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -3914,11 +3914,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -3933,30 +3933,30 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CHACARAS AEROPORTO</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CIDADE JARDIM</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -3971,11 +3971,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
         </is>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -3990,11 +3990,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CJ RES PARIGOT DE SOUZA</t>
+          <t>PIATA</t>
         </is>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -4009,17 +4009,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4028,11 +4028,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
+          <t>RECANTO DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4047,30 +4047,30 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>REQUIAO</t>
         </is>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DISTRITO IGUATEMI</t>
+          <t>RESIDENCIAL IBIRAPUERA</t>
         </is>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -4085,11 +4085,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DONA ANGELINA</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -4104,17 +4104,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>TARUMA</t>
         </is>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4123,17 +4123,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>UNIVERSO</t>
         </is>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4142,7 +4142,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B126">
@@ -4161,7 +4161,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GRAJAU</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B127">
@@ -4180,7 +4180,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>HABITACIONAL SOL NASCENTE</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B128">
@@ -4199,7 +4199,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B129">
@@ -4218,7 +4218,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B130">
@@ -4237,7 +4237,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B131">
@@ -4247,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4256,7 +4256,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B132">
@@ -4275,7 +4275,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>JARDIM ATLANTA</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B133">
@@ -4294,26 +4294,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>JARDIM AURORA</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>CIDADE ALTA</t>
         </is>
       </c>
       <c r="B135">
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4332,7 +4332,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>JARDIM BELO HORIZONTE IGUATEM</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B136">
@@ -4351,26 +4351,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B138">
@@ -4389,7 +4389,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>CONJUNTO HABITACIONAL ITATIAIA</t>
         </is>
       </c>
       <c r="B139">
@@ -4408,7 +4408,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>JARDIM CAMPOS ELISIOS</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B140">
@@ -4427,7 +4427,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B141">
@@ -4446,7 +4446,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JARDIM CERRO AZUL</t>
+          <t>DISTRITO IGUATEMI</t>
         </is>
       </c>
       <c r="B142">
@@ -4465,7 +4465,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>JARDIM CIDADE MONCOES</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B143">
@@ -4475,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4484,7 +4484,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B144">
@@ -4494,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4503,7 +4503,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>JARDIM DAS ESTACOES</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B145">
@@ -4522,7 +4522,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B146">
@@ -4541,7 +4541,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>GRAJAU</t>
         </is>
       </c>
       <c r="B147">
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JARDIM DOS PASSAROS</t>
+          <t>HABITACIONAL SOL NASCENTE</t>
         </is>
       </c>
       <c r="B148">
@@ -4579,7 +4579,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>JARDIM EVEREST</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B149">
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -4598,7 +4598,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>JARDIM GUAIRACA</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B150">
@@ -4608,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -4617,7 +4617,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>JARDIM IGUACU</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B151">
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -4636,7 +4636,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B152">
@@ -4646,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -4655,7 +4655,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B153">
@@ -4674,26 +4674,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>JARDIM AURORA</t>
         </is>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA II</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B155">
@@ -4703,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -4712,64 +4712,64 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE III</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JARDIM MANDACARU</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157">
         <v>1</v>
       </c>
       <c r="E157">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B159">
@@ -4779,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -4788,7 +4788,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B160">
@@ -4807,7 +4807,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JARDIM NOROESTE</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B161">
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>JARDIM NOVO ALVORADA</t>
+          <t>JARDIM DIAS II</t>
         </is>
       </c>
       <c r="B162">
@@ -4845,7 +4845,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B163">
@@ -4864,7 +4864,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JARDIM ORIENTAL</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B164">
@@ -4874,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -4883,7 +4883,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM HANOVER</t>
         </is>
       </c>
       <c r="B165">
@@ -4902,7 +4902,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA III</t>
+          <t>JARDIM IGUACU</t>
         </is>
       </c>
       <c r="B166">
@@ -4921,7 +4921,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS II</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B167">
@@ -4940,7 +4940,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B168">
@@ -4959,7 +4959,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B169">
@@ -4978,26 +4978,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ALICE</t>
+          <t>JARDIM LAODICEIA</t>
         </is>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM LEBLON</t>
         </is>
       </c>
       <c r="B171">
@@ -5007,7 +5007,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5016,26 +5016,26 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM LIBERDADE III</t>
         </is>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM MANDACARU</t>
         </is>
       </c>
       <c r="B173">
@@ -5054,26 +5054,26 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>JARDIM SOCIAL</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B174">
         <v>1</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JARDIM TABAETE</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B175">
@@ -5092,7 +5092,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>JARDIM TOQUIO</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B176">
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5111,7 +5111,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM NOROESTE</t>
         </is>
       </c>
       <c r="B177">
@@ -5130,7 +5130,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JARDIM VITORIA</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B178">
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -5149,26 +5149,26 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JOAO DE BARRO</t>
+          <t>JARDIM ORIENTAL</t>
         </is>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B180">
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -5187,7 +5187,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM PARQUE DO HORTO</t>
         </is>
       </c>
       <c r="B181">
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -5206,7 +5206,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM PINHEIROS II</t>
         </is>
       </c>
       <c r="B182">
@@ -5225,7 +5225,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B183">
@@ -5244,7 +5244,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LUCIANOPOLIS</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B184">
@@ -5263,7 +5263,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM SANTA ALICE</t>
         </is>
       </c>
       <c r="B185">
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -5282,7 +5282,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MANDACARU</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B186">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -5301,7 +5301,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B187">
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -5320,7 +5320,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM TOQUIO</t>
         </is>
       </c>
       <c r="B188">
@@ -5330,7 +5330,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -5339,26 +5339,26 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM TUPINAMBA</t>
         </is>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>NOVA ALVORADA</t>
+          <t>JARDIM VITORIA</t>
         </is>
       </c>
       <c r="B190">
@@ -5368,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -5377,7 +5377,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDINS DE MONET RESIDENCE</t>
         </is>
       </c>
       <c r="B191">
@@ -5387,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -5396,26 +5396,26 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>OASIS</t>
+          <t>JOAO DE BARRO</t>
         </is>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>KAKOGAWA</t>
         </is>
       </c>
       <c r="B193">
@@ -5434,7 +5434,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PARIGOT DE SOUZA</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B194">
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="D194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -5453,7 +5453,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PARIS</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B195">
@@ -5472,7 +5472,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PARQUE AVENIDA</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B196">
@@ -5491,7 +5491,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PARQUE DA GAVEA</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B197">
@@ -5501,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="D197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -5510,26 +5510,26 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>MANDACARU</t>
         </is>
       </c>
       <c r="B198">
         <v>1</v>
       </c>
       <c r="C198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B199">
@@ -5548,7 +5548,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B200">
@@ -5567,7 +5567,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B201">
@@ -5586,7 +5586,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>PIONEIRO ODWALDO BUENO</t>
+          <t>NOVA ALVORADA</t>
         </is>
       </c>
       <c r="B202">
@@ -5605,7 +5605,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>PORTAL DAS TORRES</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="B203">
@@ -5624,7 +5624,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B204">
@@ -5643,7 +5643,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PORTO SEGURO II</t>
+          <t>PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B205">
@@ -5662,7 +5662,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>RESIDENCIAL DOS MAGNATAS</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="B206">
@@ -5672,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -5681,7 +5681,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B207">
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -5700,26 +5700,26 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SANENGE</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B208">
         <v>1</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208">
         <v>0</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
         </is>
       </c>
       <c r="B209">
@@ -5729,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -5738,7 +5738,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>PARQUE RESIDENCIAL PATRICIA</t>
         </is>
       </c>
       <c r="B210">
@@ -5757,7 +5757,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SAO JORGE</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B211">
@@ -5776,7 +5776,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SAO SILVESTRE</t>
+          <t>PIONEIRO ODWALDO BUENO</t>
         </is>
       </c>
       <c r="B212">
@@ -5795,7 +5795,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>PORTAL DAS TORRES</t>
         </is>
       </c>
       <c r="B213">
@@ -5805,7 +5805,7 @@
         <v>0</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -5814,7 +5814,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TRES LAGOAS</t>
+          <t>PORTO SEGURO</t>
         </is>
       </c>
       <c r="B214">
@@ -5833,26 +5833,26 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TROPICAL</t>
+          <t>PORTO SEGURO II</t>
         </is>
       </c>
       <c r="B215">
         <v>1</v>
       </c>
       <c r="C215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>RECANTO DOS GUERREIROS</t>
         </is>
       </c>
       <c r="B216">
@@ -5871,7 +5871,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VILA CLEOPATRA</t>
+          <t>RESIDENCIAL DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B217">
@@ -5881,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VILA SANTO AMARAL</t>
+          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
         </is>
       </c>
       <c r="B218">
@@ -5909,7 +5909,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>SANENGE</t>
         </is>
       </c>
       <c r="B219">
@@ -5928,7 +5928,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ZONA 1</t>
+          <t>SANTA TEREZINHA</t>
         </is>
       </c>
       <c r="B220">
@@ -5947,7 +5947,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ZONA 2</t>
+          <t>SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B221">
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -5966,26 +5966,26 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>SAO JORGE</t>
         </is>
       </c>
       <c r="B222">
         <v>1</v>
       </c>
       <c r="C222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>SAO SILVESTRE</t>
         </is>
       </c>
       <c r="B223">
@@ -6004,7 +6004,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ZONA 8</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="B224">
@@ -6014,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -6023,19 +6023,247 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
+          <t>TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B225">
+        <v>1</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226">
+        <v>1</v>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B227">
+        <v>1</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>VILA CLEOPATRA</t>
+        </is>
+      </c>
+      <c r="B228">
+        <v>1</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>VILA PROGRESSO</t>
+        </is>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>VILA SANTO AMARAL</t>
+        </is>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>ZONA 02</t>
+        </is>
+      </c>
+      <c r="B231">
+        <v>1</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>ZONA 1</t>
+        </is>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ZONA 2</t>
+        </is>
+      </c>
+      <c r="B233">
+        <v>1</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>1</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+      <c r="D234">
+        <v>1</v>
+      </c>
+      <c r="E234">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B235">
+        <v>1</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ZONA 8</t>
+        </is>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>1</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
           <t>ZONA ARMAZEM</t>
         </is>
       </c>
-      <c r="B225">
-        <v>1</v>
-      </c>
-      <c r="C225">
-        <v>0</v>
-      </c>
-      <c r="D225">
-        <v>0</v>
-      </c>
-      <c r="E225">
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
         <v>0</v>
       </c>
     </row>
@@ -6046,7 +6274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6079,30 +6307,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALVAMAR</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6111,26 +6339,26 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>ALVAMAR</t>
         </is>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6174,11 +6402,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>NOVO PANORAMA</t>
         </is>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -6193,7 +6421,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B8">
@@ -6203,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6212,7 +6440,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B9">
@@ -6222,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6250,7 +6478,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B11">
@@ -6288,26 +6516,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>ECOVALLEY</t>
         </is>
       </c>
       <c r="B13">
         <v>2</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B14">
@@ -6317,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6326,7 +6554,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MAUA</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B15">
@@ -6336,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6345,7 +6573,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B16">
@@ -6355,7 +6583,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6364,7 +6592,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA</t>
+          <t>MAUA</t>
         </is>
       </c>
       <c r="B17">
@@ -6374,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6383,7 +6611,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>NOVA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B18">
@@ -6393,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6402,45 +6630,45 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>PARQUE ALVAMAR</t>
         </is>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALVAMAR II</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B21">
@@ -6459,7 +6687,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>ALVAMAR II</t>
         </is>
       </c>
       <c r="B22">
@@ -6478,7 +6706,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B23">
@@ -6488,7 +6716,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6497,7 +6725,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="B24">
@@ -6507,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6516,20 +6744,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ECOVALLEY</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6554,7 +6782,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>ESPERANCA</t>
         </is>
       </c>
       <c r="B27">
@@ -6573,7 +6801,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B28">
@@ -6592,7 +6820,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JARDIM COMETA</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B29">
@@ -6611,7 +6839,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM DOM BOSCO</t>
+          <t>JARDIM COMETA</t>
         </is>
       </c>
       <c r="B30">
@@ -6621,7 +6849,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6630,7 +6858,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>JARDIM DOM BOSCO</t>
         </is>
       </c>
       <c r="B31">
@@ -6640,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6649,7 +6877,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM NOVA PAULISTA</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B32">
@@ -6659,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6668,7 +6896,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JARDIM OURO VERDE III</t>
+          <t>JARDIM NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B33">
@@ -6687,7 +6915,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>JARDIM OURO VERDE III</t>
         </is>
       </c>
       <c r="B34">
@@ -6697,7 +6925,7 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6706,7 +6934,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JARDIM SAO PAULO II</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B35">
@@ -6716,7 +6944,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6725,7 +6953,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>JARDIM SAO PAULO</t>
         </is>
       </c>
       <c r="B36">
@@ -6744,7 +6972,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NACOES</t>
+          <t>JARDIM SAO PAULO II</t>
         </is>
       </c>
       <c r="B37">
@@ -6763,7 +6991,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA I</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B38">
@@ -6782,7 +7010,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OURO VERDE</t>
+          <t>NACOES</t>
         </is>
       </c>
       <c r="B39">
@@ -6792,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6801,7 +7029,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B40">
@@ -6820,7 +7048,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BELA VISTA</t>
+          <t>OURO VERDE</t>
         </is>
       </c>
       <c r="B41">
@@ -6839,7 +7067,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PIONEIROS</t>
+          <t>PARQUE ALVAMAR II</t>
         </is>
       </c>
       <c r="B42">
@@ -6858,7 +7086,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RESIDENCIAL GOVERNADOR JOSE RI</t>
+          <t>PARQUE RESIDENCIAL BELA VISTA</t>
         </is>
       </c>
       <c r="B43">
@@ -6868,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -6877,7 +7105,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SAO JOSE</t>
+          <t>PIONEIROS</t>
         </is>
       </c>
       <c r="B44">
@@ -6896,7 +7124,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>RESIDENCIAL GOVERNADOR JOSE RI</t>
         </is>
       </c>
       <c r="B45">
@@ -6915,7 +7143,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>VALE AZUL</t>
+          <t>SANTA TEREZA</t>
         </is>
       </c>
       <c r="B46">
@@ -6925,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -6934,19 +7162,76 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>SAO JOSE</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VALE AZUL</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>VERA CRUZ</t>
         </is>
       </c>
-      <c r="B47">
-        <v>1</v>
-      </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47">
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
         <v>0</v>
       </c>
     </row>
@@ -6957,7 +7242,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7019,7 +7304,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -7049,7 +7334,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -7069,7 +7354,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
@@ -7079,7 +7364,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -7089,7 +7374,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -7109,7 +7394,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -7119,7 +7404,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -7129,7 +7414,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -7139,7 +7424,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -7149,7 +7434,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -7169,7 +7454,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
@@ -7179,7 +7464,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23">
@@ -7229,7 +7514,27 @@
         </is>
       </c>
       <c r="B27">
-        <v>22</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -7239,7 +7544,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7516,7 +7821,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -7551,11 +7856,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -7564,24 +7869,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -7590,11 +7895,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -7603,11 +7908,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -7616,24 +7921,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -7642,11 +7947,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -7655,11 +7960,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -7668,24 +7973,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C33">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C34">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -7694,11 +7999,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -7707,11 +8012,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -7720,24 +8025,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -7746,11 +8051,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -7759,11 +8064,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -7772,24 +8077,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C42">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -7798,11 +8103,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -7811,7 +8116,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C44">
@@ -7824,24 +8129,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C45">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C46">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -7850,11 +8155,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -7863,11 +8168,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -7876,24 +8181,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C49">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C50">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -7902,11 +8207,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -7915,20 +8220,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C53">
@@ -7941,11 +8246,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -7954,11 +8259,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
@@ -7967,24 +8272,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -7993,11 +8298,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
@@ -8006,11 +8311,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C59">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -8019,11 +8324,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -8032,24 +8337,24 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C61">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C62">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -8058,11 +8363,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
@@ -8071,11 +8376,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -8084,11 +8389,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66">
@@ -8097,24 +8402,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C66">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C67">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
@@ -8123,11 +8428,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -8136,11 +8441,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
@@ -8149,24 +8454,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C70">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C71">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -8175,11 +8480,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -8188,11 +8493,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -8201,11 +8506,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
@@ -8214,24 +8519,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C75">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C76">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
@@ -8240,11 +8545,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
@@ -8253,11 +8558,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -8266,24 +8571,24 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C79">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C80">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8292,11 +8597,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82">
@@ -8305,11 +8610,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C82">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="83">
@@ -8318,11 +8623,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C83">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
@@ -8331,24 +8636,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C84">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C85">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86">
@@ -8357,11 +8662,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C86">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -8370,11 +8675,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C87">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -8383,24 +8688,24 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C88">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C89">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -8409,11 +8714,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C90">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -8422,7 +8727,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C91">
@@ -8435,24 +8740,24 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C92">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C93">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
@@ -8461,11 +8766,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C94">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -8474,11 +8779,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C95">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
@@ -8487,24 +8792,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C96">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97">
+        <v>24</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C97">
         <v>23</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C97">
-        <v>15</v>
       </c>
     </row>
     <row r="98">
@@ -8513,11 +8818,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C98">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -8526,11 +8831,11 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C99">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100">
@@ -8539,24 +8844,24 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
       <c r="A101">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8565,11 +8870,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103">
@@ -8578,11 +8883,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C103">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104">
@@ -8591,11 +8896,11 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C104">
-        <v>40</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105">
@@ -8604,24 +8909,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C105">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106">
       <c r="A106">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C106">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
@@ -8630,11 +8935,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -8643,11 +8948,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C108">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109">
@@ -8656,24 +8961,115 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110">
       <c r="A110">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>27</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>27</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>27</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C110">
-        <v>2</v>
+      <c r="C113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>28</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>28</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>28</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>28</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -773,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -833,13 +833,13 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -853,13 +853,13 @@
         <v>27142</v>
       </c>
       <c r="H2">
-        <v>320.5</v>
+        <v>361.1</v>
       </c>
       <c r="I2">
-        <v>7.4</v>
+        <v>18.4</v>
       </c>
       <c r="J2">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="3">
@@ -867,10 +867,10 @@
         <v>412830</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -887,13 +887,13 @@
         <v>2106</v>
       </c>
       <c r="H3">
-        <v>237.4</v>
+        <v>284.9</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -901,7 +901,7 @@
         <v>410220</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>4046</v>
       </c>
       <c r="H4">
-        <v>197.7</v>
+        <v>222.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -932,7 +932,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>412530</v>
+        <v>411090</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -941,24 +941,24 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAO JORGE DO IVAI</t>
+          <t>ITAGUAJE</t>
         </is>
       </c>
       <c r="G5">
-        <v>5170</v>
+        <v>4530</v>
       </c>
       <c r="H5">
-        <v>193.4</v>
+        <v>220.8</v>
       </c>
       <c r="I5">
-        <v>19.3</v>
+        <v>22.1</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>411640</v>
+        <v>411740</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -982,14 +982,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NOSSA SENHORA DAS GRACAS</t>
+          <t>OURIZONA</t>
         </is>
       </c>
       <c r="G6">
-        <v>3669</v>
+        <v>3193</v>
       </c>
       <c r="H6">
-        <v>190.8</v>
+        <v>219.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1000,138 +1000,138 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>411520</v>
+        <v>411640</v>
       </c>
       <c r="B7">
-        <v>708</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>191</v>
+        <v>3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MARINGA</t>
+          <t>NOSSA SENHORA DAS GRACAS</t>
         </is>
       </c>
       <c r="G7">
-        <v>429660</v>
+        <v>3669</v>
       </c>
       <c r="H7">
-        <v>164.8</v>
+        <v>218</v>
       </c>
       <c r="I7">
-        <v>14.9</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>411740</v>
+        <v>412530</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OURIZONA</t>
+          <t>SAO JORGE DO IVAI</t>
         </is>
       </c>
       <c r="G8">
-        <v>3193</v>
+        <v>5170</v>
       </c>
       <c r="H8">
-        <v>156.6</v>
+        <v>212.8</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>19.3</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>412450</v>
+        <v>411520</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>829</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANTO INACIO</t>
+          <t>MARINGA</t>
         </is>
       </c>
       <c r="G9">
-        <v>6463</v>
+        <v>429660</v>
       </c>
       <c r="H9">
-        <v>154.7</v>
+        <v>192.9</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>18.9</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>411090</v>
+        <v>412450</v>
       </c>
       <c r="B10">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ITAGUAJE</t>
+          <t>SANTO INACIO</t>
         </is>
       </c>
       <c r="G10">
-        <v>4530</v>
+        <v>6463</v>
       </c>
       <c r="H10">
-        <v>154.5</v>
+        <v>185.7</v>
       </c>
       <c r="I10">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1139,7 +1139,7 @@
         <v>410590</v>
       </c>
       <c r="B11">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>23313</v>
       </c>
       <c r="H11">
-        <v>150.1</v>
+        <v>175.9</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1182,18 +1182,18 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FLORAI</t>
+          <t>ITAMBE</t>
         </is>
       </c>
       <c r="G12">
-        <v>4805</v>
+        <v>6228</v>
       </c>
       <c r="H12">
-        <v>124.9</v>
+        <v>160.6</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>411110</v>
+        <v>410780</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1216,18 +1216,18 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ITAMBE</t>
+          <t>FLORAI</t>
         </is>
       </c>
       <c r="G13">
-        <v>6228</v>
+        <v>4805</v>
       </c>
       <c r="H13">
-        <v>112.4</v>
+        <v>124.9</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>411480</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1250,7 +1250,7 @@
         <v>3</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1261,41 +1261,41 @@
         <v>44749</v>
       </c>
       <c r="H14">
-        <v>109.5</v>
+        <v>120.7</v>
       </c>
       <c r="I14">
         <v>4.5</v>
       </c>
       <c r="J14">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>411810</v>
+        <v>412360</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PARANACITY</t>
+          <t>SANTA INES</t>
         </is>
       </c>
       <c r="G15">
-        <v>9549</v>
+        <v>1745</v>
       </c>
       <c r="H15">
-        <v>94.3</v>
+        <v>114.6</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1306,112 +1306,112 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>412625</v>
+        <v>411810</v>
       </c>
       <c r="B16">
-        <v>95</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SARANDI</t>
+          <t>PARANACITY</t>
         </is>
       </c>
       <c r="G16">
-        <v>128106</v>
+        <v>9549</v>
       </c>
       <c r="H16">
-        <v>74.2</v>
+        <v>104.7</v>
       </c>
       <c r="I16">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>412360</v>
+        <v>412625</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA INES</t>
+          <t>SARANDI</t>
         </is>
       </c>
       <c r="G17">
-        <v>1745</v>
+        <v>128106</v>
       </c>
       <c r="H17">
-        <v>57.3</v>
+        <v>84.3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>410790</v>
+        <v>410210</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>ASTORGA</t>
         </is>
       </c>
       <c r="G18">
-        <v>11522</v>
+        <v>26203</v>
       </c>
       <c r="H18">
-        <v>52.1</v>
+        <v>53.4</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>412040</v>
+        <v>410790</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1420,18 +1420,18 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>PRESIDENTE CASTELO BRANCO</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="G19">
-        <v>4304</v>
+        <v>11522</v>
       </c>
       <c r="H19">
-        <v>46.5</v>
+        <v>52.1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>412340</v>
+        <v>411630</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1454,18 +1454,18 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTA FE</t>
+          <t>MUNHOZ DE MELO</t>
         </is>
       </c>
       <c r="G20">
-        <v>11730</v>
+        <v>4057</v>
       </c>
       <c r="H20">
-        <v>42.6</v>
+        <v>49.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1476,30 +1476,30 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>411360</v>
+        <v>411410</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LOBATO</t>
+          <t>MANDAGUACU</t>
         </is>
       </c>
       <c r="G21">
-        <v>4707</v>
+        <v>34521</v>
       </c>
       <c r="H21">
-        <v>42.5</v>
+        <v>49.2</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1510,78 +1510,78 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>411750</v>
+        <v>412040</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>PAICANDU</t>
+          <t>PRESIDENTE CASTELO BRANCO</t>
         </is>
       </c>
       <c r="G22">
-        <v>48695</v>
+        <v>4304</v>
       </c>
       <c r="H22">
-        <v>41.1</v>
+        <v>46.5</v>
       </c>
       <c r="I22">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>411410</v>
+        <v>411750</v>
       </c>
       <c r="B23">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MANDAGUACU</t>
+          <t>PAICANDU</t>
         </is>
       </c>
       <c r="G23">
-        <v>34521</v>
+        <v>48695</v>
       </c>
       <c r="H23">
-        <v>40.6</v>
+        <v>45.2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>410210</v>
+        <v>412340</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1590,18 +1590,18 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ASTORGA</t>
+          <t>SANTA FE</t>
         </is>
       </c>
       <c r="G24">
-        <v>26203</v>
+        <v>11730</v>
       </c>
       <c r="H24">
-        <v>38.2</v>
+        <v>42.6</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1612,30 +1612,30 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>411420</v>
+        <v>411360</v>
       </c>
       <c r="B25">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MANDAGUARI</t>
+          <t>LOBATO</t>
         </is>
       </c>
       <c r="G25">
-        <v>38313</v>
+        <v>4707</v>
       </c>
       <c r="H25">
-        <v>26.1</v>
+        <v>42.5</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>411630</v>
+        <v>410810</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MUNHOZ DE MELO</t>
+          <t>FLORIDA</t>
         </is>
       </c>
       <c r="G26">
-        <v>4057</v>
+        <v>2711</v>
       </c>
       <c r="H26">
-        <v>24.6</v>
+        <v>36.9</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>411000</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>5693</v>
       </c>
       <c r="H27">
-        <v>17.6</v>
+        <v>35.1</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1714,35 +1714,69 @@
     </row>
     <row r="28">
       <c r="A28">
+        <v>411420</v>
+      </c>
+      <c r="B28">
+        <v>13</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>MANDAGUARI</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>38313</v>
+      </c>
+      <c r="H28">
+        <v>33.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
         <v>410730</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>DOUTOR CAMARGO</t>
         </is>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>6517</v>
       </c>
-      <c r="H28">
-        <v>15.3</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
+      <c r="H29">
+        <v>30.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
         <v>0</v>
       </c>
     </row>
@@ -1753,7 +1787,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E237"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1790,16 +1824,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C2">
         <v>5</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>11.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="3">
@@ -1809,16 +1843,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>3.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4">
@@ -1828,16 +1862,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>11.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -1847,16 +1881,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>11.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6">
@@ -1866,92 +1900,92 @@
         </is>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PARQUE HORTENCIA</t>
+          <t>ZONA 01</t>
         </is>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ZONA 01</t>
+          <t>LOTEAMENTO MADRID</t>
         </is>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL INOCENTE</t>
+          <t>PARQUE HORTENCIA</t>
         </is>
       </c>
       <c r="B9">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>36.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LOTEAMENTO MADRID</t>
+          <t>ZONA 03</t>
         </is>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1961,60 +1995,60 @@
         </is>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+          <t>CONJUNTO HABITACIONAL INOCENTE</t>
         </is>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12">
-        <v>11.1</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PARQUE TARUMA</t>
+          <t>VILA MARUMBY</t>
         </is>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ZONA 03</t>
+          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
         </is>
       </c>
       <c r="B14">
@@ -2024,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2033,93 +2067,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ZONA 08</t>
+          <t>DISTRITO DE IGUATEMI IGUATEMI</t>
         </is>
       </c>
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL TUIUTI</t>
+          <t>JARDIM OLIMPICO</t>
         </is>
       </c>
       <c r="B16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16">
-        <v>12.5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JARDIM COLINA VERDE</t>
+          <t>JARDIM ITAIPU</t>
         </is>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JARDIM DIAMANTE</t>
+          <t>JARDIM UNIVERSO</t>
         </is>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSO</t>
+          <t>PARQUE TARUMA</t>
         </is>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2128,93 +2162,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
+          <t>VILA EMILIA</t>
         </is>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>VILA EMILIA</t>
+          <t>ZONA 04</t>
         </is>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VILA MARUMBY</t>
+          <t>ZONA 06</t>
         </is>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZONA 04</t>
+          <t>ZONA 08</t>
         </is>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
+          <t>CHACARA PAULISTA</t>
         </is>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2223,36 +2257,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
+          <t>EBENEZER</t>
         </is>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>JARDIM IPANEMA</t>
+          <t>JARDIM AMERICA</t>
         </is>
       </c>
       <c r="B26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2261,87 +2295,87 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JARDIM OLIMPICO</t>
+          <t>JARDIM COLINA VERDE</t>
         </is>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JARDIM REAL</t>
+          <t>JARDIM DIAMANTE</t>
         </is>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LOTEAMENTO SUMARE</t>
+          <t>PARQUE INDUSTRIAL</t>
         </is>
       </c>
       <c r="B29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E29">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>VILA NOVA</t>
+          <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
         </is>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VILA SANTO ANTONIO</t>
+          <t>PARQUE RESIDENCIAL TUIUTI</t>
         </is>
       </c>
       <c r="B31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -2350,23 +2384,23 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>16.7</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ZONA 7</t>
+          <t>VILA SANTA IZABEL</t>
         </is>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2375,20 +2409,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CHACARA PAULISTA</t>
+          <t>VILA SANTO ANTONIO</t>
         </is>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="34">
@@ -2398,7 +2432,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2407,23 +2441,23 @@
         <v>1</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JARDIM AMERICA</t>
+          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
         </is>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2432,30 +2466,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JARDIM ITAIPU</t>
+          <t>CONJUNTO RESIDENCIAL NEY BRAGA</t>
         </is>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JARDIM NOVO OASIS</t>
+          <t>JARDIM IPANEMA</t>
         </is>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2470,74 +2504,74 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ROSA</t>
+          <t>JARDIM NOVO OASIS</t>
         </is>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>JOAO DE BARROS</t>
+          <t>LOTEAMENTO SUMARE</t>
         </is>
       </c>
       <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+      <c r="D39">
         <v>5</v>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
       <c r="E39">
-        <v>20</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
+          <t>VILA NOVA</t>
         </is>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>VILA SANTA IZABEL</t>
+          <t>ZONA 7</t>
         </is>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2546,106 +2580,106 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>VILA VARDELINA</t>
+          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
         </is>
       </c>
       <c r="B42">
         <v>5</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ZONA 06</t>
+          <t>JARDIM DIAS I</t>
         </is>
       </c>
       <c r="B43">
         <v>5</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL SANENGE</t>
+          <t>JARDIM REAL</t>
         </is>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO PORTO S</t>
+          <t>JARDIM SANTA ROSA</t>
         </is>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
+          <t>JOAO DE BARROS</t>
         </is>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
+          <t>PARQUE DAS BANDEIRAS</t>
         </is>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -2660,45 +2694,45 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GREVILEAS</t>
+          <t>PARQUE DAS GREVILEAS 3A PARTE</t>
         </is>
       </c>
       <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48">
         <v>4</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
       <c r="D48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JARDIM ANDRADE</t>
+          <t>VILA VARDELINA</t>
         </is>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JARDIM DIAS I</t>
+          <t>CONJUNTO HABITACIONAL SANENGE</t>
         </is>
       </c>
       <c r="B50">
@@ -2708,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2717,7 +2751,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JARDIM OASIS</t>
+          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
         </is>
       </c>
       <c r="B51">
@@ -2727,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2736,7 +2770,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JARDIM SAN REMO</t>
+          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
         </is>
       </c>
       <c r="B52">
@@ -2746,7 +2780,7 @@
         <v>2</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52">
         <v>50</v>
@@ -2755,7 +2789,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>JARDIM TROPICAL</t>
+          <t>COPACABANA RESIDENCIAL</t>
         </is>
       </c>
       <c r="B53">
@@ -2765,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2774,7 +2808,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PARQUE DAS BANDEIRAS</t>
+          <t>GREVILEAS</t>
         </is>
       </c>
       <c r="B54">
@@ -2793,7 +2827,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PARQUE DAS LARANJEIRAS</t>
+          <t>JARDIM ANDRADE</t>
         </is>
       </c>
       <c r="B55">
@@ -2803,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2812,7 +2846,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL</t>
+          <t>JARDIM BRASIL</t>
         </is>
       </c>
       <c r="B56">
@@ -2822,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2831,36 +2865,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VILA ESPERANCA</t>
+          <t>JARDIM CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B57">
         <v>4</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AEROPORTO</t>
+          <t>JARDIM OASIS</t>
         </is>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2869,17 +2903,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL JOAO DE</t>
+          <t>JARDIM PARAISO</t>
         </is>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2888,17 +2922,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL KARINA</t>
+          <t>JARDIM PARIS</t>
         </is>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2907,30 +2941,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CHAMPAG</t>
+          <t>JARDIM SAN REMO</t>
         </is>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
+          <t>JARDIM TROPICAL</t>
         </is>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2945,17 +2979,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO I</t>
+          <t>NEY BRAGA</t>
         </is>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2964,49 +2998,49 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
+          <t>PARQUE DAS GREVILEAS I PARTE</t>
         </is>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL SANTA TER</t>
+          <t>PARQUE DAS LARANJEIRAS</t>
         </is>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65">
-        <v>66.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EBENEZER</t>
+          <t>REQUIAO</t>
         </is>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -3015,17 +3049,17 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ITAIPU</t>
+          <t>VILA BOSQUE</t>
         </is>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3040,17 +3074,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE</t>
+          <t>VILA ESPERANCA</t>
         </is>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3059,17 +3093,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>JARDIM NOVO HORIZONTE</t>
+          <t>VILA IPIRANGA</t>
         </is>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3078,17 +3112,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>JARDIM PARAISO</t>
+          <t>ZONA 05</t>
         </is>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3097,7 +3131,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>JARDIM PARIS</t>
+          <t>AEROPORTO</t>
         </is>
       </c>
       <c r="B71">
@@ -3107,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3116,7 +3150,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA</t>
+          <t>CJ RES PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B72">
@@ -3135,7 +3169,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BATEL</t>
+          <t>CONJUNTO HABITACIONAL JOAO DE</t>
         </is>
       </c>
       <c r="B73">
@@ -3145,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3154,7 +3188,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NEY BRAGA</t>
+          <t>CONJUNTO HABITACIONAL KARINA</t>
         </is>
       </c>
       <c r="B74">
@@ -3164,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3173,7 +3207,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PARQUE PALMEIRAS</t>
+          <t>CONJUNTO JOAO DE BARRO CIDADE</t>
         </is>
       </c>
       <c r="B75">
@@ -3192,7 +3226,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>VILA BOSQUE</t>
+          <t>CONJUNTO JOAO DE BARRO I</t>
         </is>
       </c>
       <c r="B76">
@@ -3211,7 +3245,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>VILA IPIRANGA</t>
+          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
         </is>
       </c>
       <c r="B77">
@@ -3221,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3230,49 +3264,49 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZONA 05</t>
+          <t>CONJUNTO RESIDENCIAL BRANCA VI</t>
         </is>
       </c>
       <c r="B78">
         <v>3</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>CONJUNTO RESIDENCIAL PAULINO C</t>
         </is>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BRANCA VIEIRA</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3287,11 +3321,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CHACARAS AEROPORTO</t>
+          <t>ITAIPU</t>
         </is>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3306,17 +3340,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CJ RES PARIGOT DE SOUZA</t>
+          <t>JARDIM ALVORADA III</t>
         </is>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3325,11 +3359,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CONJUNTO JOAO DE BARRO ITAPARI</t>
+          <t>JARDIM LIBERDADE</t>
         </is>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3344,17 +3378,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>COPACABANA RESIDENCIAL</t>
+          <t>JARDIM NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3363,30 +3397,30 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DIAMANTE</t>
+          <t>JARDIM PAULISTA</t>
         </is>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E85">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DISTRITO DE FLORIANO FLORIANO</t>
+          <t>JARDIM PAULISTA III</t>
         </is>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3401,11 +3435,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EVEREST</t>
+          <t>LOTEAMENTO BATEL</t>
         </is>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3420,17 +3454,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GUAIRACA</t>
+          <t>PARQUE AVENIDA</t>
         </is>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3439,17 +3473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IPANEMA</t>
+          <t>PARQUE PALMEIRAS</t>
         </is>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3458,36 +3492,36 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>JARDIM ALVORADA III</t>
+          <t>PARQUE RESIDENCIAL QUEBEC</t>
         </is>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>JARDIM ARAUCARIA</t>
+          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
         </is>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3496,7 +3530,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>JARDIM BRASIL</t>
+          <t>AMERICA</t>
         </is>
       </c>
       <c r="B92">
@@ -3515,7 +3549,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>JARDIM CAMPOS ELISIOS</t>
+          <t>AREA RURAL DE MARINGA</t>
         </is>
       </c>
       <c r="B93">
@@ -3534,7 +3568,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JARDIM CIDADE MONCOES</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B94">
@@ -3544,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3553,7 +3587,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JARDIM DAS ESTACOES</t>
+          <t>BRANCA VIEIRA</t>
         </is>
       </c>
       <c r="B95">
@@ -3563,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3572,7 +3606,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JARDIM DAS FLORES</t>
+          <t>CHACARAS AEROPORTO</t>
         </is>
       </c>
       <c r="B96">
@@ -3591,26 +3625,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JARDIM DO CARMO</t>
+          <t>CIDADE ALTA</t>
         </is>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>1</v>
       </c>
       <c r="E97">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JARDIM GUAIRACA</t>
+          <t>CONJUNTO HABITACIONAL ITATIAIA</t>
         </is>
       </c>
       <c r="B98">
@@ -3629,7 +3663,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JARDIM IMPERIAL II</t>
+          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
         </is>
       </c>
       <c r="B99">
@@ -3639,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3648,7 +3682,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA</t>
+          <t>DIAMANTE</t>
         </is>
       </c>
       <c r="B100">
@@ -3667,7 +3701,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JARDIM MONTE CARLO</t>
+          <t>EVEREST</t>
         </is>
       </c>
       <c r="B101">
@@ -3686,7 +3720,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JARDIM MONTE REI</t>
+          <t>GUAIRACA</t>
         </is>
       </c>
       <c r="B102">
@@ -3705,7 +3739,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JARDIM NOVO ALVORADA</t>
+          <t>JARDIM CIDADE MONCOES</t>
         </is>
       </c>
       <c r="B103">
@@ -3715,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3724,7 +3758,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JARDIM PARIS III</t>
+          <t>JARDIM DO CARMO</t>
         </is>
       </c>
       <c r="B104">
@@ -3734,7 +3768,7 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>50</v>
@@ -3743,7 +3777,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JARDIM PAULISTA III</t>
+          <t>JARDIM GUAIRACA</t>
         </is>
       </c>
       <c r="B105">
@@ -3753,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3762,26 +3796,26 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JARDIM SAO JORGE</t>
+          <t>JARDIM IMPERIAL II</t>
         </is>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JARDIM TABAETE</t>
+          <t>JARDIM IMPERIO DO SOL</t>
         </is>
       </c>
       <c r="B107">
@@ -3791,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3800,7 +3834,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JARDIM TRES LAGOAS</t>
+          <t>JARDIM INTERNORTE</t>
         </is>
       </c>
       <c r="B108">
@@ -3819,7 +3853,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KARINA</t>
+          <t>JARDIM ITALIA</t>
         </is>
       </c>
       <c r="B109">
@@ -3829,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3838,7 +3872,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LOTEAMENTO BELA VISTA</t>
+          <t>JARDIM ITALIA II</t>
         </is>
       </c>
       <c r="B110">
@@ -3848,7 +3882,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3857,7 +3891,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LOTEAMENTO GRAJAU</t>
+          <t>JARDIM MONTE CARLO</t>
         </is>
       </c>
       <c r="B111">
@@ -3867,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3876,7 +3910,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NOVO HORIZONTE</t>
+          <t>JARDIM MONTE REI</t>
         </is>
       </c>
       <c r="B112">
@@ -3886,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3895,7 +3929,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PARQUE AVENIDA</t>
+          <t>JARDIM MONTREAL</t>
         </is>
       </c>
       <c r="B113">
@@ -3905,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3914,45 +3948,45 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PARQUE DAS GREVILEAS I PARTE</t>
+          <t>JARDIM NOVO ALVORADA</t>
         </is>
       </c>
       <c r="B114">
         <v>2</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL 200</t>
+          <t>JARDIM ORIENTAL</t>
         </is>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
+          <t>JARDIM OURO COLA</t>
         </is>
       </c>
       <c r="B116">
@@ -3962,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -3971,45 +4005,45 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL QUEBEC</t>
+          <t>JARDIM PARIS III</t>
         </is>
       </c>
       <c r="B117">
         <v>2</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PIATA</t>
+          <t>JARDIM REBOUCAS</t>
         </is>
       </c>
       <c r="B118">
         <v>2</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>QUEBEC</t>
+          <t>JARDIM SAO FRANCISCO</t>
         </is>
       </c>
       <c r="B119">
@@ -4028,7 +4062,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>RECANTO DOS MAGNATAS</t>
+          <t>JARDIM SAO JORGE</t>
         </is>
       </c>
       <c r="B120">
@@ -4038,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4047,45 +4081,45 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REQUIAO</t>
+          <t>JARDIM TABAETE</t>
         </is>
       </c>
       <c r="B121">
         <v>2</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>RESIDENCIAL IBIRAPUERA</t>
+          <t>JOAO DE BARRO</t>
         </is>
       </c>
       <c r="B122">
         <v>2</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SUMARE</t>
+          <t>KARINA</t>
         </is>
       </c>
       <c r="B123">
@@ -4104,7 +4138,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TARUMA</t>
+          <t>LOTEAMENTO BELA VISTA</t>
         </is>
       </c>
       <c r="B124">
@@ -4114,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4123,7 +4157,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>UNIVERSO</t>
+          <t>LOTEAMENTO GRAJAU</t>
         </is>
       </c>
       <c r="B125">
@@ -4133,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4142,11 +4176,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ALTO DAS GREVILEAS</t>
+          <t>NOVO ALVORADA</t>
         </is>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -4161,11 +4195,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AMERICA</t>
+          <t>NOVO HORIZONTE</t>
         </is>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -4180,17 +4214,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ARMAZEM</t>
+          <t>PARIS</t>
         </is>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4199,17 +4233,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ATLANTA</t>
+          <t>PARQUE DAS GREVILEAS II PARTE</t>
         </is>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4218,30 +4252,30 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>AURORA</t>
+          <t>PARQUE INDUSTRIAL 200</t>
         </is>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>AVENIDA</t>
+          <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
         </is>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -4256,11 +4290,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BOM JARDIM</t>
+          <t>PIATA</t>
         </is>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -4275,11 +4309,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BRASIL</t>
+          <t>QUEBEC</t>
         </is>
       </c>
       <c r="B133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -4294,11 +4328,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>CAMPOS ELISIOS</t>
+          <t>RECANTO DOS MAGNATAS</t>
         </is>
       </c>
       <c r="B134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -4313,11 +4347,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>CIDADE ALTA</t>
+          <t>SUMARE</t>
         </is>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -4332,17 +4366,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CIDADE JARDIM</t>
+          <t>TARUMA</t>
         </is>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4351,17 +4385,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CIDADE UNIVERSITARIA</t>
+          <t>UNIVERSO</t>
         </is>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4370,11 +4404,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
+          <t>ZONA 02</t>
         </is>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -4389,7 +4423,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CONJUNTO HABITACIONAL ITATIAIA</t>
+          <t>ALTO DAS GREVILEAS</t>
         </is>
       </c>
       <c r="B139">
@@ -4408,7 +4442,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
+          <t>ARMAZEM</t>
         </is>
       </c>
       <c r="B140">
@@ -4427,7 +4461,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>COPACABANA</t>
+          <t>ATLANTA</t>
         </is>
       </c>
       <c r="B141">
@@ -4446,7 +4480,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DISTRITO IGUATEMI</t>
+          <t>AURORA</t>
         </is>
       </c>
       <c r="B142">
@@ -4465,7 +4499,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DONA ANGELINA</t>
+          <t>AVENIDA</t>
         </is>
       </c>
       <c r="B143">
@@ -4484,7 +4518,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FORTALEZA</t>
+          <t>BOM JARDIM</t>
         </is>
       </c>
       <c r="B144">
@@ -4503,7 +4537,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GALEAO</t>
+          <t>BRASIL</t>
         </is>
       </c>
       <c r="B145">
@@ -4522,7 +4556,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GLEBA PATRIMONIO MARINGA</t>
+          <t>CAMPOS ELISIOS</t>
         </is>
       </c>
       <c r="B146">
@@ -4541,7 +4575,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>GRAJAU</t>
+          <t>CIDADE JARDIM</t>
         </is>
       </c>
       <c r="B147">
@@ -4560,7 +4594,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>HABITACIONAL SOL NASCENTE</t>
+          <t>CIDADE UNIVERSITARIA</t>
         </is>
       </c>
       <c r="B148">
@@ -4579,7 +4613,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>HORTENSIA</t>
+          <t>COLINA VERDE</t>
         </is>
       </c>
       <c r="B149">
@@ -4598,7 +4632,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>IBIRAPUERA</t>
+          <t>CONJUNTO HABITACIONAL DEL PLAT</t>
         </is>
       </c>
       <c r="B150">
@@ -4608,7 +4642,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -4617,7 +4651,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>IGUATEMI</t>
+          <t>CONJUNTO RESEDENCIAL</t>
         </is>
       </c>
       <c r="B151">
@@ -4627,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -4636,7 +4670,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>INDUSTRIAL</t>
+          <t>CONJUNTO RESIDENCIAL JOAO PAUL</t>
         </is>
       </c>
       <c r="B152">
@@ -4646,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -4655,7 +4689,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JARDIM ATLANTA</t>
+          <t>COPACABANA</t>
         </is>
       </c>
       <c r="B153">
@@ -4665,7 +4699,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -4674,26 +4708,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>JARDIM AURORA</t>
+          <t>DISTRITO DE FLORIANO FLORIANO</t>
         </is>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>JARDIM BELA VISTA</t>
+          <t>DISTRITO IGUATEMI</t>
         </is>
       </c>
       <c r="B155">
@@ -4703,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -4712,7 +4746,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>JARDIM BELO HORIZONTE IGUATEM</t>
+          <t>DONA ANGELINA</t>
         </is>
       </c>
       <c r="B156">
@@ -4731,26 +4765,26 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>JARDIM BERTIOGA</t>
+          <t>FORTALEZA</t>
         </is>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>JARDIM BRASILIA</t>
+          <t>GALEAO</t>
         </is>
       </c>
       <c r="B158">
@@ -4769,7 +4803,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JARDIM CANADA</t>
+          <t>GLEBA PATRIMONIO MARINGA</t>
         </is>
       </c>
       <c r="B159">
@@ -4779,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -4788,7 +4822,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>JARDIM CERRO AZUL</t>
+          <t>GLORIA</t>
         </is>
       </c>
       <c r="B160">
@@ -4807,7 +4841,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>JARDIM COPACABANA</t>
+          <t>GRAJAU</t>
         </is>
       </c>
       <c r="B161">
@@ -4817,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="D161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -4826,7 +4860,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>JARDIM DIAS II</t>
+          <t>HABITACIONAL PIONEIRO JOSE</t>
         </is>
       </c>
       <c r="B162">
@@ -4845,7 +4879,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>JARDIM DOS PASSAROS</t>
+          <t>HABITACIONAL SOL NASCENTE</t>
         </is>
       </c>
       <c r="B163">
@@ -4864,7 +4898,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>JARDIM EVEREST</t>
+          <t>HORTENSIA</t>
         </is>
       </c>
       <c r="B164">
@@ -4883,7 +4917,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>JARDIM HANOVER</t>
+          <t>IBIRAPUERA</t>
         </is>
       </c>
       <c r="B165">
@@ -4893,7 +4927,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -4902,7 +4936,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>JARDIM IGUACU</t>
+          <t>IGUATEMI</t>
         </is>
       </c>
       <c r="B166">
@@ -4912,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -4921,7 +4955,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>IMPERIAL</t>
         </is>
       </c>
       <c r="B167">
@@ -4940,7 +4974,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JARDIM INTERNORTE</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="B168">
@@ -4959,7 +4993,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>JARDIM ITALIA II</t>
+          <t>JARDIM ACLIMACAO</t>
         </is>
       </c>
       <c r="B169">
@@ -4978,26 +5012,26 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>JARDIM LAODICEIA</t>
+          <t>JARDIM ARAUCARIA</t>
         </is>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170">
         <v>0</v>
       </c>
       <c r="E170">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>JARDIM LEBLON</t>
+          <t>JARDIM ATLANTA</t>
         </is>
       </c>
       <c r="B171">
@@ -5016,7 +5050,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>JARDIM LIBERDADE III</t>
+          <t>JARDIM AURORA</t>
         </is>
       </c>
       <c r="B172">
@@ -5026,7 +5060,7 @@
         <v>1</v>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172">
         <v>100</v>
@@ -5035,7 +5069,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>JARDIM MANDACARU</t>
+          <t>JARDIM BELA VISTA</t>
         </is>
       </c>
       <c r="B173">
@@ -5054,45 +5088,45 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>JARDIM MARAJOARA IGUATEMI</t>
+          <t>JARDIM BELO HORIZONTE IGUATEM</t>
         </is>
       </c>
       <c r="B174">
         <v>1</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>JARDIM MARAVILHA</t>
+          <t>JARDIM BERTIOGA</t>
         </is>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E175">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>JARDIM BRASILIA</t>
         </is>
       </c>
       <c r="B176">
@@ -5111,7 +5145,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>JARDIM NOROESTE</t>
+          <t>JARDIM CANADA</t>
         </is>
       </c>
       <c r="B177">
@@ -5121,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -5130,26 +5164,26 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>JARDIM NOVO PAULISTA</t>
+          <t>JARDIM CATEDRAL</t>
         </is>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>JARDIM ORIENTAL</t>
+          <t>JARDIM CERRO AZUL</t>
         </is>
       </c>
       <c r="B179">
@@ -5168,7 +5202,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>JARDIM OURO COLA</t>
+          <t>JARDIM COPACABANA</t>
         </is>
       </c>
       <c r="B180">
@@ -5187,7 +5221,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>JARDIM PARQUE DO HORTO</t>
+          <t>JARDIM DAS ESTACOES</t>
         </is>
       </c>
       <c r="B181">
@@ -5197,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -5206,7 +5240,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS II</t>
+          <t>JARDIM DAS FLORES</t>
         </is>
       </c>
       <c r="B182">
@@ -5225,7 +5259,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>JARDIM PINHEIROS III</t>
+          <t>JARDIM DIAS II</t>
         </is>
       </c>
       <c r="B183">
@@ -5244,7 +5278,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>JARDIM REBOUCAS</t>
+          <t>JARDIM DOS PASSAROS</t>
         </is>
       </c>
       <c r="B184">
@@ -5263,7 +5297,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>JARDIM SANTA ALICE</t>
+          <t>JARDIM ESPANHA</t>
         </is>
       </c>
       <c r="B185">
@@ -5273,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -5282,7 +5316,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>JARDIM SANTA HELENA</t>
+          <t>JARDIM EVEREST</t>
         </is>
       </c>
       <c r="B186">
@@ -5301,7 +5335,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>JARDIM SAO FRANCISCO</t>
+          <t>JARDIM HANOVER</t>
         </is>
       </c>
       <c r="B187">
@@ -5311,7 +5345,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -5320,7 +5354,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>JARDIM TOQUIO</t>
+          <t>JARDIM IGUACU</t>
         </is>
       </c>
       <c r="B188">
@@ -5330,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -5339,26 +5373,26 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>JARDIM TUPINAMBA</t>
+          <t>JARDIM IMPERIAL</t>
         </is>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>JARDIM VITORIA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B190">
@@ -5368,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -5377,64 +5411,64 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>JARDINS DE MONET RESIDENCE</t>
+          <t>JARDIM LAODICEIA</t>
         </is>
       </c>
       <c r="B191">
         <v>1</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>JOAO DE BARRO</t>
+          <t>JARDIM LEBLON</t>
         </is>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KAKOGAWA</t>
+          <t>JARDIM LIBERDADE III</t>
         </is>
       </c>
       <c r="B193">
         <v>1</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>LEA LEAL</t>
+          <t>JARDIM LICCE</t>
         </is>
       </c>
       <c r="B194">
@@ -5453,7 +5487,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>LOT SUMARE</t>
+          <t>JARDIM MANDACARU</t>
         </is>
       </c>
       <c r="B195">
@@ -5463,7 +5497,7 @@
         <v>0</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -5472,26 +5506,26 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>LUCIANOPOLIS</t>
+          <t>JARDIM MARAJOARA IGUATEMI</t>
         </is>
       </c>
       <c r="B196">
         <v>1</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196">
         <v>0</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>MADRID</t>
+          <t>JARDIM MARAVILHA</t>
         </is>
       </c>
       <c r="B197">
@@ -5510,7 +5544,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MANDACARU</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B198">
@@ -5529,7 +5563,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>MARUMBY</t>
+          <t>JARDIM NOROESTE</t>
         </is>
       </c>
       <c r="B199">
@@ -5539,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -5548,7 +5582,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>MONTE REI</t>
+          <t>JARDIM NOVO PAULISTA</t>
         </is>
       </c>
       <c r="B200">
@@ -5567,7 +5601,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>MORANGUEIRA</t>
+          <t>JARDIM PARQUE DO HORTO</t>
         </is>
       </c>
       <c r="B201">
@@ -5577,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -5586,7 +5620,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>NOVA ALVORADA</t>
+          <t>JARDIM PAULISTA IV</t>
         </is>
       </c>
       <c r="B202">
@@ -5605,7 +5639,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>OASIS</t>
+          <t>JARDIM PINHEIROS</t>
         </is>
       </c>
       <c r="B203">
@@ -5615,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -5624,7 +5658,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>PARAISO</t>
+          <t>JARDIM PINHEIROS II</t>
         </is>
       </c>
       <c r="B204">
@@ -5643,7 +5677,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>PARIGOT DE SOUZA</t>
+          <t>JARDIM PINHEIROS III</t>
         </is>
       </c>
       <c r="B205">
@@ -5653,7 +5687,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -5662,7 +5696,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>PARIS</t>
+          <t>JARDIM SANTA ALICE</t>
         </is>
       </c>
       <c r="B206">
@@ -5672,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -5681,7 +5715,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PARQUE DA GAVEA</t>
+          <t>JARDIM SANTA HELENA</t>
         </is>
       </c>
       <c r="B207">
@@ -5700,26 +5734,26 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL AEROPORTO</t>
+          <t>JARDIM SAO PAULO</t>
         </is>
       </c>
       <c r="B208">
         <v>1</v>
       </c>
       <c r="C208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D208">
         <v>0</v>
       </c>
       <c r="E208">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL ELDORADO</t>
+          <t>JARDIM TOQUIO</t>
         </is>
       </c>
       <c r="B209">
@@ -5738,7 +5772,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL PATRICIA</t>
+          <t>JARDIM TRES LAGOAS</t>
         </is>
       </c>
       <c r="B210">
@@ -5748,7 +5782,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -5757,26 +5791,26 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PINHEIROS</t>
+          <t>JARDIM TUPINAMBA</t>
         </is>
       </c>
       <c r="B211">
         <v>1</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PIONEIRO ODWALDO BUENO</t>
+          <t>JARDIM VITORIA</t>
         </is>
       </c>
       <c r="B212">
@@ -5786,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -5795,7 +5829,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>PORTAL DAS TORRES</t>
+          <t>JARDINS DE MONET RESIDENCE</t>
         </is>
       </c>
       <c r="B213">
@@ -5814,7 +5848,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PORTO SEGURO</t>
+          <t>KAKOGAWA</t>
         </is>
       </c>
       <c r="B214">
@@ -5833,7 +5867,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>PORTO SEGURO II</t>
+          <t>LEA LEAL</t>
         </is>
       </c>
       <c r="B215">
@@ -5843,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="D215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -5852,7 +5886,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RECANTO DOS GUERREIROS</t>
+          <t>LOT SUMARE</t>
         </is>
       </c>
       <c r="B216">
@@ -5871,7 +5905,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>RESIDENCIAL DOS MAGNATAS</t>
+          <t>LUCIANOPOLIS</t>
         </is>
       </c>
       <c r="B217">
@@ -5881,7 +5915,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -5890,7 +5924,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
+          <t>MADRID</t>
         </is>
       </c>
       <c r="B218">
@@ -5909,7 +5943,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SANENGE</t>
+          <t>MANDACARU</t>
         </is>
       </c>
       <c r="B219">
@@ -5928,7 +5962,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SANTA TEREZINHA</t>
+          <t>MARUMBY</t>
         </is>
       </c>
       <c r="B220">
@@ -5938,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -5947,7 +5981,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SAO FRANCISCO</t>
+          <t>MONTE REI</t>
         </is>
       </c>
       <c r="B221">
@@ -5966,7 +6000,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SAO JORGE</t>
+          <t>MORANGUEIRA</t>
         </is>
       </c>
       <c r="B222">
@@ -5985,7 +6019,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SAO SILVESTRE</t>
+          <t>NOVA ALVORADA</t>
         </is>
       </c>
       <c r="B223">
@@ -6004,7 +6038,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>OASIS</t>
         </is>
       </c>
       <c r="B224">
@@ -6023,7 +6057,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TRES LAGOAS</t>
+          <t>PARAISO</t>
         </is>
       </c>
       <c r="B225">
@@ -6042,26 +6076,26 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TROPICAL</t>
+          <t>PARIGOT DE SOUZA</t>
         </is>
       </c>
       <c r="B226">
         <v>1</v>
       </c>
       <c r="C226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D226">
         <v>1</v>
       </c>
       <c r="E226">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TUIUTI</t>
+          <t>PARQUE DA GAVEA</t>
         </is>
       </c>
       <c r="B227">
@@ -6071,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -6080,7 +6114,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VILA CLEOPATRA</t>
+          <t>PARQUE LAGOA DOURADA</t>
         </is>
       </c>
       <c r="B228">
@@ -6099,26 +6133,26 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VILA PROGRESSO</t>
+          <t>PARQUE RESIDENCIAL AEROPORTO</t>
         </is>
       </c>
       <c r="B229">
         <v>1</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229">
         <v>0</v>
       </c>
       <c r="E229">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VILA SANTO AMARAL</t>
+          <t>PARQUE RESIDENCIAL ELDORADO</t>
         </is>
       </c>
       <c r="B230">
@@ -6128,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6137,7 +6171,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ZONA 02</t>
+          <t>PARQUE RESIDENCIAL PATRICIA</t>
         </is>
       </c>
       <c r="B231">
@@ -6156,7 +6190,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ZONA 1</t>
+          <t>PINHEIROS</t>
         </is>
       </c>
       <c r="B232">
@@ -6175,7 +6209,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ZONA 2</t>
+          <t>PIONEIRO ODWALDO BUENO</t>
         </is>
       </c>
       <c r="B233">
@@ -6185,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -6194,26 +6228,26 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ZONA 3</t>
+          <t>PORTAL DAS TORRES</t>
         </is>
       </c>
       <c r="B234">
         <v>1</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234">
         <v>1</v>
       </c>
       <c r="E234">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ZONA 6</t>
+          <t>PORTO SEGURO</t>
         </is>
       </c>
       <c r="B235">
@@ -6232,7 +6266,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ZONA 8</t>
+          <t>PORTO SEGURO II</t>
         </is>
       </c>
       <c r="B236">
@@ -6251,19 +6285,418 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
+          <t>RECANTO DOS GUERREIROS</t>
+        </is>
+      </c>
+      <c r="B237">
+        <v>1</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL DOS MAGNATAS</t>
+        </is>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+      <c r="E238">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL IBIRAPUERA</t>
+        </is>
+      </c>
+      <c r="B239">
+        <v>1</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>SANENGE</t>
+        </is>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>SANTA TEREZINHA</t>
+        </is>
+      </c>
+      <c r="B241">
+        <v>1</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>SAO FRANCISCO</t>
+        </is>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>SAO JORGE</t>
+        </is>
+      </c>
+      <c r="B243">
+        <v>1</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>SAO SILVESTRE</t>
+        </is>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>TRES LAGOAS</t>
+        </is>
+      </c>
+      <c r="B246">
+        <v>1</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>TROPICAL</t>
+        </is>
+      </c>
+      <c r="B247">
+        <v>1</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+      <c r="E247">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>TUIUTI</t>
+        </is>
+      </c>
+      <c r="B248">
+        <v>1</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>VILA CLEOPATRA</t>
+        </is>
+      </c>
+      <c r="B249">
+        <v>1</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>VILA PROGRESSO</t>
+        </is>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>VILA SANTO AMARAL</t>
+        </is>
+      </c>
+      <c r="B251">
+        <v>1</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>ZONA 1</t>
+        </is>
+      </c>
+      <c r="B252">
+        <v>1</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>ZONA 2</t>
+        </is>
+      </c>
+      <c r="B253">
+        <v>1</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ZONA 28</t>
+        </is>
+      </c>
+      <c r="B254">
+        <v>1</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ZONA 3</t>
+        </is>
+      </c>
+      <c r="B255">
+        <v>1</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+      <c r="E255">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ZONA 6</t>
+        </is>
+      </c>
+      <c r="B256">
+        <v>1</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ZONA 8</t>
+        </is>
+      </c>
+      <c r="B257">
+        <v>1</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
           <t>ZONA ARMAZEM</t>
         </is>
       </c>
-      <c r="B237">
-        <v>1</v>
-      </c>
-      <c r="C237">
-        <v>0</v>
-      </c>
-      <c r="D237">
-        <v>0</v>
-      </c>
-      <c r="E237">
+      <c r="B258">
+        <v>1</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
         <v>0</v>
       </c>
     </row>
@@ -6274,7 +6707,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -6307,39 +6740,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PANORAMA</t>
+          <t>VERAO</t>
         </is>
       </c>
       <c r="B2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>28.6</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VERAO</t>
+          <t>PANORAMA</t>
         </is>
       </c>
       <c r="B3">
         <v>7</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="4">
@@ -6383,26 +6816,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JARDIM VERAO</t>
+          <t>INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NOVO PANORAMA</t>
+          <t>JARDIM INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B7">
@@ -6412,7 +6845,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6421,36 +6854,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDEPENDENCIA</t>
+          <t>JARDIM VERAO</t>
         </is>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JARDIM INDEPENDENCIA</t>
+          <t>MONTEREY</t>
         </is>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6459,11 +6892,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>JARDIM UNIVERSAL</t>
+          <t>NOVO PANORAMA</t>
         </is>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -6478,7 +6911,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MONTEREY</t>
+          <t>FLORESTA</t>
         </is>
       </c>
       <c r="B11">
@@ -6488,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6497,7 +6930,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
+          <t>JARDIM PANORAMA</t>
         </is>
       </c>
       <c r="B12">
@@ -6507,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6516,30 +6949,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ECOVALLEY</t>
+          <t>JARDIM UNIVERSAL</t>
         </is>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FLORESTA</t>
+          <t>PARQUE RESIDENCIAL BOM PASTOR</t>
         </is>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -6554,26 +6987,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>JARDIM MONTEREY</t>
+          <t>ECOVALLEY</t>
         </is>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JARDIM PANORAMA</t>
+          <t>ESPLANADA</t>
         </is>
       </c>
       <c r="B16">
@@ -6583,7 +7016,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6592,7 +7025,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MAUA</t>
+          <t>JARDIM MONTEREY</t>
         </is>
       </c>
       <c r="B17">
@@ -6602,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6611,7 +7044,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA</t>
+          <t>MAUA</t>
         </is>
       </c>
       <c r="B18">
@@ -6621,7 +7054,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6630,7 +7063,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NOVA PAULISTA</t>
+          <t>NOVA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B19">
@@ -6640,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6649,49 +7082,49 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR</t>
+          <t>NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ALPHAVILLE</t>
+          <t>PARQUE ALVAMAR</t>
         </is>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ALVAMAR II</t>
+          <t>VALE AZUL</t>
         </is>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -6706,7 +7139,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BELA VISTA</t>
+          <t>ALPHAVILLE</t>
         </is>
       </c>
       <c r="B23">
@@ -6725,7 +7158,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CENTRO</t>
+          <t>ALVAMAR II</t>
         </is>
       </c>
       <c r="B24">
@@ -6735,7 +7168,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6744,7 +7177,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CEREJEIRA</t>
+          <t>BELA VISTA</t>
         </is>
       </c>
       <c r="B25">
@@ -6763,7 +7196,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ECOVALLEY ECOLOGIC CITY</t>
+          <t>CENTRO</t>
         </is>
       </c>
       <c r="B26">
@@ -6782,7 +7215,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ESPERANCA</t>
+          <t>CEREJEIRA</t>
         </is>
       </c>
       <c r="B27">
@@ -6801,7 +7234,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ESPLANADA</t>
+          <t>ECOVALLEY ECOLOGIC CITY</t>
         </is>
       </c>
       <c r="B28">
@@ -6811,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6820,7 +7253,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GRALHA AZUL</t>
+          <t>ESPERANCA</t>
         </is>
       </c>
       <c r="B29">
@@ -6839,7 +7272,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JARDIM COMETA</t>
+          <t>GRALHA AZUL</t>
         </is>
       </c>
       <c r="B30">
@@ -6858,7 +7291,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JARDIM DOM BOSCO</t>
+          <t>IPANEMA</t>
         </is>
       </c>
       <c r="B31">
@@ -6868,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6877,7 +7310,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JARDIM NOVA INDEPENDENCIA I</t>
+          <t>JARDIM COMETA</t>
         </is>
       </c>
       <c r="B32">
@@ -6896,7 +7329,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JARDIM NOVA PAULISTA</t>
+          <t>JARDIM DOM BOSCO</t>
         </is>
       </c>
       <c r="B33">
@@ -6915,7 +7348,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JARDIM OURO VERDE III</t>
+          <t>JARDIM INDEPENDENCIA II</t>
         </is>
       </c>
       <c r="B34">
@@ -6934,7 +7367,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JARDIM PERIMETRAL</t>
+          <t>JARDIM NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B35">
@@ -6953,7 +7386,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JARDIM SAO PAULO</t>
+          <t>JARDIM NOVA PAULISTA</t>
         </is>
       </c>
       <c r="B36">
@@ -6963,7 +7396,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6972,7 +7405,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JARDIM SAO PAULO II</t>
+          <t>JARDIM OURO VERDE III</t>
         </is>
       </c>
       <c r="B37">
@@ -6991,7 +7424,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JARDIM TRIANGULO</t>
+          <t>JARDIM PERIMETRAL</t>
         </is>
       </c>
       <c r="B38">
@@ -7010,7 +7443,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NACOES</t>
+          <t>JARDIM SAO PAULO</t>
         </is>
       </c>
       <c r="B39">
@@ -7020,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7029,7 +7462,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NOVA INDEPENDENCIA I</t>
+          <t>JARDIM SAO PAULO II</t>
         </is>
       </c>
       <c r="B40">
@@ -7039,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7048,7 +7481,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OURO VERDE</t>
+          <t>JARDIM TRIANGULO</t>
         </is>
       </c>
       <c r="B41">
@@ -7067,7 +7500,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PARQUE ALVAMAR II</t>
+          <t>NACOES</t>
         </is>
       </c>
       <c r="B42">
@@ -7077,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -7086,7 +7519,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PARQUE RESIDENCIAL BELA VISTA</t>
+          <t>NOVA ALIANCA</t>
         </is>
       </c>
       <c r="B43">
@@ -7096,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -7105,7 +7538,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PIONEIROS</t>
+          <t>NOVA INDEPENDENCIA I</t>
         </is>
       </c>
       <c r="B44">
@@ -7124,7 +7557,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RESIDENCIAL GOVERNADOR JOSE RI</t>
+          <t>NOVO INDEPENDENCIA</t>
         </is>
       </c>
       <c r="B45">
@@ -7134,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -7143,7 +7576,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SANTA TEREZA</t>
+          <t>OURO VERDE</t>
         </is>
       </c>
       <c r="B46">
@@ -7153,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -7162,7 +7595,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SAO JOSE</t>
+          <t>PARQUE ALVAMAR II</t>
         </is>
       </c>
       <c r="B47">
@@ -7181,7 +7614,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SAO PAULO</t>
+          <t>PARQUE RESIDENCIAL BELA VISTA</t>
         </is>
       </c>
       <c r="B48">
@@ -7191,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -7200,7 +7633,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>VALE AZUL</t>
+          <t>PARQUE SAO PEDRO</t>
         </is>
       </c>
       <c r="B49">
@@ -7210,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -7219,19 +7652,133 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>PIONEIROS</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>RESIDENCIAL GOVERNADOR JOSE RI</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SANTA TEREZA</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SAO JOSE</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SAO PAULO</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>UNIVERSAL</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>1</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>VERA CRUZ</t>
         </is>
       </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50">
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
         <v>0</v>
       </c>
     </row>
@@ -7242,7 +7789,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7354,7 +7901,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -7384,7 +7931,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -7404,7 +7951,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
@@ -7454,7 +8001,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -7464,7 +8011,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23">
@@ -7514,7 +8061,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
@@ -7534,7 +8081,57 @@
         </is>
       </c>
       <c r="B29">
-        <v>56</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7544,7 +8141,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C117"/>
+  <dimension ref="A1:C136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7687,7 +8284,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro agente etiológico</t>
         </is>
       </c>
       <c r="C11">
@@ -7700,24 +8297,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Outro agente etiológico</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C13">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7726,11 +8323,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -7739,24 +8336,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -7765,11 +8362,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -7778,11 +8375,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro agente etiológico</t>
         </is>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -7791,11 +8388,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Outro agente etiológico</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -7804,24 +8401,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -7830,11 +8427,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -7843,11 +8440,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -7856,24 +8453,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -7882,11 +8479,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -7895,11 +8492,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -7925,7 +8522,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -8055,7 +8652,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -8198,7 +8795,7 @@
         </is>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -8250,7 +8847,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -8263,7 +8860,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -8276,7 +8873,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
@@ -8315,7 +8912,7 @@
         </is>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -8328,7 +8925,7 @@
         </is>
       </c>
       <c r="C60">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -8341,7 +8938,7 @@
         </is>
       </c>
       <c r="C61">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
@@ -8380,7 +8977,7 @@
         </is>
       </c>
       <c r="C64">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -8393,7 +8990,7 @@
         </is>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -8406,7 +9003,7 @@
         </is>
       </c>
       <c r="C66">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -8432,7 +9029,7 @@
         </is>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -8458,7 +9055,7 @@
         </is>
       </c>
       <c r="C70">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
@@ -8484,7 +9081,7 @@
         </is>
       </c>
       <c r="C72">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -8497,7 +9094,7 @@
         </is>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -8510,7 +9107,7 @@
         </is>
       </c>
       <c r="C74">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
@@ -8523,7 +9120,7 @@
         </is>
       </c>
       <c r="C75">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
@@ -8536,7 +9133,7 @@
         </is>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
@@ -8545,11 +9142,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -8558,7 +9155,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C78">
@@ -8567,15 +9164,15 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C79">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8584,11 +9181,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -8597,11 +9194,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C81">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -8610,11 +9207,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C82">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83">
@@ -8623,7 +9220,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C83">
@@ -8632,15 +9229,15 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C84">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
@@ -8649,11 +9246,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C85">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -8662,11 +9259,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C86">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
@@ -8675,24 +9272,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
@@ -8701,11 +9298,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C89">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -8714,11 +9311,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C90">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91">
@@ -8727,24 +9324,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C91">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C92">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
@@ -8753,11 +9350,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C93">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -8766,11 +9363,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95">
@@ -8779,24 +9376,24 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C95">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96">
+        <v>24</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C96">
         <v>23</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>SRAG não especificada</t>
-        </is>
-      </c>
-      <c r="C96">
-        <v>17</v>
       </c>
     </row>
     <row r="97">
@@ -8805,11 +9402,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C97">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -8818,11 +9415,11 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C98">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
@@ -8831,24 +9428,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C99">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100">
       <c r="A100">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -8857,11 +9454,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
@@ -8870,11 +9467,11 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C102">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
@@ -8883,11 +9480,11 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C103">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
@@ -8896,24 +9493,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C104">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C105">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
@@ -8922,11 +9519,11 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C106">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -8935,11 +9532,11 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C107">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -8948,24 +9545,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C108">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C109">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110">
@@ -8974,11 +9571,11 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C110">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="111">
@@ -8987,11 +9584,11 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C111">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112">
@@ -9000,24 +9597,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C112">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
       <c r="A113">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SRAG não especificada</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -9026,11 +9623,11 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Não classificado</t>
         </is>
       </c>
       <c r="C114">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115">
@@ -9039,11 +9636,11 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Não classificado</t>
+          <t>Outro vírus respiratório</t>
         </is>
       </c>
       <c r="C115">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116">
@@ -9052,24 +9649,271 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Outro vírus respiratório</t>
+          <t>SRAG não especificada</t>
         </is>
       </c>
       <c r="C116">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117">
       <c r="A117">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>29</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>29</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>29</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>29</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>SRAG não especificada</t>
         </is>
       </c>
-      <c r="C117">
+      <c r="C121">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>30</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>30</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>30</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Outro agente etiológico</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>30</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>30</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>31</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>31</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>31</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>31</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>32</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>32</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>32</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Outro vírus respiratório</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>32</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SRAG não especificada</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>33</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="C135">
         <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>33</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Não classificado</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="395">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -174,39 +174,45 @@
     <t>PARQUE HORTENCIA</t>
   </si>
   <si>
+    <t>CONJUNTO HABITACIONAL INOCENTE</t>
+  </si>
+  <si>
     <t>ZONA 03</t>
   </si>
   <si>
     <t>ALVORADA</t>
   </si>
   <si>
-    <t>CONJUNTO HABITACIONAL INOCENTE</t>
-  </si>
-  <si>
     <t>VILA MARUMBY</t>
   </si>
   <si>
+    <t>DISTRITO DE IGUATEMI IGUATEMI</t>
+  </si>
+  <si>
     <t>CONJUNTO RESIDENCIAL CIDADE AL</t>
   </si>
   <si>
-    <t>DISTRITO DE IGUATEMI IGUATEMI</t>
-  </si>
-  <si>
     <t>JARDIM OLIMPICO</t>
   </si>
   <si>
+    <t>PARQUE TARUMA</t>
+  </si>
+  <si>
     <t>JARDIM ITAIPU</t>
   </si>
   <si>
     <t>JARDIM UNIVERSO</t>
   </si>
   <si>
-    <t>PARQUE TARUMA</t>
+    <t>PARQUE RESIDENCIAL TUIUTI</t>
   </si>
   <si>
     <t>VILA EMILIA</t>
   </si>
   <si>
+    <t>VILA SANTO ANTONIO</t>
+  </si>
+  <si>
     <t>ZONA 04</t>
   </si>
   <si>
@@ -240,15 +246,9 @@
     <t>PARQUE RESIDENCIAL CIDADE NOVA</t>
   </si>
   <si>
-    <t>PARQUE RESIDENCIAL TUIUTI</t>
-  </si>
-  <si>
     <t>VILA SANTA IZABEL</t>
   </si>
   <si>
-    <t>VILA SANTO ANTONIO</t>
-  </si>
-  <si>
     <t>CONJUNTO JOAO DE BARRO PORTO S</t>
   </si>
   <si>
@@ -264,6 +264,9 @@
     <t>LOTEAMENTO SUMARE</t>
   </si>
   <si>
+    <t>PARQUE DAS BANDEIRAS</t>
+  </si>
+  <si>
     <t>VILA NOVA</t>
   </si>
   <si>
@@ -276,6 +279,9 @@
     <t>CONJUNTO RESIDENCIAL RODOLPHO</t>
   </si>
   <si>
+    <t>JARDIM ANDRADE</t>
+  </si>
+  <si>
     <t>JARDIM DIAS I</t>
   </si>
   <si>
@@ -288,12 +294,18 @@
     <t>JOAO DE BARROS</t>
   </si>
   <si>
-    <t>PARQUE DAS BANDEIRAS</t>
-  </si>
-  <si>
     <t>PARQUE DAS GREVILEAS 3A PARTE</t>
   </si>
   <si>
+    <t>VILA ESPERANCA</t>
+  </si>
+  <si>
+    <t>CJ RES PARIGOT DE SOUZA</t>
+  </si>
+  <si>
+    <t>CONJUNTO HABITACIONAL KARINA</t>
+  </si>
+  <si>
     <t>CONJUNTO HABITACIONAL SANENGE</t>
   </si>
   <si>
@@ -309,7 +321,7 @@
     <t>GREVILEAS</t>
   </si>
   <si>
-    <t>JARDIM ANDRADE</t>
+    <t>JARDIM ALVORADA III</t>
   </si>
   <si>
     <t>JARDIM BRASIL</t>
@@ -351,9 +363,6 @@
     <t>VILA BOSQUE</t>
   </si>
   <si>
-    <t>VILA ESPERANCA</t>
-  </si>
-  <si>
     <t>VILA IPIRANGA</t>
   </si>
   <si>
@@ -363,15 +372,12 @@
     <t>AEROPORTO</t>
   </si>
   <si>
-    <t>CJ RES PARIGOT DE SOUZA</t>
+    <t>CONJUNTO HABITACIONAL ITATIAIA</t>
   </si>
   <si>
     <t>CONJUNTO HABITACIONAL JOAO DE</t>
   </si>
   <si>
-    <t>CONJUNTO HABITACIONAL KARINA</t>
-  </si>
-  <si>
     <t>CONJUNTO JOAO DE BARRO CIDADE</t>
   </si>
   <si>
@@ -387,15 +393,15 @@
     <t>CONJUNTO RESIDENCIAL PAULINO C</t>
   </si>
   <si>
+    <t>DISTRITO DE FLORIANO FLORIANO</t>
+  </si>
+  <si>
     <t>IPANEMA</t>
   </si>
   <si>
     <t>ITAIPU</t>
   </si>
   <si>
-    <t>JARDIM ALVORADA III</t>
-  </si>
-  <si>
     <t>JARDIM LIBERDADE</t>
   </si>
   <si>
@@ -426,6 +432,9 @@
     <t>RESIDENCIAL PIONEIRO ODWALDO B</t>
   </si>
   <si>
+    <t>ZONA 02</t>
+  </si>
+  <si>
     <t>AMERICA</t>
   </si>
   <si>
@@ -438,24 +447,21 @@
     <t>BRANCA VIEIRA</t>
   </si>
   <si>
+    <t>CAMPOS ELISIOS</t>
+  </si>
+  <si>
     <t>CHACARAS AEROPORTO</t>
   </si>
   <si>
     <t>CIDADE ALTA</t>
   </si>
   <si>
-    <t>CONJUNTO HABITACIONAL ITATIAIA</t>
-  </si>
-  <si>
     <t>CONJUNTO RESIDENCIAL DONA ANGE</t>
   </si>
   <si>
     <t>DIAMANTE</t>
   </si>
   <si>
-    <t>DISTRITO DE FLORIANO FLORIANO</t>
-  </si>
-  <si>
     <t>EVEREST</t>
   </si>
   <si>
@@ -561,9 +567,6 @@
     <t>UNIVERSO</t>
   </si>
   <si>
-    <t>ZONA 02</t>
-  </si>
-  <si>
     <t>ALTO DAS GREVILEAS</t>
   </si>
   <si>
@@ -585,9 +588,6 @@
     <t>BRASIL</t>
   </si>
   <si>
-    <t>CAMPOS ELISIOS</t>
-  </si>
-  <si>
     <t>CIDADE JARDIM</t>
   </si>
   <si>
@@ -756,6 +756,9 @@
     <t>JARDIM PAULISTA IV</t>
   </si>
   <si>
+    <t>JARDIM PIATA</t>
+  </si>
+  <si>
     <t>JARDIM PINHEIROS</t>
   </si>
   <si>
@@ -972,6 +975,9 @@
     <t>NOVA PAULISTA</t>
   </si>
   <si>
+    <t>OURO VERDE</t>
+  </si>
+  <si>
     <t>PARQUE ALVAMAR</t>
   </si>
   <si>
@@ -1038,9 +1044,6 @@
     <t>NOVO INDEPENDENCIA</t>
   </si>
   <si>
-    <t>OURO VERDE</t>
-  </si>
-  <si>
     <t>PARQUE ALVAMAR II</t>
   </si>
   <si>
@@ -1174,6 +1177,9 @@
   </si>
   <si>
     <t>33</t>
+  </si>
+  <si>
+    <t>34</t>
   </si>
   <si>
     <t>SEM_EPI</t>
@@ -1931,7 +1937,7 @@
         <v>411690</v>
       </c>
       <c r="B2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1949,7 +1955,7 @@
         <v>27142</v>
       </c>
       <c r="H2">
-        <v>361.1</v>
+        <v>364.7</v>
       </c>
       <c r="I2">
         <v>18.4</v>
@@ -1992,10 +1998,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4">
-        <v>410220</v>
+        <v>411740</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2004,16 +2010,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>4046</v>
+        <v>3193</v>
       </c>
       <c r="H4">
-        <v>222.4</v>
+        <v>250.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2024,42 +2030,42 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5">
-        <v>411090</v>
+        <v>412360</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G5">
-        <v>4530</v>
+        <v>1745</v>
       </c>
       <c r="H5">
-        <v>220.8</v>
+        <v>229.2</v>
       </c>
       <c r="I5">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6">
-        <v>411740</v>
+        <v>410220</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2068,16 +2074,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>3193</v>
+        <v>4046</v>
       </c>
       <c r="H6">
-        <v>219.2</v>
+        <v>222.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2088,138 +2094,138 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>411640</v>
+        <v>411090</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>3669</v>
+        <v>4530</v>
       </c>
       <c r="H7">
-        <v>218</v>
+        <v>220.8</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8">
-        <v>412530</v>
+        <v>411640</v>
       </c>
       <c r="B8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>5170</v>
+        <v>3669</v>
       </c>
       <c r="H8">
-        <v>212.8</v>
+        <v>218</v>
       </c>
       <c r="I8">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9">
-        <v>411520</v>
+        <v>412530</v>
       </c>
       <c r="B9">
-        <v>836</v>
+        <v>11</v>
       </c>
       <c r="C9">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>239</v>
+        <v>3</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>429660</v>
+        <v>5170</v>
       </c>
       <c r="H9">
-        <v>194.6</v>
+        <v>212.8</v>
       </c>
       <c r="I9">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="J9">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10">
-        <v>412450</v>
+        <v>411520</v>
       </c>
       <c r="B10">
-        <v>12</v>
+        <v>855</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G10">
-        <v>6463</v>
+        <v>429660</v>
       </c>
       <c r="H10">
-        <v>185.7</v>
+        <v>199</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11">
-        <v>410590</v>
+        <v>412450</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -2231,13 +2237,13 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="G11">
-        <v>23313</v>
+        <v>6463</v>
       </c>
       <c r="H11">
-        <v>175.9</v>
+        <v>185.7</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2248,10 +2254,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12">
-        <v>411110</v>
+        <v>410590</v>
       </c>
       <c r="B12">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2263,13 +2269,13 @@
         <v>2</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12">
-        <v>6228</v>
+        <v>23313</v>
       </c>
       <c r="H12">
-        <v>160.6</v>
+        <v>175.9</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2280,28 +2286,28 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13">
-        <v>410780</v>
+        <v>411110</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>4805</v>
+        <v>6228</v>
       </c>
       <c r="H13">
-        <v>124.9</v>
+        <v>160.6</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2315,7 +2321,7 @@
         <v>411480</v>
       </c>
       <c r="B14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -2324,7 +2330,7 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
         <v>18</v>
@@ -2333,39 +2339,39 @@
         <v>44749</v>
       </c>
       <c r="H14">
-        <v>122.9</v>
+        <v>127.4</v>
       </c>
       <c r="I14">
         <v>4.5</v>
       </c>
       <c r="J14">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>412360</v>
+        <v>410780</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="G15">
-        <v>1745</v>
+        <v>4805</v>
       </c>
       <c r="H15">
-        <v>114.6</v>
+        <v>124.9</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2411,7 +2417,7 @@
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -2420,7 +2426,7 @@
         <v>11</v>
       </c>
       <c r="E17">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
         <v>31</v>
@@ -2429,7 +2435,7 @@
         <v>128106</v>
       </c>
       <c r="H17">
-        <v>87.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="I17">
         <v>6.2</v>
@@ -2829,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -2854,16 +2860,16 @@
         <v>43</v>
       </c>
       <c r="B2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>17</v>
       </c>
       <c r="E2">
-        <v>10.9</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2939,16 +2945,16 @@
         <v>48</v>
       </c>
       <c r="B7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2956,7 +2962,7 @@
         <v>49</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -2965,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2993,13 +2999,13 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3007,16 +3013,16 @@
         <v>52</v>
       </c>
       <c r="B11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11">
-        <v>9.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3027,13 +3033,13 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3058,16 +3064,16 @@
         <v>55</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3078,13 +3084,13 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3109,13 +3115,13 @@
         <v>58</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -3129,13 +3135,13 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3146,13 +3152,13 @@
         <v>8</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3163,13 +3169,13 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3180,13 +3186,13 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3197,13 +3203,13 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3214,13 +3220,13 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3228,16 +3234,16 @@
         <v>65</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3245,16 +3251,16 @@
         <v>66</v>
       </c>
       <c r="B25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3265,13 +3271,13 @@
         <v>7</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3282,13 +3288,13 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3302,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28">
         <v>14.3</v>
@@ -3316,13 +3322,13 @@
         <v>7</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3333,13 +3339,13 @@
         <v>7</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3353,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E31">
         <v>14.3</v>
@@ -3367,13 +3373,13 @@
         <v>7</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3384,13 +3390,13 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3401,13 +3407,13 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3506,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3520,13 +3526,13 @@
         <v>6</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>2</v>
       </c>
       <c r="E41">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3537,13 +3543,13 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -3551,13 +3557,13 @@
         <v>84</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3588,13 +3594,13 @@
         <v>5</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -3605,13 +3611,13 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>1</v>
       </c>
       <c r="E46">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -3639,13 +3645,13 @@
         <v>5</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -3656,13 +3662,13 @@
         <v>5</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>80</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -3670,16 +3676,16 @@
         <v>91</v>
       </c>
       <c r="B50">
+        <v>5</v>
+      </c>
+      <c r="C50">
         <v>4</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
       <c r="D50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -3687,7 +3693,7 @@
         <v>92</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -3707,13 +3713,13 @@
         <v>4</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -3727,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3775,13 +3781,13 @@
         <v>4</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3792,13 +3798,13 @@
         <v>4</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3812,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3829,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3860,13 +3866,13 @@
         <v>4</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3880,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3928,13 +3934,13 @@
         <v>4</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3948,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -3962,13 +3968,13 @@
         <v>4</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>1</v>
       </c>
       <c r="E67">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3982,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3996,13 +4002,13 @@
         <v>4</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4016,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4030,13 +4036,13 @@
         <v>4</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4044,13 +4050,13 @@
         <v>113</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4061,16 +4067,16 @@
         <v>114</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4078,13 +4084,13 @@
         <v>115</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4101,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4135,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4152,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4166,13 +4172,13 @@
         <v>3</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4183,13 +4189,13 @@
         <v>3</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4200,13 +4206,13 @@
         <v>3</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4217,13 +4223,13 @@
         <v>3</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4234,13 +4240,13 @@
         <v>3</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4271,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4288,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4302,13 +4308,13 @@
         <v>3</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4319,13 +4325,13 @@
         <v>3</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
       <c r="E88">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4336,13 +4342,13 @@
         <v>3</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4353,13 +4359,13 @@
         <v>3</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4373,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -4387,13 +4393,13 @@
         <v>3</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4418,16 +4424,16 @@
         <v>135</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4435,13 +4441,13 @@
         <v>136</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -4452,13 +4458,13 @@
         <v>137</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -4509,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4560,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4577,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4594,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4611,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4642,13 +4648,13 @@
         <v>2</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E107">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -4679,7 +4685,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>50</v>
@@ -4696,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4710,13 +4716,13 @@
         <v>2</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E111">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -4730,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4747,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4795,13 +4801,13 @@
         <v>2</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E116">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -4815,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4829,13 +4835,13 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4846,13 +4852,13 @@
         <v>2</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -4866,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4880,13 +4886,13 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>1</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4900,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4914,13 +4920,13 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4934,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4948,13 +4954,13 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4985,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -5019,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -5050,13 +5056,13 @@
         <v>2</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -5084,13 +5090,13 @@
         <v>2</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5155,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -5172,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -5200,13 +5206,13 @@
         <v>181</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -5240,7 +5246,7 @@
         <v>0</v>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -5257,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -5682,7 +5688,7 @@
         <v>0</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -6294,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6311,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6345,7 +6351,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6379,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -6396,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -6427,13 +6433,13 @@
         <v>1</v>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212">
         <v>1</v>
       </c>
       <c r="E212">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -6444,13 +6450,13 @@
         <v>1</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D213">
         <v>1</v>
       </c>
       <c r="E213">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -6498,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -6583,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -6600,7 +6606,7 @@
         <v>0</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -6685,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -6719,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6733,13 +6739,13 @@
         <v>1</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D230">
         <v>0</v>
       </c>
       <c r="E230">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -6750,13 +6756,13 @@
         <v>1</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -6770,7 +6776,7 @@
         <v>0</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6821,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="D235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -6838,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -6855,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="D237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -6872,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -6886,13 +6892,13 @@
         <v>1</v>
       </c>
       <c r="C239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -6903,13 +6909,13 @@
         <v>1</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -7039,13 +7045,13 @@
         <v>1</v>
       </c>
       <c r="C248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E248">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249" spans="1:5">
@@ -7056,13 +7062,13 @@
         <v>1</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -7144,7 +7150,7 @@
         <v>0</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -7161,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -7175,13 +7181,13 @@
         <v>1</v>
       </c>
       <c r="C256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -7192,13 +7198,13 @@
         <v>1</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -7212,7 +7218,7 @@
         <v>0</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -7229,9 +7235,26 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" t="s">
+        <v>301</v>
+      </c>
+      <c r="B260">
+        <v>1</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
         <v>0</v>
       </c>
     </row>
@@ -7264,7 +7287,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -7281,7 +7304,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -7298,7 +7321,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -7315,7 +7338,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -7332,7 +7355,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7341,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -7349,7 +7372,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -7383,7 +7406,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -7400,7 +7423,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -7417,7 +7440,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -7451,7 +7474,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -7468,7 +7491,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -7485,7 +7508,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -7502,7 +7525,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B16">
         <v>2</v>
@@ -7536,7 +7559,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -7553,7 +7576,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -7570,7 +7593,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -7587,44 +7610,44 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B22">
         <v>2</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -7638,7 +7661,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -7655,7 +7678,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -7672,7 +7695,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>321</v>
+        <v>140</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -7681,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7689,7 +7712,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -7698,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7706,7 +7729,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -7715,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7723,7 +7746,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -7732,7 +7755,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7740,7 +7763,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -7757,7 +7780,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>327</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -7774,7 +7797,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>326</v>
+        <v>125</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -7791,7 +7814,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -7800,7 +7823,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7808,7 +7831,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -7825,7 +7848,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -7834,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7842,7 +7865,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -7851,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7859,7 +7882,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -7876,7 +7899,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -7885,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7893,7 +7916,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>250</v>
+        <v>334</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -7910,7 +7933,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>333</v>
+        <v>251</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -7919,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7927,7 +7950,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -7936,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7944,7 +7967,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -7953,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -7961,7 +7984,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -7978,7 +8001,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -7987,7 +8010,7 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -7995,7 +8018,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -8012,7 +8035,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -8029,7 +8052,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -8046,7 +8069,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -8063,7 +8086,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -8080,7 +8103,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -8097,7 +8120,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -8114,7 +8137,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -8131,7 +8154,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -8148,7 +8171,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -8165,7 +8188,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -8182,7 +8205,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -8204,20 +8227,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -8225,7 +8248,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -8233,7 +8256,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -8241,7 +8264,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B5">
         <v>14</v>
@@ -8249,7 +8272,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B6">
         <v>19</v>
@@ -8257,7 +8280,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B7">
         <v>26</v>
@@ -8265,7 +8288,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B8">
         <v>25</v>
@@ -8273,7 +8296,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B9">
         <v>29</v>
@@ -8281,7 +8304,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B10">
         <v>21</v>
@@ -8289,7 +8312,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B11">
         <v>31</v>
@@ -8297,7 +8320,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B12">
         <v>34</v>
@@ -8305,7 +8328,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B13">
         <v>23</v>
@@ -8313,7 +8336,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B14">
         <v>18</v>
@@ -8321,7 +8344,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B15">
         <v>35</v>
@@ -8329,7 +8352,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16">
         <v>51</v>
@@ -8337,15 +8360,15 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B17">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B18">
         <v>42</v>
@@ -8353,7 +8376,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B19">
         <v>51</v>
@@ -8361,7 +8384,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B20">
         <v>57</v>
@@ -8369,7 +8392,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B21">
         <v>67</v>
@@ -8377,7 +8400,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B22">
         <v>55</v>
@@ -8385,7 +8408,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B23">
         <v>68</v>
@@ -8393,7 +8416,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B24">
         <v>64</v>
@@ -8401,7 +8424,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B25">
         <v>57</v>
@@ -8409,7 +8432,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B26">
         <v>66</v>
@@ -8417,7 +8440,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B27">
         <v>66</v>
@@ -8425,7 +8448,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B28">
         <v>59</v>
@@ -8433,7 +8456,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B29">
         <v>69</v>
@@ -8441,15 +8464,15 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B30">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B31">
         <v>47</v>
@@ -8457,7 +8480,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B32">
         <v>41</v>
@@ -8465,7 +8488,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B33">
         <v>42</v>
@@ -8473,10 +8496,18 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B34">
-        <v>12</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>386</v>
+      </c>
+      <c r="B35">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8486,15 +8517,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C137"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>34</v>
@@ -8505,7 +8536,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -8516,7 +8547,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -8527,7 +8558,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -8538,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -8549,7 +8580,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -8560,7 +8591,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -8571,7 +8602,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -8582,7 +8613,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -8593,7 +8624,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -8604,7 +8635,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -8615,7 +8646,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -8626,7 +8657,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -8637,7 +8668,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -8648,7 +8679,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -8659,7 +8690,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -8670,7 +8701,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -8681,7 +8712,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -8692,7 +8723,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -8703,7 +8734,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -8714,7 +8745,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -8725,7 +8756,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -8736,7 +8767,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -8747,7 +8778,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C24">
         <v>13</v>
@@ -8758,7 +8789,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -8769,7 +8800,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -8780,7 +8811,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -8791,7 +8822,7 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C28">
         <v>13</v>
@@ -8802,7 +8833,7 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -8813,7 +8844,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -8824,7 +8855,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -8835,7 +8866,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -8846,7 +8877,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C33">
         <v>19</v>
@@ -8857,7 +8888,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -8868,7 +8899,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -8879,7 +8910,7 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -8890,7 +8921,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -8901,7 +8932,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -8912,7 +8943,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -8923,7 +8954,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -8934,7 +8965,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C41">
         <v>15</v>
@@ -8945,7 +8976,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -8956,7 +8987,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C43">
         <v>7</v>
@@ -8967,7 +8998,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C44">
         <v>9</v>
@@ -8978,7 +9009,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C45">
         <v>16</v>
@@ -8989,7 +9020,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -9000,7 +9031,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -9011,7 +9042,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C48">
         <v>9</v>
@@ -9022,7 +9053,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -9033,7 +9064,7 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -9044,7 +9075,7 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -9055,7 +9086,7 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C52">
         <v>11</v>
@@ -9066,7 +9097,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C53">
         <v>11</v>
@@ -9077,7 +9108,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -9088,7 +9119,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -9099,7 +9130,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C56">
         <v>11</v>
@@ -9110,7 +9141,7 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -9121,7 +9152,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C58">
         <v>13</v>
@@ -9132,7 +9163,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -9143,7 +9174,7 @@
         <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C60">
         <v>15</v>
@@ -9154,7 +9185,7 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C61">
         <v>21</v>
@@ -9165,7 +9196,7 @@
         <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -9176,10 +9207,10 @@
         <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -9187,7 +9218,7 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -9198,7 +9229,7 @@
         <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C65">
         <v>12</v>
@@ -9209,7 +9240,7 @@
         <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C66">
         <v>8</v>
@@ -9220,7 +9251,7 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C67">
         <v>13</v>
@@ -9231,7 +9262,7 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -9242,7 +9273,7 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C69">
         <v>15</v>
@@ -9253,7 +9284,7 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C70">
         <v>13</v>
@@ -9264,7 +9295,7 @@
         <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -9275,7 +9306,7 @@
         <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C72">
         <v>6</v>
@@ -9286,7 +9317,7 @@
         <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -9297,7 +9328,7 @@
         <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C74">
         <v>35</v>
@@ -9308,7 +9339,7 @@
         <v>18</v>
       </c>
       <c r="B75" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C75">
         <v>8</v>
@@ -9319,7 +9350,7 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C76">
         <v>9</v>
@@ -9330,7 +9361,7 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C77">
         <v>26</v>
@@ -9341,7 +9372,7 @@
         <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C78">
         <v>22</v>
@@ -9352,7 +9383,7 @@
         <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -9363,7 +9394,7 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C80">
         <v>22</v>
@@ -9374,7 +9405,7 @@
         <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -9385,7 +9416,7 @@
         <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C82">
         <v>23</v>
@@ -9396,7 +9427,7 @@
         <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C83">
         <v>20</v>
@@ -9407,7 +9438,7 @@
         <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C84">
         <v>18</v>
@@ -9418,7 +9449,7 @@
         <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C85">
         <v>6</v>
@@ -9429,7 +9460,7 @@
         <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C86">
         <v>11</v>
@@ -9440,7 +9471,7 @@
         <v>21</v>
       </c>
       <c r="B87" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C87">
         <v>20</v>
@@ -9451,7 +9482,7 @@
         <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C88">
         <v>22</v>
@@ -9462,7 +9493,7 @@
         <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C89">
         <v>10</v>
@@ -9473,7 +9504,7 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C90">
         <v>18</v>
@@ -9484,7 +9515,7 @@
         <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C91">
         <v>18</v>
@@ -9495,7 +9526,7 @@
         <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C92">
         <v>24</v>
@@ -9506,7 +9537,7 @@
         <v>23</v>
       </c>
       <c r="B93" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C93">
         <v>5</v>
@@ -9517,7 +9548,7 @@
         <v>23</v>
       </c>
       <c r="B94" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C94">
         <v>20</v>
@@ -9528,7 +9559,7 @@
         <v>23</v>
       </c>
       <c r="B95" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C95">
         <v>15</v>
@@ -9539,7 +9570,7 @@
         <v>24</v>
       </c>
       <c r="B96" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C96">
         <v>23</v>
@@ -9550,7 +9581,7 @@
         <v>24</v>
       </c>
       <c r="B97" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C97">
         <v>5</v>
@@ -9561,7 +9592,7 @@
         <v>24</v>
       </c>
       <c r="B98" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C98">
         <v>11</v>
@@ -9572,7 +9603,7 @@
         <v>24</v>
       </c>
       <c r="B99" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C99">
         <v>18</v>
@@ -9583,7 +9614,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -9594,7 +9625,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C101">
         <v>21</v>
@@ -9605,7 +9636,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C102">
         <v>7</v>
@@ -9616,7 +9647,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C103">
         <v>15</v>
@@ -9627,7 +9658,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C104">
         <v>22</v>
@@ -9638,7 +9669,7 @@
         <v>26</v>
       </c>
       <c r="B105" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C105">
         <v>17</v>
@@ -9649,7 +9680,7 @@
         <v>26</v>
       </c>
       <c r="B106" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C106">
         <v>12</v>
@@ -9660,7 +9691,7 @@
         <v>26</v>
       </c>
       <c r="B107" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C107">
         <v>13</v>
@@ -9671,7 +9702,7 @@
         <v>26</v>
       </c>
       <c r="B108" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C108">
         <v>24</v>
@@ -9682,7 +9713,7 @@
         <v>27</v>
       </c>
       <c r="B109" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C109">
         <v>16</v>
@@ -9693,7 +9724,7 @@
         <v>27</v>
       </c>
       <c r="B110" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C110">
         <v>6</v>
@@ -9704,7 +9735,7 @@
         <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C111">
         <v>19</v>
@@ -9715,7 +9746,7 @@
         <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C112">
         <v>18</v>
@@ -9726,7 +9757,7 @@
         <v>28</v>
       </c>
       <c r="B113" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C113">
         <v>23</v>
@@ -9737,10 +9768,10 @@
         <v>28</v>
       </c>
       <c r="B114" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C114">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -9748,7 +9779,7 @@
         <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C115">
         <v>22</v>
@@ -9759,10 +9790,10 @@
         <v>28</v>
       </c>
       <c r="B116" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C116">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -9770,7 +9801,7 @@
         <v>29</v>
       </c>
       <c r="B117" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -9781,10 +9812,10 @@
         <v>29</v>
       </c>
       <c r="B118" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C118">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -9792,10 +9823,10 @@
         <v>29</v>
       </c>
       <c r="B119" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C119">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -9803,7 +9834,7 @@
         <v>29</v>
       </c>
       <c r="B120" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C120">
         <v>13</v>
@@ -9814,10 +9845,10 @@
         <v>29</v>
       </c>
       <c r="B121" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C121">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -9825,10 +9856,10 @@
         <v>30</v>
       </c>
       <c r="B122" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C122">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -9836,10 +9867,10 @@
         <v>30</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C123">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -9847,7 +9878,7 @@
         <v>30</v>
       </c>
       <c r="B124" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -9858,10 +9889,10 @@
         <v>30</v>
       </c>
       <c r="B125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C125">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3">
@@ -9869,10 +9900,10 @@
         <v>30</v>
       </c>
       <c r="B126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C126">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:3">
@@ -9880,10 +9911,10 @@
         <v>31</v>
       </c>
       <c r="B127" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C127">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:3">
@@ -9891,10 +9922,10 @@
         <v>31</v>
       </c>
       <c r="B128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C128">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3">
@@ -9902,7 +9933,7 @@
         <v>31</v>
       </c>
       <c r="B129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -9913,7 +9944,7 @@
         <v>31</v>
       </c>
       <c r="B130" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C130">
         <v>9</v>
@@ -9924,10 +9955,10 @@
         <v>31</v>
       </c>
       <c r="B131" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C131">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="132" spans="1:3">
@@ -9935,10 +9966,10 @@
         <v>32</v>
       </c>
       <c r="B132" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C132">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:3">
@@ -9946,10 +9977,10 @@
         <v>32</v>
       </c>
       <c r="B133" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C133">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134" spans="1:3">
@@ -9957,10 +9988,10 @@
         <v>32</v>
       </c>
       <c r="B134" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3">
@@ -9968,10 +9999,10 @@
         <v>32</v>
       </c>
       <c r="B135" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C135">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:3">
@@ -9979,10 +10010,10 @@
         <v>33</v>
       </c>
       <c r="B136" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C136">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:3">
@@ -9990,10 +10021,43 @@
         <v>33</v>
       </c>
       <c r="B137" t="s">
+        <v>394</v>
+      </c>
+      <c r="C137">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138">
+        <v>33</v>
+      </c>
+      <c r="B138" t="s">
         <v>392</v>
       </c>
-      <c r="C137">
-        <v>5</v>
+      <c r="C138">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139">
+        <v>34</v>
+      </c>
+      <c r="B139" t="s">
+        <v>390</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140">
+        <v>34</v>
+      </c>
+      <c r="B140" t="s">
+        <v>394</v>
+      </c>
+      <c r="C140">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/tabelas/srag_15rs_2026.xlsx
+++ b/tabelas/srag_15rs_2026.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="396">
   <si>
     <t>codigo_ibge_6</t>
   </si>
@@ -195,15 +195,18 @@
     <t>JARDIM OLIMPICO</t>
   </si>
   <si>
+    <t>JARDIM UNIVERSO</t>
+  </si>
+  <si>
     <t>PARQUE TARUMA</t>
   </si>
   <si>
+    <t>ZONA 08</t>
+  </si>
+  <si>
     <t>JARDIM ITAIPU</t>
   </si>
   <si>
-    <t>JARDIM UNIVERSO</t>
-  </si>
-  <si>
     <t>PARQUE RESIDENCIAL TUIUTI</t>
   </si>
   <si>
@@ -219,9 +222,6 @@
     <t>ZONA 06</t>
   </si>
   <si>
-    <t>ZONA 08</t>
-  </si>
-  <si>
     <t>CHACARA PAULISTA</t>
   </si>
   <si>
@@ -249,6 +249,9 @@
     <t>VILA SANTA IZABEL</t>
   </si>
   <si>
+    <t>VILA VARDELINA</t>
+  </si>
+  <si>
     <t>CONJUNTO JOAO DE BARRO PORTO S</t>
   </si>
   <si>
@@ -270,9 +273,6 @@
     <t>VILA NOVA</t>
   </si>
   <si>
-    <t>VILA VARDELINA</t>
-  </si>
-  <si>
     <t>ZONA 7</t>
   </si>
   <si>
@@ -402,6 +402,9 @@
     <t>ITAIPU</t>
   </si>
   <si>
+    <t>JARDIM IMPERIO DO SOL</t>
+  </si>
+  <si>
     <t>JARDIM LIBERDADE</t>
   </si>
   <si>
@@ -465,6 +468,9 @@
     <t>EVEREST</t>
   </si>
   <si>
+    <t>GELBA RIBEIRAO COLOMBO</t>
+  </si>
+  <si>
     <t>GUAIRACA</t>
   </si>
   <si>
@@ -474,15 +480,15 @@
     <t>JARDIM DO CARMO</t>
   </si>
   <si>
+    <t>JARDIM EVEREST</t>
+  </si>
+  <si>
     <t>JARDIM GUAIRACA</t>
   </si>
   <si>
     <t>JARDIM IMPERIAL II</t>
   </si>
   <si>
-    <t>JARDIM IMPERIO DO SOL</t>
-  </si>
-  <si>
     <t>JARDIM INTERNORTE</t>
   </si>
   <si>
@@ -549,6 +555,9 @@
     <t>PARQUE INDUSTRIAL BANDEIRANTES</t>
   </si>
   <si>
+    <t>PARQUE RESIDENCIAL AEROPORTO</t>
+  </si>
+  <si>
     <t>PIATA</t>
   </si>
   <si>
@@ -705,9 +714,6 @@
     <t>JARDIM ESPANHA</t>
   </si>
   <si>
-    <t>JARDIM EVEREST</t>
-  </si>
-  <si>
     <t>JARDIM HANOVER</t>
   </si>
   <si>
@@ -837,9 +843,6 @@
     <t>PARQUE LAGOA DOURADA</t>
   </si>
   <si>
-    <t>PARQUE RESIDENCIAL AEROPORTO</t>
-  </si>
-  <si>
     <t>PARQUE RESIDENCIAL ELDORADO</t>
   </si>
   <si>
@@ -957,6 +960,9 @@
     <t>JARDIM PANORAMA</t>
   </si>
   <si>
+    <t>NOVA INDEPENDENCIA</t>
+  </si>
+  <si>
     <t>PARQUE RESIDENCIAL BOM PASTOR</t>
   </si>
   <si>
@@ -967,9 +973,6 @@
   </si>
   <si>
     <t>MAUA</t>
-  </si>
-  <si>
-    <t>NOVA INDEPENDENCIA</t>
   </si>
   <si>
     <t>NOVA PAULISTA</t>
@@ -1940,10 +1943,10 @@
         <v>99</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -1958,10 +1961,10 @@
         <v>364.7</v>
       </c>
       <c r="I2">
-        <v>18.4</v>
+        <v>36.8</v>
       </c>
       <c r="J2">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -2193,16 +2196,16 @@
         <v>411520</v>
       </c>
       <c r="B10">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="C10">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
       <c r="E10">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F10" t="s">
         <v>19</v>
@@ -2211,13 +2214,13 @@
         <v>429660</v>
       </c>
       <c r="H10">
-        <v>199</v>
+        <v>200.9</v>
       </c>
       <c r="I10">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="J10">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -2257,7 +2260,7 @@
         <v>410590</v>
       </c>
       <c r="B12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -2275,7 +2278,7 @@
         <v>23313</v>
       </c>
       <c r="H12">
-        <v>175.9</v>
+        <v>180.2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2318,66 +2321,66 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14">
-        <v>411480</v>
+        <v>410780</v>
       </c>
       <c r="B14">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="G14">
-        <v>44749</v>
+        <v>4805</v>
       </c>
       <c r="H14">
-        <v>127.4</v>
+        <v>145.7</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15">
-        <v>410780</v>
+        <v>411480</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G15">
-        <v>4805</v>
+        <v>44749</v>
       </c>
       <c r="H15">
-        <v>124.9</v>
+        <v>129.6</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -2417,7 +2420,7 @@
         <v>412625</v>
       </c>
       <c r="B17">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -2426,7 +2429,7 @@
         <v>11</v>
       </c>
       <c r="E17">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" t="s">
         <v>31</v>
@@ -2435,13 +2438,13 @@
         <v>128106</v>
       </c>
       <c r="H17">
-        <v>88.2</v>
+        <v>89</v>
       </c>
       <c r="I17">
         <v>6.2</v>
       </c>
       <c r="J17">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -2612,7 +2615,7 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -2630,10 +2633,10 @@
         <v>46.5</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2734,28 +2737,28 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27">
-        <v>411000</v>
+        <v>411420</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G27">
-        <v>5693</v>
+        <v>38313</v>
       </c>
       <c r="H27">
-        <v>35.1</v>
+        <v>36.5</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2766,28 +2769,28 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28">
-        <v>411420</v>
+        <v>411000</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G28">
-        <v>38313</v>
+        <v>5693</v>
       </c>
       <c r="H28">
-        <v>33.9</v>
+        <v>35.1</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2835,7 +2838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E260"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1">
@@ -3118,13 +3121,13 @@
         <v>9</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3132,13 +3135,13 @@
         <v>59</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3149,16 +3152,16 @@
         <v>60</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3169,13 +3172,13 @@
         <v>8</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3186,13 +3189,13 @@
         <v>8</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3203,13 +3206,13 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3223,7 +3226,7 @@
         <v>2</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23">
         <v>25</v>
@@ -3237,13 +3240,13 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3254,13 +3257,13 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3421,16 +3424,16 @@
         <v>76</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3441,13 +3444,13 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E36">
-        <v>16.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3458,13 +3461,13 @@
         <v>6</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3492,13 +3495,13 @@
         <v>6</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3509,13 +3512,13 @@
         <v>6</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3529,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3543,13 +3546,13 @@
         <v>6</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>2</v>
       </c>
       <c r="E42">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4294,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4311,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4328,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -4342,13 +4345,13 @@
         <v>3</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4362,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E90">
         <v>33.3</v>
@@ -4376,13 +4379,13 @@
         <v>3</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4396,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -4427,13 +4430,13 @@
         <v>3</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4444,13 +4447,13 @@
         <v>3</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>1</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4475,7 +4478,7 @@
         <v>138</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4498,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4532,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4549,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4583,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4600,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4617,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4651,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4682,13 +4685,13 @@
         <v>2</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E109">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -4719,7 +4722,7 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>50</v>
@@ -4736,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -4753,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -4767,13 +4770,13 @@
         <v>2</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -4787,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4835,13 +4838,13 @@
         <v>2</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E118">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -4855,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4869,13 +4872,13 @@
         <v>2</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -4886,13 +4889,13 @@
         <v>2</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -4906,7 +4909,7 @@
         <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4920,13 +4923,13 @@
         <v>2</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>1</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -4940,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4954,13 +4957,13 @@
         <v>2</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
         <v>1</v>
       </c>
       <c r="E125">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -4974,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4988,13 +4991,13 @@
         <v>2</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -5025,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -5059,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -5090,13 +5093,13 @@
         <v>2</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -5124,13 +5127,13 @@
         <v>2</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -5158,13 +5161,13 @@
         <v>2</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -5195,7 +5198,7 @@
         <v>0</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -5212,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -5223,7 +5226,7 @@
         <v>182</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5240,13 +5243,13 @@
         <v>183</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -5257,7 +5260,7 @@
         <v>184</v>
       </c>
       <c r="B143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -5314,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5382,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5399,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5433,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5464,13 +5467,13 @@
         <v>1</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -5501,7 +5504,7 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5518,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5637,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5671,7 +5674,7 @@
         <v>0</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5722,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5739,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5770,13 +5773,13 @@
         <v>1</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -5790,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5824,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E176">
         <v>100</v>
@@ -5841,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -5858,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -5923,13 +5926,13 @@
         <v>1</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -5960,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6011,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="D187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6028,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6062,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6093,13 +6096,13 @@
         <v>1</v>
       </c>
       <c r="C192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -6130,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="D194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>100</v>
@@ -6161,13 +6164,13 @@
         <v>1</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196">
         <v>1</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -6178,13 +6181,13 @@
         <v>1</v>
       </c>
       <c r="C197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -6198,7 +6201,7 @@
         <v>0</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6212,13 +6215,13 @@
         <v>1</v>
       </c>
       <c r="C199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -6266,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6300,7 +6303,7 @@
         <v>0</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6317,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="D205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6351,7 +6354,7 @@
         <v>0</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6368,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -6385,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -6402,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -6436,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -6450,13 +6453,13 @@
         <v>1</v>
       </c>
       <c r="C213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D213">
         <v>1</v>
       </c>
       <c r="E213">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -6484,13 +6487,13 @@
         <v>1</v>
       </c>
       <c r="C215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D215">
         <v>1</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -6521,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -6538,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -6606,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -6640,7 +6643,7 @@
         <v>0</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -6708,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -6725,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6742,7 +6745,7 @@
         <v>0</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6756,13 +6759,13 @@
         <v>1</v>
       </c>
       <c r="C231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -6776,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6793,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -6844,7 +6847,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -6861,7 +6864,7 @@
         <v>0</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -6878,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -6895,7 +6898,7 @@
         <v>0</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -6909,13 +6912,13 @@
         <v>1</v>
       </c>
       <c r="C240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -6926,13 +6929,13 @@
         <v>1</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -7062,13 +7065,13 @@
         <v>1</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -7079,13 +7082,13 @@
         <v>1</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -7167,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -7184,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -7198,13 +7201,13 @@
         <v>1</v>
       </c>
       <c r="C257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E257">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -7215,13 +7218,13 @@
         <v>1</v>
       </c>
       <c r="C258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -7235,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -7252,9 +7255,26 @@
         <v>0</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" t="s">
+        <v>302</v>
+      </c>
+      <c r="B261">
+        <v>1</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
         <v>0</v>
       </c>
     </row>
@@ -7287,7 +7307,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B2">
         <v>8</v>
@@ -7304,7 +7324,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B3">
         <v>7</v>
@@ -7321,7 +7341,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -7338,7 +7358,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -7355,7 +7375,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -7372,7 +7392,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -7389,7 +7409,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -7406,7 +7426,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -7423,7 +7443,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -7440,7 +7460,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -7474,7 +7494,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -7491,7 +7511,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -7500,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7508,41 +7528,41 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B16">
         <v>2</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="B17">
         <v>2</v>
@@ -7551,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7559,7 +7579,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>315</v>
+        <v>242</v>
       </c>
       <c r="B18">
         <v>2</v>
@@ -7568,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7576,7 +7596,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -7585,7 +7605,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7593,7 +7613,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -7610,7 +7630,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -7627,7 +7647,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -7644,7 +7664,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -7661,7 +7681,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -7678,7 +7698,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -7695,7 +7715,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -7712,7 +7732,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -7729,7 +7749,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -7746,7 +7766,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -7763,7 +7783,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -7780,7 +7800,7 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -7814,7 +7834,7 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -7831,7 +7851,7 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -7848,7 +7868,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -7865,7 +7885,7 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -7882,7 +7902,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -7899,7 +7919,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -7916,7 +7936,7 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -7933,7 +7953,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -7950,7 +7970,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -7967,7 +7987,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -7984,7 +8004,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -8001,7 +8021,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -8018,7 +8038,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -8035,7 +8055,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -8052,7 +8072,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -8069,7 +8089,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -8086,7 +8106,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -8103,7 +8123,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -8120,7 +8140,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -8137,7 +8157,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -8154,7 +8174,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -8171,7 +8191,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -8188,7 +8208,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -8205,7 +8225,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -8232,15 +8252,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -8248,7 +8268,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -8256,7 +8276,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B4">
         <v>20</v>
@@ -8264,7 +8284,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B5">
         <v>14</v>
@@ -8272,7 +8292,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B6">
         <v>19</v>
@@ -8280,7 +8300,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B7">
         <v>26</v>
@@ -8288,7 +8308,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B8">
         <v>25</v>
@@ -8296,7 +8316,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B9">
         <v>29</v>
@@ -8304,7 +8324,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B10">
         <v>21</v>
@@ -8312,7 +8332,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B11">
         <v>31</v>
@@ -8320,7 +8340,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B12">
         <v>34</v>
@@ -8328,7 +8348,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B13">
         <v>23</v>
@@ -8336,7 +8356,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B14">
         <v>18</v>
@@ -8344,7 +8364,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B15">
         <v>35</v>
@@ -8352,7 +8372,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B16">
         <v>51</v>
@@ -8360,7 +8380,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B17">
         <v>28</v>
@@ -8368,7 +8388,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B18">
         <v>42</v>
@@ -8376,7 +8396,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B19">
         <v>51</v>
@@ -8384,7 +8404,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B20">
         <v>57</v>
@@ -8392,7 +8412,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B21">
         <v>67</v>
@@ -8400,7 +8420,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B22">
         <v>55</v>
@@ -8408,15 +8428,15 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B23">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B24">
         <v>64</v>
@@ -8424,15 +8444,15 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B25">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B26">
         <v>66</v>
@@ -8440,15 +8460,15 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B27">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B28">
         <v>59</v>
@@ -8456,7 +8476,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B29">
         <v>69</v>
@@ -8464,7 +8484,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B30">
         <v>58</v>
@@ -8472,7 +8492,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B31">
         <v>47</v>
@@ -8480,7 +8500,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B32">
         <v>41</v>
@@ -8488,7 +8508,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B33">
         <v>42</v>
@@ -8496,18 +8516,18 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -8517,15 +8537,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>34</v>
@@ -8536,7 +8556,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -8547,7 +8567,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -8558,7 +8578,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -8569,7 +8589,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C5">
         <v>6</v>
@@ -8580,7 +8600,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -8591,7 +8611,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -8602,7 +8622,7 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C8">
         <v>9</v>
@@ -8613,7 +8633,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -8624,7 +8644,7 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -8635,7 +8655,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -8646,7 +8666,7 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C12">
         <v>14</v>
@@ -8657,7 +8677,7 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -8668,7 +8688,7 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -8679,7 +8699,7 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C15">
         <v>8</v>
@@ -8690,7 +8710,7 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -8701,7 +8721,7 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -8712,7 +8732,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -8723,7 +8743,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -8734,7 +8754,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C20">
         <v>8</v>
@@ -8745,7 +8765,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -8756,7 +8776,7 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C22">
         <v>4</v>
@@ -8767,7 +8787,7 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -8778,7 +8798,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C24">
         <v>13</v>
@@ -8789,7 +8809,7 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -8800,7 +8820,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -8811,7 +8831,7 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -8822,7 +8842,7 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C28">
         <v>13</v>
@@ -8833,7 +8853,7 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -8844,7 +8864,7 @@
         <v>8</v>
       </c>
       <c r="B30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -8855,7 +8875,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -8866,7 +8886,7 @@
         <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -8877,7 +8897,7 @@
         <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C33">
         <v>19</v>
@@ -8888,7 +8908,7 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -8899,7 +8919,7 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -8910,7 +8930,7 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C36">
         <v>10</v>
@@ -8921,7 +8941,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C37">
         <v>6</v>
@@ -8932,7 +8952,7 @@
         <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C38">
         <v>4</v>
@@ -8943,7 +8963,7 @@
         <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -8954,7 +8974,7 @@
         <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C40">
         <v>7</v>
@@ -8965,7 +8985,7 @@
         <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C41">
         <v>15</v>
@@ -8976,7 +8996,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -8987,7 +9007,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C43">
         <v>7</v>
@@ -8998,7 +9018,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44">
         <v>9</v>
@@ -9009,7 +9029,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C45">
         <v>16</v>
@@ -9020,7 +9040,7 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -9031,7 +9051,7 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -9042,7 +9062,7 @@
         <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C48">
         <v>9</v>
@@ -9053,7 +9073,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C49">
         <v>10</v>
@@ -9064,7 +9084,7 @@
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -9075,7 +9095,7 @@
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -9086,7 +9106,7 @@
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C52">
         <v>11</v>
@@ -9097,7 +9117,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C53">
         <v>11</v>
@@ -9108,7 +9128,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -9119,7 +9139,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -9130,7 +9150,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C56">
         <v>11</v>
@@ -9141,7 +9161,7 @@
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -9152,7 +9172,7 @@
         <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C58">
         <v>13</v>
@@ -9163,7 +9183,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -9174,7 +9194,7 @@
         <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C60">
         <v>15</v>
@@ -9185,7 +9205,7 @@
         <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C61">
         <v>21</v>
@@ -9196,7 +9216,7 @@
         <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -9207,7 +9227,7 @@
         <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C63">
         <v>6</v>
@@ -9218,7 +9238,7 @@
         <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -9229,7 +9249,7 @@
         <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C65">
         <v>12</v>
@@ -9240,7 +9260,7 @@
         <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C66">
         <v>8</v>
@@ -9251,7 +9271,7 @@
         <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C67">
         <v>13</v>
@@ -9262,7 +9282,7 @@
         <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -9273,7 +9293,7 @@
         <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C69">
         <v>15</v>
@@ -9284,7 +9304,7 @@
         <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C70">
         <v>13</v>
@@ -9295,7 +9315,7 @@
         <v>18</v>
       </c>
       <c r="B71" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -9306,7 +9326,7 @@
         <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C72">
         <v>6</v>
@@ -9317,10 +9337,10 @@
         <v>18</v>
       </c>
       <c r="B73" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -9328,21 +9348,21 @@
         <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C74">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B75" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -9350,10 +9370,10 @@
         <v>19</v>
       </c>
       <c r="B76" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C76">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -9361,21 +9381,21 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C77">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B78" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C78">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3">
@@ -9383,10 +9403,10 @@
         <v>20</v>
       </c>
       <c r="B79" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -9394,10 +9414,10 @@
         <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C80">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -9405,32 +9425,32 @@
         <v>20</v>
       </c>
       <c r="B81" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
         <v>391</v>
       </c>
       <c r="C82">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -9438,10 +9458,10 @@
         <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C84">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -9449,32 +9469,32 @@
         <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
         <v>391</v>
       </c>
       <c r="C86">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C87">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -9482,10 +9502,10 @@
         <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C88">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -9493,32 +9513,32 @@
         <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C89">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B90" t="s">
         <v>391</v>
       </c>
       <c r="C90">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B91" t="s">
         <v>392</v>
       </c>
       <c r="C91">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -9526,87 +9546,87 @@
         <v>23</v>
       </c>
       <c r="B92" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C92">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B93" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C93">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B94" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C94">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B95" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C95">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96" t="s">
         <v>390</v>
       </c>
       <c r="C96">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C98">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B99" t="s">
         <v>392</v>
       </c>
       <c r="C99">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:3">
@@ -9614,428 +9634,428 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C101">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B102" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C102">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C103">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B104" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C104">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B105" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C105">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B106" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C106">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C107">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B108" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C108">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B109" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C109">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B110" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C110">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B111" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C111">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B112" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C112">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B113" t="s">
         <v>390</v>
       </c>
       <c r="C113">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B114" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C114">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B115" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C115">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C116">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B117" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B118" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="C118">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B119" t="s">
         <v>394</v>
       </c>
       <c r="C119">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B120" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C120">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B121" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C121">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B123" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C123">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B124" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B125" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C125">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C126">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B127" t="s">
         <v>390</v>
       </c>
       <c r="C127">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B128" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C130">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B131" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C131">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B132" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C132">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B133" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C133">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B134" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B135" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C135">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B136" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C136">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B137" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C137">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B138" t="s">
         <v>392</v>
       </c>
       <c r="C138">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3">
@@ -10043,21 +10063,10 @@
         <v>34</v>
       </c>
       <c r="B139" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C139">
         <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3">
-      <c r="A140">
-        <v>34</v>
-      </c>
-      <c r="B140" t="s">
-        <v>394</v>
-      </c>
-      <c r="C140">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
